--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/kettle.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/kettle.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="kettle" sheetId="1" r:id="rId3"/>
+    <sheet name="kettle" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="522">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -299,12 +299,12 @@
 I did not share her past to speak of tragedies or the villagers' folly.</t>
   </si>
   <si>
-    <t xml:space="preserve">あの日…村を訪れた私が見たのは、命あるもの全てが死に絶えた凄惨な光景だった。それが彼女の「力」によるものかはわからない。だが、ロイテル、そして#pc、君たちには覚えておいてほしい。
+    <t xml:space="preserve">あの日…村を訪れた私を待っていたは、命あるもの全てが死に絶えた凄惨な静寂だった。それが彼女の「力」によるものかはわからない。だが、ロイテル、そして#pc、君たちには覚えておいてほしい。
 あの子は特別な力の元に生まれ、その力は確実に、彼女を取り巻くものたちの運命に影響を与えるだろう。
 もし君たちが望むなら、私とクルイツゥアは出ていくから、いつでも言ってくれ。</t>
   </si>
   <si>
-    <t xml:space="preserve">That day... what I saw when I visited the village was a horrific scene of death where every living thing had perished. Whether it was her ‘power’ I cannot say. But, Loytel, and you #pc, remember this. 
+    <t xml:space="preserve">That day... what awaited me in the village I visited was a horrific silence of death　where every living thing had perished. Whether it was her ‘power’ I cannot say. But, Loytel, and you #pc, remember this. 
 She was born under a peculiar power, and that power will undoubtedly affect the fates of those around her.
 If you ever wish us to leave, just say so.</t>
   </si>
@@ -600,7 +600,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">Their </t>
@@ -1836,7 +1836,7 @@
     <t xml:space="preserve">お、おほん…ということだ、#pcよ。
 この決断は私には荷が重い。お前に任せよう。
 死者の洞窟に赴き、「淀み」を見つけるんだ。そこでイスシズルに渡されたこの瓶を使うか、あるいはファリスさんに渡された「聖水」を使うか…それはお前次第だ、よく考えてくれ。
-…安心しろ、私もついていってやる。お前だけに責任を追わせるのは酷だからな。</t>
+…安心しろ、私もついていってやる。お前だけに責任を負わせるのは酷だからな。</t>
   </si>
   <si>
     <t xml:space="preserve">A-hem... So then, #pc.
@@ -2675,7 +2675,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">…フッ、まあ構いません。どのみち、この場に居る者の大半とは、もう二度と顔を合わせることもないのです。
@@ -2686,7 +2686,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">では、師よ。</t>
@@ -2730,7 +2730,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">…そして、僕にとって好都合とも言えるでしょう。
@@ -2740,7 +2740,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">竜の子と魔女の邂逅が意味するもの、 運命の糸に引かれた冒険者、そして何よりも師よ、魔石の秘密を知ってから、あなたという存在そのものが、僕の好奇心を離さないのです。</t>
@@ -2763,7 +2763,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">見返りか、そうだね、コルゴンがボロボロにした鍋の修理ぐらいは頼ませてもらうとするよ。
@@ -2774,7 +2774,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">そしてソリン、まだ私を師と呼ぶのなら、覚えておくといい。君も…私も、この世界にはまだ多くの学ぶべきことが残っているんだ、どれだけ長生きだろうともね。</t>
@@ -2784,755 +2784,6 @@
     <t xml:space="preserve">Well, I suppose I’ll at least ask you to repair the pots Corgon battered to pieces.
 But regardless, I welcome your stay here. 
 And Sorin, if you still call me your Master, remember. We still have much to learn from this world, however long our lives may be. </t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">你能听到风在用古老的语言低语吗？我为了学习风的故事，正在游历世界</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我有些问题</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我能帮到你什么吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">关于魔石</t>
-  </si>
-  <si>
-    <t xml:space="preserve">关于复制品贩卖</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(返回)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">帕罗米亚皇家图书馆的古书中，留下了一些关于魔石传承的记述。
-帕罗米亚曾经有三块蕴含着巨大力量的魔石。它们分别是霸者的魔石、贤者的魔石以及愚者的魔石，这些魔石曾给王国带来繁荣，但在扎西姆王的时代，这些魔石被作为保守某个秘密的代价送到了那些最强大最邪恶的存在身边。
-一个给了古代的王族，一个给了钢铁龙，还有一个给了不净的魔法师。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">此后魔石变成了怎样，扎西姆王守护的秘密到底是什么，很多学者和炼金术师们都挑战去阐明真相，但是答案却如同风中沙砾一般难以捉摸。
-也许能够在某一天解开这个谜团的，会是像你这样的冒险者吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">复制品贩卖？　嗯，我这么做是觉得能对你们的冒险活动有帮助。
-古老的炼金术中流传着一种可以复制物质特性的技术。虽然不能说所有的道具都可以进行复制，不过那些你已经制造过的手工道具和种子都可以复制哦。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">如果有想复制的物品，请交给我保管。虽然需要一些时间，但是可以定期的制作复制品。
-对了，可以复制的物品的最多个数和销售个数是根据我商店的规模决定的。虽然这样说也很令人难受，但是如果想要复制更多的物品的话，对我的商店投资就能帮上忙了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你好，罗伊特尔。怎么一副闷闷不乐的表情？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">凯特尔，你的弟子真是个难应付的孩子啊…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">弟子…？ 啊，是说库罗茨亚吗。她不是我的弟子。那孩子讨厌炼金术。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嚯，这又是为什么？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">因为她的母亲是炼金术师。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">库罗茨亚的母亲是我关系很好的朋友。她是一位乡下小村庄里的炼金术师，也是一位热情的研究者。但就像常见情况一样，村民们并不理解她。
-迷信的村民们疏远她，称她为魔女。作为「魔女」之子的库罗茨亚也受到村里孩子们排挤，天生颜色不同的两只眼睛也被人们称为「招来灾难之眼」，被大家所恐惧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">库罗茨亚的母亲因病去世后，她就被寄养在村中的教会，但是她在那里依然受到排挤。后来某一天，为了证明自己的清白，她用自己的手挖出了一只眼睛。
-我去到那个村子的时候，库罗茨亚就在村外的一间破烂小屋的床上，已经奄奄一息了。我用炼金术维系住了她的生命，同时也将我们的命运联结在一起。这就是她和我一直旅行的理由。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…这都是什么事啊。因为眼睛的颜色不同就把人当成魔女，简直愚蠢透顶！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我懂你会感到不平，但话说回来，人身上的一些特征有时也确实是一种与生俱来「力量」的表现呢。
-…我并不是为了讲述悲剧或者讽刺村民的愚蠢才告诉你有关她过去的事情。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那一天…我在抵达村子后所见到的，是所有曾拥有生命的东西全都死绝的凄惨景象。我不清楚那是不是她的「力量」导致的。但是，罗伊特尔，还有#pc，我希望你们能好好记住。
-那孩子于特殊的力量之下诞生，那份力量毫无疑问会影响她周围人的命运。
-如果你们不想让我们留下，那我和库罗茨亚就会马上离开。有这样的想法就随时告诉我吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">凯特尔……</t>
-  </si>
-  <si>
-    <t xml:space="preserve">连一点风都没有，真是个安静到让人不舒服的夜晚。你在那里吗，迪米塔斯？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哼…果然躲不过汝。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">汝依然如往昔一般，埃鲁丁…至少在外貌上如此。
-即便我如今沦为如此存在，与汝交谈时，仍会忆起我人类时的样子。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">当你还是人的时候，原来如此，呵呵…
-你从以前开始，遇到任何事就都会参一脚。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">夜夜在我的伙伴周围徘徊，散布奇怪故事，这确实是你的作风。
-…可你这是为了什么呢？竟会对那个女孩那么在意。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呵呵…不过是有点关心罢了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那女孩极为危险。汝也知道，她的瞳中寄宿着什么。
-灾眼乃是石之容器……而此时此刻，幼龙体内沉睡的魔石，也在渴求着那个容器。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">迪米塔斯，谢谢你的关心。但是，只要我还在这里，魔石就不会觉醒。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">原来如此，若是「最初的炼金术士」这样说，那便不会有错。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呵呵呵…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…尽管如此，埃鲁丁，命运依然会造访库罗茨亚与歌罗贡。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">龙之子与人类一同生活的传闻迟早会被人们知晓。或许常人不敢冒犯龙族……但唯有一人例外。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那人知晓魔石于扎西姆王的时代被送至钢铁龙手中，龙死后，他便虎视眈眈地寻找着那颗遗失魔石的下落。
-若那人听到龙之子的传闻，定不会不为所动。
-那人必将以魔石为目的，寻找库罗茨亚和歌罗贡。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">……伊斯西泽尔</t>
-  </si>
-  <si>
-    <t xml:space="preserve">没错，暗之畸形「伊斯西泽尔」。
-曾以伟大的魔法师之名享誉各地，却因对魔石着魔，变成了身陷黑暗之中的不洁怪物……他亦是汝无法杀之，也无法救之的可怜弟子。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">汝打算如何处理这个女孩？
-是想看她也沦为魔石的囚徒，还是看她被那人利用，又或是被杀呢……</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不要逃避现实，「凯特尔」。
-那女孩无法获得救赎。汝正试图重蹈覆辙。而汝的软弱，必将再次给这个世界带来灾难。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">能稍微占用大家点时间吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">姆啾？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">怎么了凯特尔？在这么晚的时候找我们。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">其实我们正面临着一些危险。
-有些事想让你们知道。关于曾是我弟子的那个男人，伊斯西泽尔的事，以及库罗茨亚眼中潜藏的力量的事…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嗯…。这可真是错综复杂啊。
-库罗茨亚体内流淌着古代魔女的血脉…然后，歌罗贡小小的身体里竟然有魔石…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">凯特尔先生，如果真的如您所说，伊斯西泽尔是冲着魔石来的…那我们现在就应该为保护库罗茨亚和歌罗贡做些相应的准备了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">又是你啊…有什么好笑的？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那位女孩与龙之子的安全不是问题。
-这世界本身，已然显露出末日的征兆，他们的存在即为象征。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这是什么意思，迪米塔斯先生？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这些家伙…「古老的存在」们只会给这个世界带来灾难和停滞。像他们那样强大的存在会滋生歪曲，其光辉会将周围的一切都卷入并焚烧殆尽。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">吾等所创造、在乎的一切，皆会被他们的法则轻易践踏，无论那是不是他们想要的。吾等皆为在恐惧中窥望命运的人偶。这样的世界，有何发展可言？
-众神因此停止干涉人类，并离开了这片大地。神之子…神所创造的古老存在亦应当效仿。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…呃？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…即是说，无论伊斯西泽尔，龙亦或是魔女，这些碍事之物唯有被消灭掉才对这个世界好。
-凯特尔，可曾忘记汝之仁慈所引发的灾祸？汝本应杀死伊斯西泽尔。而如今，汝亦当杀死这位女孩与龙之子。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">喂喂喂，这是说到哪去了。这话可我可不能当没听到。
-你当自己是什么人？就想决定这些孩子的生死？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">库罗茨亚极其危险。汝当深知此事。此女的灾厄之眼，已将一村覆灭。而且其力量尚未「觉醒」。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">但是引起这件事的契机是什么？是把库罗茨亚逼迫到绝境的迷信村民们吧？
-这孩子对自己的力量根本一无所知。因此受到谴责就更不应该了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那么，是要因为怜悯那女孩，任由这世界灭亡也无妨？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这，这个嘛…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…我才不在乎。如果这个世界如此不通情理，否定库罗茨亚存在，那它毁灭了才好。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">姆啾！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">法…法莉斯小姐，这么说就太过分了…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不，罗伊特尔大人。库罗茨亚是我们重要的伙伴。为了保护她我什么都愿意做。就算要对抗这个世界的天意。
-…这是理所当然的吧，罗伊特尔大人？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">当…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">当然了！
-不，应该说是你让我再次看清了一切，法莉斯小姐。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我并不关心这个世界怎样。
-库罗茨亚的命运由库罗茨亚自身来决定。我不会让任何人说三道四，我会从伊斯西泽尔这些家伙的手中保护他们。
-仅此而已。这都是理所当然的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">至于迪米塔斯说的「古老的存在」什么的，我觉得伊斯西泽尔那种危险的家伙也是不能跟库罗茨亚他们相提并论的。
-他们可是会互相叫着「妈…妈…」「歌罗贡♪」在一起腻腻歪歪一整天的，有哪个危险的古老存在会这样？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">法莉斯…罗伊特尔…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">任由感情驱使，不明事理的愚钝之人…如此定论，只会让同样的错误再次重演。
-汝等不知，那种无法拯救，亦无法毁灭的苦痛。汝等的仁慈，终将为此女带来更大的悲哀！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">迪米塔斯…难道说，你还在为特蕾西亚的事情…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">特蕾西亚…？ 呵…是吗，呵呵呵…原来如此。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呵呵…原来是在此女身上看到她的影子…真不像我会做的事…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…算了，我们互相还不够了解呢。但是这点可以靠时间可以解决。
-当务之急是要大家共同努力，想想把伊斯西泽尔赶走的方法。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我赞成，罗伊特尔。关于这点，我也有些想法。
-…但是，今天就到此为止吧。已经快天亮了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哼，真是的，为了这种理所当然的结论，居然消耗了一整晚的时间。
-#pc，你听到了么？ 接下来要有的忙了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…索林，是你吗？自从和你最后一次见面，已经不知过了多少岁月。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你还记得我吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（无法听懂的古代语言）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真令我意外。就是说，你依然…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你在等着…我？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哼，这样就差不多了吧。我已经好久没以这个样子示人了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">如何，用现在的样子我们就能更方便地对话了吧，老师？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">知道你还记得自己以前的样子，让我放心多了，索林。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真是讽刺。无论我是否记得自己从前的样子，我都从未拥有过你所期待的人性。
-…无所谓了。我可不想给时隔二百年的再会泼冷水。就像以前一样在这个昏暗的房间里聊聊…关于「魔石」的事吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">看起来，我的到来和我的来意，都早被你看穿了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…钢铁龙「歌罗贡」。过去被帕罗米亚王授予魔石的伟大之龙，在二十年前被屠龙者「托兰」消灭。但是愚蠢的托兰并没有带回魔石，后来魔石的下落便不知所踪。
-…直到最近，你们找到了歌罗贡的遗孤。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">听到龙之子传闻的那天，我就找到了它。这对我来说易如反掌。原本我只需杀了龙之子，再夺取魔石即可。然而，我却看到了在龙之子身旁的你。
-于是，我就在这个城里等着你的到来。我知道，如果是你的话一定会来这里。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好了，说来听听吧，老师。你对那个龙之子…还有龙体内的魔石到底有何打算？
-你早在几百年前就同意了我的计划。难道这期间有什么让你改变了心意？　毕竟你没有带龙之子来见我，也就是说你已经不打算继续协助我了吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">正如你所说，我不能交出歌罗贡。在我说出理由前，有一件事我要问你，索林。你还在继续研究魔石吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哼，那是当然的。灵魂被束缚在腐臭的躯体里，还要背上暗之畸形这样忌讳的名号在朽烂阴暗的古城中生活，难道我甘愿这样还能是有什么其他理由？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我必须揭开魔石的秘密。
-…诸神离去，神秘正从这个世界中逐渐消失。「古老的存在」也都在缓缓地步入衰亡。这一切都意味着魔法的终结。
-没错，我是必须得到魔石。让这个世界继续存在下去，依靠魔石的力量，将诸神再度呼唤回大地。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">如你所知，如今的世界，无论是「古老的存在」们，还是神秘的根源——魔法，都在无声地消失。
-我不清楚这一切消亡的终点是会在百年后还是千年后。但是自从诸神离开之后，这个结果就已经是我们无法逃离的宿命了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">正是如此…这样下去再过不久神话就会变成睡前讲的陈年故事，元素精灵也将不复存在，变成只能从书中插画才看得到的东西。
-但是，你有没有这样想过，也许这才是世界回到了原本的样子？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">原本那个无聊、野蛮、连生存价值都没有的世界吗？
-…你所说的这种变化如今已经有所预示了。曾席卷整个西埃尔·泰尔的古代艾沃达纳失去了昔日的荣光，倒是在东方出现了一支以科学为势的新王国耶鲁正在日益兴盛。魔法正在被降格为单纯的学问，古老的种族大多都面临被人类灭亡或奴役的命运。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">是的，人的时代正在到来。而且，如果回顾这个星球的整个历史你就会明白…正如艾斯·泰尔或是莱姆·伊德的下场一样，人类迟早会仓促地走向灭亡之路。而他们甚至不会理解自己夺走和破坏之物的价值。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">无论什么文明，终结都不可避免。然而有毁灭，就会有新生。你不觉得这才是超越了我们善恶观的真理吗，索林？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哼，这话题就到此为止吧，别再拐弯抹角了。
-人类的盛衰，善恶…这些都是该诸神去考虑的事情，与我无关。我只是不想失去我的力量。能够摆布世界的魔法之力就是我的一切。我无论如何都不能容忍它被夺走。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…老师啊，二百年前，你为什么没有杀我呢？　我还以为我们是坐在同一条船上。
-难道说你来这座城堡，是为了弥补二百年前没有对我下手的遗憾吗？　可惜我的力量早已今非昔比，也远远超过了你。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">魔石是原初时代众神所创之物…只要解析它的力量，就能将诸神重新唤回大地，阻止这个世界的「退化」。
-…我要杀了龙之子得到魔石。就算你想阻止也是徒劳的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">索林，你误会一件事情。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">误会…？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你的魔石研究，已经完成了。你恐怕已经把魔石的力量「全部激发出来了」。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">研究已经完成？　开什么玩笑。魔石之力岂会仅有如此程度…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你已经掌握了魔石的力量。但是…没错，正如你所察觉的那样，很遗憾，那个魔石…不，就算你拿到另外两个魔石，也远远无法达到你所期望的力量。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哼，还以为你要说什么…老师啊，连魔石都没有的你究竟懂什么？
-确实，你对魔石的研究之深令人匪夷所思，但那都是陈年旧事了。如今的你的知识不可能比得过在这件事上倾注了二百年时间的我。
-魔石蕴藏的力量，可以打开众神领域的大门，把众神唤回大地…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…如果是真正的魔石，那或许可以。但是，你所拥有的不过是魔石的伪造品。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真是胡说八道…呵呵，你就是为了说这种蠢话才特意来找我的？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">索林，你的魔石，是我做的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">老师啊，你是什么时候学会说这种笑话的…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你不信吗…也难怪。
-那就来看看我的眼睛吧，索林。看看我眼中被刻下的永恒的诅咒。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你一定听说过《奥拉的石晶》的传说吧，这才是真正的魔石啊，索林。
-你和歌罗贡手中魔石，不过是很久以前，我模仿石晶制作的仿品。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不可能…《奥拉的石晶》…永恒之瞳…？　那只是神话故事里的…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神话……　是…是…真的…？　是吗，是这样啊…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呵呵…呵呵呵…我竟然也会犯下这种错…原来如此，原来是这样啊…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「最初的炼金术师」…。这样啊，你才是一切的起点。
-人类在这个时代发出第一声啼哭时，你就已经活着了。不，应该说是没能死成吧。现在我明白了。你眼睛的秘密，还有你没有杀我的理由。
-呼，请坐吧，老师。我们似乎还有很多话要说。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那么，那个传说就应该是真的了。
-…她还身为森林的精灵时的名字是奥拉。
-爱上了人类男子，将自己囚禁在石棺中的她，最终与向往天空的雏鸟一起展翅高飞，升格为了女神。没错，这就是璐璐薇诞生的神话。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">虽然这段神话很有名，但几乎没有记录有关那人类男子之后命运的书籍留存下来。
-有一种说法是，奥拉…不对，是璐璐薇。为了把自己曾倾心于人类这件事当作教训，就给予了那男人残酷的命运。为了让那男人再也看不到她的身影，她夺走了他的双眼，还对他施加了不死的诅咒。因为她知道那个男人今后也会爱着自己，所以这样就可以让他承受永远的痛苦。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…女神璐璐薇诞生于上古时代，那是被人们称作「起源的时代」的第二纪。那之后到底是经过了多少的岁月？　数千万年，不，数亿年…？
-哼哼，真没想到…老师啊，也不知这世界上无数的秘密还会有多少与你有关？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">可以确定的是，那都不会是让人羡慕的经历。
-那传说毫无疑问也是我本人写的，但流传至今会不会出现偏差就另当别论了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">没错，我在那片森林里…「偶然」遇见了已经成为女神的她。
-当她转向我的瞬间，我的眼睛就被刻上了这石晶。感情也好，言语也罢，什么都没有了。在那以后，我曾在永恒的黑暗中追寻过她的声音，她却再也没有在我面前出现过。
-这眼睛，也算不上什么惩罚，只是她随性而起的决定罢了。对于已经成为女神的璐璐薇，我不过是风中的一粒尘埃，根本不是什么值得让她留意的东西。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…话虽如此，这双眼睛却成了我与璐璐薇唯一的联系。只要解开这双眼睛的秘密，或许就能再一次得到她的垂怜。我就是怀揣着这份微弱的希望，开始不分昼夜地探寻晶石的秘密，也是这份热忱最终驱使我踏上了仿造晶石的道路。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不知不觉中我就被称为了伟大的炼金术师。但是人的智慧还是难以企及神的奇迹。我创造的无数魔石中没有一个能拥有和这双眼一样的力量。
-…最终我放弃了，赝品的魔石也被埋藏进了历史的尘埃之中。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…然而，你所创造的那三块魔石却在经过漫长时间的考验后又出现在了这个时代。是这样吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…嗯，没错。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你在得知弟子拿到魔石，成了那股力量的俘虏时，就来到了我所在的城堡。你一向对弟子关爱有加，所以你是为了拯救我的灵魂，来杀我的。
-但当你知道我的计划时…你犹豫了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你想到如果把我强大的魔力与魔石结合起来，也许真的可以把众神唤回大地。
-这样一来或许你就能和璐璐薇重逢，好知晓你眼中诅咒的真正含义。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…这双眼睛的含义吗。其实这件事已经无所谓了。
-索林，我只是想再见一次璐璐薇。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呵呵，呵呵呵…老师啊，看来你我之间终于能找到一个共同点了。
-在你内心的深处，也有一股理性和道德都无法压制的黑暗火焰在燃烧着。你和我一样，都有着无论这个世界变得怎样也没法放下的强烈愿望。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…而成为你这股黑暗热情牺牲品的，就是我的身体吗。
-让我变成污秽的怪物，去渴求伪造的魔石。这可真是…太好笑了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…抱歉，索林。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不，老师。
-…讽刺的是，这污秽的身体除了延长了我可悲的生命之外，也还是有点别的用处的。
-倒不如说在魔石研究之路被断绝的现在，靠这幅身体所得到的知识才成了我最后的希望。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你是什么意思，索林？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">死者的世界里，是有活人无从知晓的秘密的。
-但在谈论这秘密之前，有一件事情我们必须说清楚。即使夺取龙之子的假魔石对我而言几乎没有意义…但也只是「几乎」而已。多拿一块魔石对我是没有坏处的。
-毕竟交涉筹码还是在拥有夺取魔石力量的我手中。 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">你的意思是…有事情想让我做吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你如此通情达理真是太好了。其实也没什么，只是想让你帮忙做一件小事。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在离这座古城稍有距离的沼泽地里，有一个无人靠近的洞窟。在那个被称为「死者的洞窟」之处的深处，有着被死者守护，但死者无法接近的「黑潭」。
-…拿好这个瓶子。
-我希望你把这个瓶子里的液体滴一滴到那个「黑潭」里。
-…怎么样，很简单吧？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">当然，要进入死者洞窟的深层也需要相当的实力。和跟你在一起的冒险者商量一下就好了吧。
-呵呵，你看起来一脸诧异呢…但我不会告诉你更多的秘密了。
-那一滴显现效果只会是在几百年后了。至少我可以保证这件事绝对不会危害到你的同伴。我认为用这件事换来龙之子的性命还是很划算的，你觉得呢，老师？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">啊…是凯特尔。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">欢迎回来，凯特尔！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我回来了，库罗茨亚，歌罗贡。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">闷闷不乐的表情呢…怎么了？　果然是…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不是的，不是坏消息。只是…
-是啊，首先，能叫大家来吗，库罗茨亚？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">姆啾…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…事情就是这样了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">原来如此，作为保证歌罗贡安全的交换条件，要向那个「黑潭」里面滴一滴液体吗。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嗯…探索洞窟时肯定少不了#pc的帮助。不过也就是滴一滴液体而已，好像也没什么危险，这听起来是笔不错的买卖？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不行。绝对不能把那瓶子里的液体和「黑潭」混合！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">可是，法莉斯小姐…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不，听我说，罗伊特尔大人。我觉得这事情没有那么简单，甚至可能有邪恶的阴谋。
-关于死者的洞窟，其实流传着这样一种传说。
-那洞窟中曾有一个「污秽不净之人」，在里面不断重复着令人毛骨悚然的可怕仪式。尽管足以威胁大地与天界的异形最终被诸神消灭了，但污秽不净之人的血肉却溶入了洞窟的最深处，变成了绝对不会干涸的黑色淤积物。
-罗伊特尔大人，那「黑潭」是凡人绝不能接触的东西。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">原来如此，真是可怕的传说…等等，原来是这样，我懂了。
-将瓶中的东西滴一滴到淤积物里，在数百年后让邪恶发芽…一个连众神都无法忽视的邪恶…就能成为让众神回归地上的诱饵。这一定就是他的打算吧。
-确实，如果听了伊斯西泽尔的要求，肯定会给后世留下不得了的诅咒之物。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">可…按照凯特尔所说的，伊斯西泽尔是十分强大的魔法师。如果我们拒绝了这笔交易，光靠自己的力量能从他手中守住这只小不点龙么？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不是的，不需要拒绝这笔交易。我有一样东西，罗伊特尔大人。
-就拿这个瓶子代替吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">代替？　这是哪来的瓶子？　确实很像伊斯西泽尔交给我们的瓶子…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嗯…但是，这个瓶子里是股清爽的香味。里面装的是哪种圣水吗？
-我懂了，你是想利用圣水把「黑潭」净化掉吗。不愧是法莉斯小姐…可是这样的东西到底是哪里来的？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不过…这味道还真是让人舒服。清香又清爽，…对了，简直就像刚洗好的…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">难道说这里面是…呃，算了，刨根问底就有点不识趣了。我觉得这主意不错，法莉斯小姐。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">至少，这瓶子里的一滴液体不至于把邪神唤回这个世界。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">是…是啊。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嗯，咳咳…事情就是这样了，#pc。  
-这个决断对我而言太沉重了，还是交给你吧。
-前往死者的洞窟，找到「黑潭」。至于在那里是用伊斯西泽尔的瓶子，还是用法莉斯小姐交给我们的「圣水」…就看你的了。
-…不过放心吧，我也和你一起去。让你独自承担责任也太残酷了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这就是「黑潭」吗。
-漆黑又浑浊…只是凝视着就仿佛要被吞噬一样。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真是个恶心的地方。办完伊斯西泽尔的事，就早点离开吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这点我完全赞同。
-向这「黑潭」滴下一滴液体…简单的工作。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那么，#pc，要用哪个瓶子呢？是伊斯西泽尔给的那个可疑的瓶子，还是法莉斯小姐特制的洗…圣水呢。
-（…喂，#pc，听得到吗？）
-（法莉斯小姐虽然也跟来了，不过放心吧，不管你怎么选，我都不会让她知道的。我尊重你的决定。）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">使用伊斯西泽尔的瓶子</t>
-  </si>
-  <si>
-    <t xml:space="preserve">使用法莉斯的瓶子</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…伊斯西泽尔的瓶子没错吧？
-这污秽至极的气味。恐怕只要一滴，就能孕育出邪恶之物。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">是的</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不是</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…法莉斯小姐的瓶子没错吧？
-十分…好闻的味道。只是很难想象这一滴下去会发生什么啊。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好了。那么我就把这瓶子里的液体滴一滴到「黑潭」里吧。
-不，#pc，这里就交给我吧。不能把重担压在你一个人身上。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…一想到这一滴或许会改变世界的命运，就让人感到窒息。
-而且这地板好像变得…有点黏糊糊的…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">啊！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">冷、冷静点，我没事！
-…呼，全身都湿透了，真恶心啊，还好这「黑潭」没有多深。
-哈啊…瓶子…那两个瓶子去哪里了？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…罗伊特尔大人…！！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">法莉斯小姐，冷静点…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">后面，你后面！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">什么…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">虽然我根本不知道它在说什么，但是看上去相当生气啊。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哦哦…污秽不净之人安茨拉西祖鲁…曾令世间陷入恐惧，被众神封印的邪神…！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…这个「黑潭」的真面目，就是迟早萌芽的灾厄之种吗。正好，这种东西，就该趁现在彻底斩草除根。
-呼，就算是邪神，在那清新的香气下也无法发挥全部力量。
-来吧，#pc，接下来就交给你了！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哦哦，做得好，#pc！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">干得漂亮，#player大人。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在那怪物出来的时候，我还以为完蛋了呢…嗯，不过最终还是船到桥头自然直。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">伊斯西泽尔这家伙…真是个疯子。居然为了自己的野心，打算在将来放这样的家伙出来。
-可是这下麻烦了啊。这样一来我们就无法实现和他的约定了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我们什么都没看到，这里什么都没发生…没错吧，罗伊特尔大人？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…嗯。虽然我觉得他不会这么轻易就相信，但也没别的办法了。
-好了，总之我们先回到据点，等待伊斯西泽尔吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">凯特尔…有时间吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">怎么了，库罗茨亚？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">刚才有个我们没见过的黑袍男孩，他一直盯着我和歌罗贡看。正打算和他搭话的时候，迪米塔斯突然气势汹汹地插了进来，和他吵了起来…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…是吗，我也觉得他差不多该出现了呢。
-那个穿黑袍的叫索林，是伊斯西泽尔的人类形态。迪米塔斯和他在过去曾有些因缘。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那孩子是…伊斯西泽尔？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">没什么好怕的，库罗茨亚。我们在死者的洞窟已经完成了与他的约定。
-没错吧，罗伊特尔？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…那个，凯特尔…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">怎么了？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">没、没什么，确实危险已经过去了…不过以防万一还是问一下。如果伊斯西泽尔发怒的话…会发生什么？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">像他这样的魔法师，如果有那个意愿，力量足以轻松毁灭一个国家。他应该是这个时代里，我们最不该去惹怒的一个人了。
-但是，不用担心，罗伊特尔。要说为什么的话，呵呵，如果你做了什么「让他发怒」的事情的话，你早就已经在地下长眠了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…哈…哈哈哈，这样啊…！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（交头接耳）法莉斯小姐，「黑潭」发生的事情，绝对不能让他知道。凯特尔都开始起疑心了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（交头接耳）好的，罗伊特尔大人…不能把它编成歌曲真是遗憾，但这次也是不得已了啊。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…好了，迪米塔斯这会儿应该也冷静下来了。我们去听听他要说什么吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…那么，可以认为约定已经顺利完成了吧？
-没事，只是确认下而已。对「黑潭」的干涉，我也能立刻感受到。只是…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">只是…？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">只是从那时起，我就失去了部分魔力。准确来说，我失去了「伊斯西泽尔」的不死之躯。
-哼，当然，这也意味着「黑潭」再次开始活动，无疑是令我欣喜的证据。
-无须担心。只要「黑潭」中那位的力量增长，我的魔力也会随之恢复。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你失去了魔力吗？　真是太好…不对，真是灾难啊！
-那么，歌罗贡和库罗茨亚已经不会再面临危险了吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…老师啊，为了让这里的这群愚钝之人也能理解，您最好还是好好教教他们。对魔法师而言，话语是多么沉重的东西。
-我决定遵守约定。即便我现在依然留有足够的魔力，可以仅因那个男人触怒了我而将此地化为地狱。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…哼，也罢。 反正我与大多数在场者，今后都不会再相见了。 
-看到了龙与魔女这种稀罕物，和老朋友来了场充实又融洽的交流，看来是不虚此行了。
-那么再会了，老师。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…索林，你真的打算以这样的身体返回那古城吗？
-我并无恶意，之前拜访的时候，那里看起来可不像是「人类」能够放松休息的地方啊。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呵呵，别摆出那么可怕的表情啦。我换个说法吧。
-为什么不在你的魔力恢复之前，试着在这里生活呢，索林？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（嘶…）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这可真是…意外的邀请啊，老师。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…而这对我来说也很有利。
-龙之子与魔女邂逅的意义， 被命运之线所牵引的冒险者，还有最重要的是，老师，在知晓了魔石的秘密后，对于你这个存在本身，我实在难以放下好奇心啊。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">当然，我不打算免费住下。
-你希望从我这里得到什么作为回报呢？ 是失落的上古魔法书，长生不老的灵药，还是说，想要制造一批不眠不休能一直劳作的死者军团呢？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">回报吗，对了，被歌罗贡弄坏的锅就拜托你修理吧。
-不过首先，还是要欢迎你的留宿。
-还有索林，如果你还称呼我为老师的话，就记住一点。不管是你也好…我也好，无论我们活了多久，在这世上都仍有很多需要学习的事物。</t>
   </si>
 </sst>
 </file>
@@ -3554,25 +2805,25 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -3586,7 +2837,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -3651,7 +2902,7 @@
     <font>
       <sz val="10"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -3670,7 +2921,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -3679,110 +2930,110 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3796,13 +3047,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -3978,26 +3229,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:IX451"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.85" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.85" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.28" style="1" customWidth="1"/>
-    <col min="4" max="5" width="11.85" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
-    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
-    <col min="10" max="10" width="60.76" style="1" customWidth="1"/>
-    <col min="11" max="11" width="62.33" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.06" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="60.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="62.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.06"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4035,24 +3286,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="I2" s="1">
-        <f>MAX(I4:I1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I2" s="1" t="n">
+        <f aca="false">MAX(I4:I1048576)</f>
         <v>281</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="12.8">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" ht="13.8">
-      <c r="I8" s="1">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -4061,15 +3312,12 @@
       <c r="K8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L8" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="9" ht="12.8">
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" ht="12.8">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
@@ -4079,7 +3327,7 @@
       <c r="E10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10" s="1" t="n">
         <v>2</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -4088,11 +3336,8 @@
       <c r="K10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L10" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="11" ht="12.8">
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E11" s="1" t="s">
         <v>21</v>
       </c>
@@ -4100,21 +3345,21 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" ht="12.8">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E12" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" ht="12.8">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E13" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" ht="12.8">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I15" s="1">
+      <c r="I15" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J15" s="1" t="s">
@@ -4123,18 +3368,15 @@
       <c r="K15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L15" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="16" ht="12.8">
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="1">
+      <c r="I16" s="1" t="n">
         <v>4</v>
       </c>
       <c r="J16" s="1" t="s">
@@ -4143,11 +3385,8 @@
       <c r="K16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L16" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="17" ht="12.8">
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
         <v>30</v>
       </c>
@@ -4157,7 +3396,7 @@
       <c r="E17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I17" s="1">
+      <c r="I17" s="1" t="n">
         <v>21</v>
       </c>
       <c r="J17" s="1" t="s">
@@ -4166,18 +3405,15 @@
       <c r="K17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="L17" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="18" ht="12.8">
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I18" s="1">
+      <c r="I18" s="1" t="n">
         <v>5</v>
       </c>
       <c r="J18" s="1" t="s">
@@ -4186,11 +3422,8 @@
       <c r="K18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L18" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="19" ht="12.8">
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="1" t="s">
         <v>13</v>
       </c>
@@ -4198,13 +3431,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" ht="12.8">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="22" ht="116.4">
-      <c r="I22" s="1">
+    <row r="22" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I22" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J22" s="5" t="s">
@@ -4213,12 +3446,9 @@
       <c r="K22" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="L22" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="23" ht="74.6">
-      <c r="I23" s="1">
+    </row>
+    <row r="23" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="1" t="n">
         <v>7</v>
       </c>
       <c r="J23" s="7" t="s">
@@ -4227,22 +3457,19 @@
       <c r="K23" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L23" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="24" ht="12.8">
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="26" ht="12.8">
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="27" ht="64.15">
-      <c r="I27" s="1">
+    <row r="27" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I27" s="1" t="n">
         <v>22</v>
       </c>
       <c r="J27" s="6" t="s">
@@ -4251,12 +3478,9 @@
       <c r="K27" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="L27" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="28" ht="64.15">
-      <c r="I28" s="1">
+    </row>
+    <row r="28" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I28" s="1" t="n">
         <v>23</v>
       </c>
       <c r="J28" s="6" t="s">
@@ -4265,21 +3489,18 @@
       <c r="K28" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="L28" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="29" ht="12.8">
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="31" ht="12.8">
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="32" ht="12.8">
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E32" s="1" t="s">
         <v>46</v>
       </c>
@@ -4287,7 +3508,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" ht="12.8">
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E33" s="1" t="s">
         <v>48</v>
       </c>
@@ -4295,8 +3516,8 @@
         <v>49</v>
       </c>
     </row>
-    <row r="34" ht="13.8">
-      <c r="I34" s="1">
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I34" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J34" s="7" t="s">
@@ -4305,15 +3526,12 @@
       <c r="K34" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="L34" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="35" ht="13.8">
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G35" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I35" s="1">
+      <c r="I35" s="1" t="n">
         <v>11</v>
       </c>
       <c r="J35" s="7" t="s">
@@ -4322,12 +3540,9 @@
       <c r="K35" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="L35" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="36" ht="23.85">
-      <c r="I36" s="1">
+    </row>
+    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I36" s="1" t="n">
         <v>12</v>
       </c>
       <c r="J36" s="7" t="s">
@@ -4336,15 +3551,12 @@
       <c r="K36" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="L36" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="37" ht="13.8">
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G37" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I37" s="1">
+      <c r="I37" s="1" t="n">
         <v>13</v>
       </c>
       <c r="J37" s="7" t="s">
@@ -4353,12 +3565,9 @@
       <c r="K37" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L37" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="38" ht="13.8">
-      <c r="I38" s="1">
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I38" s="1" t="n">
         <v>14</v>
       </c>
       <c r="J38" s="7" t="s">
@@ -4367,15 +3576,12 @@
       <c r="K38" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L38" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="39" ht="13.8">
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G39" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I39" s="1">
+      <c r="I39" s="1" t="n">
         <v>15</v>
       </c>
       <c r="J39" s="7" t="s">
@@ -4384,22 +3590,19 @@
       <c r="K39" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L39" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" ht="13.8">
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E40" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40" s="1" t="n">
         <v>58</v>
       </c>
       <c r="J40" s="7"/>
       <c r="K40" s="4"/>
     </row>
-    <row r="41" ht="79.85">
-      <c r="I41" s="1">
+    <row r="41" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I41" s="1" t="n">
         <v>16</v>
       </c>
       <c r="J41" s="7" t="s">
@@ -4408,12 +3611,9 @@
       <c r="K41" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="L41" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="42" ht="91">
-      <c r="I42" s="1">
+    </row>
+    <row r="42" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I42" s="1" t="n">
         <v>17</v>
       </c>
       <c r="J42" s="7" t="s">
@@ -4422,15 +3622,12 @@
       <c r="K42" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="L42" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="43" ht="23.85">
+    </row>
+    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G43" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I43" s="1">
+      <c r="I43" s="1" t="n">
         <v>18</v>
       </c>
       <c r="J43" s="7" t="s">
@@ -4439,12 +3636,9 @@
       <c r="K43" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="L43" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="44" ht="57.45">
-      <c r="I44" s="1">
+    </row>
+    <row r="44" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I44" s="1" t="n">
         <v>19</v>
       </c>
       <c r="J44" s="7" t="s">
@@ -4453,12 +3647,9 @@
       <c r="K44" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="L44" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="45" ht="102.2">
-      <c r="I45" s="1">
+    </row>
+    <row r="45" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I45" s="1" t="n">
         <v>88</v>
       </c>
       <c r="J45" s="7" t="s">
@@ -4467,16 +3658,13 @@
       <c r="K45" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="L45" t="s">
-        <v>542</v>
-      </c>
       <c r="M45" s="1"/>
     </row>
-    <row r="46" ht="13.8">
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G46" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I46" s="1">
+      <c r="I46" s="1" t="n">
         <v>20</v>
       </c>
       <c r="J46" s="7" t="s">
@@ -4485,26 +3673,23 @@
       <c r="K46" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="L46" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="47" ht="12.8">
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E47" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="48" ht="12.8">
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E48" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="50" ht="12.8">
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="51" ht="12.8">
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E51" s="1" t="s">
         <v>46</v>
       </c>
@@ -4512,7 +3697,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="52" ht="12.8">
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E52" s="1" t="s">
         <v>48</v>
       </c>
@@ -4520,7 +3705,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="53" s="1" customFormat="1" ht="12.8">
+    <row r="53" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -4537,7 +3722,7 @@
       <c r="K53" s="6"/>
       <c r="L53" s="6"/>
     </row>
-    <row r="54" s="1" customFormat="1" ht="12.8">
+    <row r="54" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -4545,7 +3730,7 @@
       <c r="E54" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F54" s="6">
+      <c r="F54" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G54" s="6"/>
@@ -4554,7 +3739,7 @@
       <c r="K54" s="6"/>
       <c r="L54" s="6"/>
     </row>
-    <row r="55" s="1" customFormat="1" ht="12.8">
+    <row r="55" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -4571,7 +3756,7 @@
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>
     </row>
-    <row r="56" s="1" customFormat="1" ht="12.8">
+    <row r="56" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -4588,7 +3773,7 @@
       <c r="K56" s="6"/>
       <c r="L56" s="6"/>
     </row>
-    <row r="57" s="1" customFormat="1" ht="12.8">
+    <row r="57" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -4596,7 +3781,7 @@
       <c r="E57" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F57" s="6">
+      <c r="F57" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G57" s="6"/>
@@ -4605,8 +3790,8 @@
       <c r="K57" s="6"/>
       <c r="L57" s="6"/>
     </row>
-    <row r="59" ht="23.85">
-      <c r="I59" s="1">
+    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I59" s="1" t="n">
         <v>24</v>
       </c>
       <c r="J59" s="7" t="s">
@@ -4615,15 +3800,12 @@
       <c r="K59" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="L59" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="60" ht="13.8">
+    </row>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G60" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I60" s="1">
+      <c r="I60" s="1" t="n">
         <v>25</v>
       </c>
       <c r="J60" s="7" t="s">
@@ -4632,15 +3814,12 @@
       <c r="K60" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="L60" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="61" ht="46.25">
+    </row>
+    <row r="61" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G61" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I61" s="1">
+      <c r="I61" s="1" t="n">
         <v>26</v>
       </c>
       <c r="J61" s="7" t="s">
@@ -4649,12 +3828,9 @@
       <c r="K61" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="L61" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="62" ht="35.05">
-      <c r="I62" s="1">
+    </row>
+    <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I62" s="1" t="n">
         <v>27</v>
       </c>
       <c r="J62" s="7" t="s">
@@ -4663,12 +3839,9 @@
       <c r="K62" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="L62" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="63" ht="46.25">
-      <c r="I63" s="1">
+    </row>
+    <row r="63" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I63" s="1" t="n">
         <v>28</v>
       </c>
       <c r="J63" s="7" t="s">
@@ -4677,15 +3850,12 @@
       <c r="K63" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="L63" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="64" ht="13.8">
+    </row>
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G64" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I64" s="1">
+      <c r="I64" s="1" t="n">
         <v>29</v>
       </c>
       <c r="J64" s="7" t="s">
@@ -4694,21 +3864,18 @@
       <c r="K64" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="L64" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="65" ht="13.8">
+    </row>
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E65" s="6"/>
       <c r="F65" s="10"/>
       <c r="J65" s="7"/>
       <c r="K65" s="9"/>
     </row>
-    <row r="66" ht="57.45">
+    <row r="66" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G66" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I66" s="1">
+      <c r="I66" s="1" t="n">
         <v>30</v>
       </c>
       <c r="J66" s="7" t="s">
@@ -4717,14 +3884,11 @@
       <c r="K66" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="L66" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="67" ht="23.85">
+    </row>
+    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E67" s="6"/>
       <c r="F67" s="10"/>
-      <c r="I67" s="1">
+      <c r="I67" s="1" t="n">
         <v>31</v>
       </c>
       <c r="J67" s="7" t="s">
@@ -4733,11 +3897,8 @@
       <c r="K67" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="L67" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="68" ht="13.8">
+    </row>
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E68" s="6" t="s">
         <v>79</v>
       </c>
@@ -4747,15 +3908,15 @@
       <c r="J68" s="7"/>
       <c r="K68" s="9"/>
     </row>
-    <row r="69" ht="13.8">
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J69" s="7"/>
       <c r="K69" s="9"/>
     </row>
-    <row r="70" ht="13.8">
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G70" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I70" s="1">
+      <c r="I70" s="1" t="n">
         <v>32</v>
       </c>
       <c r="J70" s="7" t="s">
@@ -4764,21 +3925,18 @@
       <c r="K70" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="L70" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="71" ht="13.8">
+    </row>
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E71" s="6"/>
       <c r="F71" s="10"/>
       <c r="J71" s="7"/>
       <c r="K71" s="4"/>
     </row>
-    <row r="72" ht="13.8">
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G72" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I72" s="1">
+      <c r="I72" s="1" t="n">
         <v>33</v>
       </c>
       <c r="J72" s="7" t="s">
@@ -4787,11 +3945,8 @@
       <c r="K72" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="L72" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="73" ht="13.8">
+    </row>
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E73" s="6" t="s">
         <v>62</v>
       </c>
@@ -4801,13 +3956,13 @@
       <c r="J73" s="7"/>
       <c r="K73" s="4"/>
     </row>
-    <row r="74" ht="23.85">
+    <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E74" s="6"/>
       <c r="F74" s="10"/>
       <c r="G74" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I74" s="1">
+      <c r="I74" s="1" t="n">
         <v>34</v>
       </c>
       <c r="J74" s="7" t="s">
@@ -4816,19 +3971,16 @@
       <c r="K74" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="L74" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="75" ht="13.8">
+    </row>
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J75" s="7"/>
       <c r="K75" s="6"/>
     </row>
-    <row r="76" ht="35.05">
+    <row r="76" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G76" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I76" s="1">
+      <c r="I76" s="1" t="n">
         <v>35</v>
       </c>
       <c r="J76" s="7" t="s">
@@ -4837,12 +3989,9 @@
       <c r="K76" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="L76" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="77" ht="13.8">
-      <c r="I77" s="1">
+    </row>
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I77" s="1" t="n">
         <v>36</v>
       </c>
       <c r="J77" s="7" t="s">
@@ -4851,19 +4000,16 @@
       <c r="K77" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="L77" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="78" ht="13.8">
+    </row>
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J78" s="7"/>
       <c r="K78" s="6"/>
     </row>
-    <row r="79" ht="79.85">
+    <row r="79" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G79" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I79" s="1">
+      <c r="I79" s="1" t="n">
         <v>37</v>
       </c>
       <c r="J79" s="7" t="s">
@@ -4872,12 +4018,9 @@
       <c r="K79" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="L79" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="80" ht="13.8">
-      <c r="I80" s="1">
+    </row>
+    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I80" s="1" t="n">
         <v>87</v>
       </c>
       <c r="J80" s="7" t="s">
@@ -4886,15 +4029,12 @@
       <c r="K80" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="L80" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="81" ht="57.45">
+    </row>
+    <row r="81" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G81" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I81" s="1">
+      <c r="I81" s="1" t="n">
         <v>38</v>
       </c>
       <c r="J81" s="7" t="s">
@@ -4903,12 +4043,9 @@
       <c r="K81" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="L81" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="82" ht="13.8">
-      <c r="I82" s="1">
+    </row>
+    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I82" s="1" t="n">
         <v>39</v>
       </c>
       <c r="J82" s="7" t="s">
@@ -4917,15 +4054,12 @@
       <c r="K82" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="L82" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="83" ht="43.25">
+    </row>
+    <row r="83" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G83" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I83" s="1">
+      <c r="I83" s="1" t="n">
         <v>40</v>
       </c>
       <c r="J83" s="7" t="s">
@@ -4934,15 +4068,12 @@
       <c r="K83" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="L83" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="84" ht="46.25">
+    </row>
+    <row r="84" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G84" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I84" s="1">
+      <c r="I84" s="1" t="n">
         <v>41</v>
       </c>
       <c r="J84" s="7" t="s">
@@ -4951,36 +4082,33 @@
       <c r="K84" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="L84" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="85" ht="13.8">
+    </row>
+    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E85" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F85" s="10">
+      <c r="F85" s="10" t="n">
         <v>3</v>
       </c>
       <c r="J85" s="7"/>
       <c r="K85" s="6"/>
     </row>
-    <row r="86" ht="12.8">
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E86" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="87" ht="12.8">
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E87" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="90" ht="12.8">
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="91" ht="12.8">
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E91" s="1" t="s">
         <v>46</v>
       </c>
@@ -4988,7 +4116,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="92" ht="12.8">
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E92" s="1" t="s">
         <v>48</v>
       </c>
@@ -4996,7 +4124,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="93" ht="12.8">
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -5014,7 +4142,7 @@
       <c r="L93" s="6"/>
       <c r="M93" s="1"/>
     </row>
-    <row r="94" ht="12.8">
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -5022,7 +4150,7 @@
       <c r="E94" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F94" s="6">
+      <c r="F94" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G94" s="6"/>
@@ -5032,7 +4160,7 @@
       <c r="L94" s="6"/>
       <c r="M94" s="1"/>
     </row>
-    <row r="95" ht="12.8">
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -5050,7 +4178,7 @@
       <c r="L95" s="6"/>
       <c r="M95" s="1"/>
     </row>
-    <row r="96" ht="12.8">
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -5064,7 +4192,7 @@
       <c r="L96" s="6"/>
       <c r="M96" s="1"/>
     </row>
-    <row r="97" ht="12.8">
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -5072,7 +4200,7 @@
       <c r="E97" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F97" s="6">
+      <c r="F97" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G97" s="6"/>
@@ -5082,11 +4210,11 @@
       <c r="L97" s="6"/>
       <c r="M97" s="1"/>
     </row>
-    <row r="99" ht="13.8">
+    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G99" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I99" s="1">
+      <c r="I99" s="1" t="n">
         <v>50</v>
       </c>
       <c r="J99" s="12" t="s">
@@ -5095,15 +4223,12 @@
       <c r="K99" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="L99" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="100" ht="13.8">
+    </row>
+    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G100" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="I100" s="1">
+      <c r="I100" s="1" t="n">
         <v>51</v>
       </c>
       <c r="J100" s="12" t="s">
@@ -5112,15 +4237,12 @@
       <c r="K100" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="L100" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="101" ht="13.8">
+    </row>
+    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G101" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I101" s="1">
+      <c r="I101" s="1" t="n">
         <v>52</v>
       </c>
       <c r="J101" s="12" t="s">
@@ -5129,15 +4251,12 @@
       <c r="K101" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="L101" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="102" ht="61.15">
+    </row>
+    <row r="102" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G102" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I102" s="1">
+      <c r="I102" s="1" t="n">
         <v>53</v>
       </c>
       <c r="J102" s="12" t="s">
@@ -5146,21 +4265,18 @@
       <c r="K102" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="L102" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="103" ht="13.8">
+    </row>
+    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E103" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F103" s="6">
+      <c r="F103" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J103" s="7"/>
       <c r="K103" s="9"/>
     </row>
-    <row r="104" ht="13.8">
+    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E104" s="6" t="s">
         <v>62</v>
       </c>
@@ -5170,28 +4286,28 @@
       <c r="J104" s="7"/>
       <c r="K104" s="9"/>
     </row>
-    <row r="105" ht="13.8">
+    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E105" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F105" s="6">
+      <c r="F105" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G105" s="6"/>
       <c r="J105" s="7"/>
       <c r="K105" s="9"/>
     </row>
-    <row r="106" ht="13.8">
+    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E106" s="6"/>
       <c r="F106" s="10"/>
       <c r="J106" s="7"/>
       <c r="K106" s="9"/>
     </row>
-    <row r="107" ht="45.5">
+    <row r="107" customFormat="false" ht="45.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G107" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I107" s="1">
+      <c r="I107" s="1" t="n">
         <v>54</v>
       </c>
       <c r="J107" s="6" t="s">
@@ -5200,17 +4316,14 @@
       <c r="K107" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="L107" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="108" ht="37.3">
+    </row>
+    <row r="108" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E108" s="6"/>
       <c r="F108" s="10"/>
       <c r="G108" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I108" s="1">
+      <c r="I108" s="1" t="n">
         <v>55</v>
       </c>
       <c r="J108" s="12" t="s">
@@ -5219,23 +4332,20 @@
       <c r="K108" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="L108" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="109" ht="13.8">
+    </row>
+    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E109" s="6"/>
       <c r="F109" s="10"/>
       <c r="J109" s="12"/>
       <c r="K109" s="9"/>
     </row>
-    <row r="110" ht="13.8">
+    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E110" s="6"/>
       <c r="F110" s="10"/>
       <c r="G110" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I110" s="1">
+      <c r="I110" s="1" t="n">
         <v>56</v>
       </c>
       <c r="J110" s="12" t="s">
@@ -5244,17 +4354,14 @@
       <c r="K110" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="L110" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="111" ht="13.8">
+    </row>
+    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E111" s="6"/>
       <c r="F111" s="10"/>
       <c r="G111" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I111" s="1">
+      <c r="I111" s="1" t="n">
         <v>57</v>
       </c>
       <c r="J111" s="12" t="s">
@@ -5263,15 +4370,12 @@
       <c r="K111" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="L111" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="112" ht="49.25">
+    </row>
+    <row r="112" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G112" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I112" s="1">
+      <c r="I112" s="1" t="n">
         <v>58</v>
       </c>
       <c r="J112" s="12" t="s">
@@ -5280,15 +4384,12 @@
       <c r="K112" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="L112" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="113" ht="13.8">
+    </row>
+    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G113" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I113" s="1">
+      <c r="I113" s="1" t="n">
         <v>59</v>
       </c>
       <c r="J113" s="12" t="s">
@@ -5297,15 +4398,12 @@
       <c r="K113" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="L113" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="114" ht="35.05">
+    </row>
+    <row r="114" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G114" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I114" s="1">
+      <c r="I114" s="1" t="n">
         <v>60</v>
       </c>
       <c r="J114" s="5" t="s">
@@ -5314,15 +4412,12 @@
       <c r="K114" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="L114" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="115" ht="91">
+    </row>
+    <row r="115" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G115" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I115" s="1">
+      <c r="I115" s="1" t="n">
         <v>89</v>
       </c>
       <c r="J115" s="5" t="s">
@@ -5331,15 +4426,12 @@
       <c r="K115" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="L115" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="116" ht="13.8">
+    </row>
+    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G116" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I116" s="1">
+      <c r="I116" s="1" t="n">
         <v>61</v>
       </c>
       <c r="J116" s="12" t="s">
@@ -5348,15 +4440,12 @@
       <c r="K116" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="L116" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="117" ht="73.1">
+    </row>
+    <row r="117" customFormat="false" ht="73.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G117" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I117" s="1">
+      <c r="I117" s="1" t="n">
         <v>62</v>
       </c>
       <c r="J117" s="12" t="s">
@@ -5365,15 +4454,12 @@
       <c r="K117" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="L117" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="118" ht="13.8">
+    </row>
+    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G118" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I118" s="1">
+      <c r="I118" s="1" t="n">
         <v>63</v>
       </c>
       <c r="J118" s="7" t="s">
@@ -5382,23 +4468,20 @@
       <c r="K118" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="L118" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="119" ht="13.8">
+    </row>
+    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E119" s="6"/>
       <c r="F119" s="10"/>
       <c r="J119" s="7"/>
       <c r="K119" s="4"/>
     </row>
-    <row r="120" ht="37.3">
+    <row r="120" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E120" s="6"/>
       <c r="F120" s="10"/>
       <c r="G120" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I120" s="1">
+      <c r="I120" s="1" t="n">
         <v>64</v>
       </c>
       <c r="J120" s="12" t="s">
@@ -5407,15 +4490,12 @@
       <c r="K120" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="L120" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="121" ht="37.3">
+    </row>
+    <row r="121" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G121" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I121" s="1">
+      <c r="I121" s="1" t="n">
         <v>65</v>
       </c>
       <c r="J121" s="12" t="s">
@@ -5424,15 +4504,12 @@
       <c r="K121" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="L121" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="122" ht="57.45">
+    </row>
+    <row r="122" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G122" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I122" s="1">
+      <c r="I122" s="1" t="n">
         <v>66</v>
       </c>
       <c r="J122" s="7" t="s">
@@ -5441,15 +4518,12 @@
       <c r="K122" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="L122" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="123" ht="25.35">
+    </row>
+    <row r="123" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G123" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I123" s="1">
+      <c r="I123" s="1" t="n">
         <v>67</v>
       </c>
       <c r="J123" s="12" t="s">
@@ -5458,11 +4532,8 @@
       <c r="K123" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="L123" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="124" ht="13.8">
+    </row>
+    <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E124" s="6" t="s">
         <v>79</v>
       </c>
@@ -5472,11 +4543,11 @@
       <c r="J124" s="12"/>
       <c r="K124" s="6"/>
     </row>
-    <row r="125" ht="13.8">
+    <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G125" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I125" s="1">
+      <c r="I125" s="1" t="n">
         <v>68</v>
       </c>
       <c r="J125" s="12" t="s">
@@ -5485,25 +4556,22 @@
       <c r="K125" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="L125" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="126" ht="13.8">
+    </row>
+    <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E126" s="6"/>
       <c r="F126" s="10"/>
       <c r="G126" s="6"/>
       <c r="J126" s="12"/>
       <c r="K126" s="6"/>
     </row>
-    <row r="127" ht="13.8">
+    <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E127" s="6"/>
       <c r="F127" s="10"/>
       <c r="G127" s="6"/>
       <c r="J127" s="12"/>
       <c r="K127" s="6"/>
     </row>
-    <row r="128" ht="13.8">
+    <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E128" s="6" t="s">
         <v>62</v>
       </c>
@@ -5513,11 +4581,11 @@
       <c r="J128" s="12"/>
       <c r="K128" s="6"/>
     </row>
-    <row r="129" ht="25.35">
+    <row r="129" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G129" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I129" s="1">
+      <c r="I129" s="1" t="n">
         <v>69</v>
       </c>
       <c r="J129" s="12" t="s">
@@ -5526,15 +4594,12 @@
       <c r="K129" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="L129" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="130" ht="13.8">
+    </row>
+    <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G130" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="I130" s="1">
+      <c r="I130" s="1" t="n">
         <v>70</v>
       </c>
       <c r="J130" s="12" t="s">
@@ -5543,15 +4608,12 @@
       <c r="K130" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="L130" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="131" ht="13.8">
+    </row>
+    <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G131" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I131" s="1">
+      <c r="I131" s="1" t="n">
         <v>71</v>
       </c>
       <c r="J131" s="12" t="s">
@@ -5560,15 +4622,12 @@
       <c r="K131" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="L131" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="132" ht="61.15">
+    </row>
+    <row r="132" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G132" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I132" s="1">
+      <c r="I132" s="1" t="n">
         <v>72</v>
       </c>
       <c r="J132" s="12" t="s">
@@ -5577,15 +4636,12 @@
       <c r="K132" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="L132" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="133" ht="13.8">
+    </row>
+    <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G133" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I133" s="1">
+      <c r="I133" s="1" t="n">
         <v>73</v>
       </c>
       <c r="J133" s="12" t="s">
@@ -5594,15 +4650,12 @@
       <c r="K133" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="L133" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="134" ht="37.3">
+    </row>
+    <row r="134" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G134" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I134" s="1">
+      <c r="I134" s="1" t="n">
         <v>74</v>
       </c>
       <c r="J134" s="12" t="s">
@@ -5611,15 +4664,12 @@
       <c r="K134" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="L134" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="135" ht="85.05">
+    </row>
+    <row r="135" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G135" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I135" s="1">
+      <c r="I135" s="1" t="n">
         <v>75</v>
       </c>
       <c r="J135" s="12" t="s">
@@ -5628,15 +4678,12 @@
       <c r="K135" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="L135" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="136" s="1" customFormat="1" ht="13.8">
+    </row>
+    <row r="136" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G136" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="I136" s="1">
+      <c r="I136" s="1" t="n">
         <v>76</v>
       </c>
       <c r="J136" s="12" t="s">
@@ -5645,15 +4692,12 @@
       <c r="K136" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="L136" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="137" ht="53.7">
+    </row>
+    <row r="137" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G137" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I137" s="1">
+      <c r="I137" s="1" t="n">
         <v>77</v>
       </c>
       <c r="J137" s="5" t="s">
@@ -5662,15 +4706,12 @@
       <c r="K137" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="L137" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="138" ht="13.8">
+    </row>
+    <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G138" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I138" s="1">
+      <c r="I138" s="1" t="n">
         <v>78</v>
       </c>
       <c r="J138" s="12" t="s">
@@ -5679,15 +4720,12 @@
       <c r="K138" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="L138" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="139" ht="13.8">
+    </row>
+    <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G139" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I139" s="1">
+      <c r="I139" s="1" t="n">
         <v>79</v>
       </c>
       <c r="J139" s="12" t="s">
@@ -5696,15 +4734,12 @@
       <c r="K139" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="L139" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="140" ht="68.65">
+    </row>
+    <row r="140" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G140" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I140" s="1">
+      <c r="I140" s="1" t="n">
         <v>80</v>
       </c>
       <c r="J140" s="7" t="s">
@@ -5713,12 +4748,9 @@
       <c r="K140" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="L140" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="141" ht="13.8">
-      <c r="I141" s="1">
+    </row>
+    <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I141" s="1" t="n">
         <v>81</v>
       </c>
       <c r="J141" s="12" t="s">
@@ -5727,15 +4759,12 @@
       <c r="K141" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="L141" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="142" s="1" customFormat="1" ht="13.8">
+    </row>
+    <row r="142" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G142" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I142" s="1">
+      <c r="I142" s="1" t="n">
         <v>82</v>
       </c>
       <c r="J142" s="12" t="s">
@@ -5744,15 +4773,12 @@
       <c r="K142" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L142" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="143" s="1" customFormat="1" ht="13.8">
+    </row>
+    <row r="143" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G143" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I143" s="1">
+      <c r="I143" s="1" t="n">
         <v>83</v>
       </c>
       <c r="J143" s="12" t="s">
@@ -5761,15 +4787,12 @@
       <c r="K143" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="L143" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="144" ht="61.15">
+    </row>
+    <row r="144" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G144" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I144" s="1">
+      <c r="I144" s="1" t="n">
         <v>84</v>
       </c>
       <c r="J144" s="12" t="s">
@@ -5778,15 +4801,12 @@
       <c r="K144" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="L144" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="145" ht="58.2">
+    </row>
+    <row r="145" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G145" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I145" s="1">
+      <c r="I145" s="1" t="n">
         <v>85</v>
       </c>
       <c r="J145" s="12" t="s">
@@ -5795,15 +4815,12 @@
       <c r="K145" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="L145" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="146" ht="49.25">
+    </row>
+    <row r="146" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G146" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I146" s="1">
+      <c r="I146" s="1" t="n">
         <v>86</v>
       </c>
       <c r="J146" s="12" t="s">
@@ -5812,31 +4829,28 @@
       <c r="K146" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="L146" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="147" ht="13.8">
+    </row>
+    <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J147" s="12"/>
       <c r="K147" s="6"/>
     </row>
-    <row r="148" ht="13.8">
+    <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E148" s="6"/>
       <c r="F148" s="10"/>
       <c r="J148" s="7"/>
       <c r="K148" s="6"/>
     </row>
-    <row r="150" ht="12.8">
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E150" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="154" ht="12.8">
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="155" ht="12.8">
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E155" s="1" t="s">
         <v>81</v>
       </c>
@@ -5846,7 +4860,7 @@
       <c r="J155" s="14"/>
       <c r="K155" s="14"/>
     </row>
-    <row r="156" ht="12.8">
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E156" s="1" t="s">
         <v>82</v>
       </c>
@@ -5856,11 +4870,11 @@
       <c r="J156" s="14"/>
       <c r="K156" s="14"/>
     </row>
-    <row r="157" ht="12.8">
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E157" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F157" s="1">
+      <c r="F157" s="1" t="n">
         <v>13</v>
       </c>
       <c r="J157" s="14"/>
@@ -6112,7 +5126,7 @@
       <c r="IW157" s="1"/>
       <c r="IX157" s="1"/>
     </row>
-    <row r="158" ht="12.8">
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E158" s="1" t="s">
         <v>85</v>
       </c>
@@ -6122,11 +5136,11 @@
       <c r="J158" s="14"/>
       <c r="K158" s="14"/>
     </row>
-    <row r="159" ht="12.8">
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G159" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I159" s="1">
+      <c r="I159" s="1" t="n">
         <v>90</v>
       </c>
       <c r="J159" s="14" t="s">
@@ -6134,9 +5148,6 @@
       </c>
       <c r="K159" s="14" t="s">
         <v>203</v>
-      </c>
-      <c r="L159" t="s">
-        <v>202</v>
       </c>
       <c r="M159" s="1"/>
       <c r="N159" s="1"/>
@@ -6385,14 +5396,14 @@
       <c r="IW159" s="1"/>
       <c r="IX159" s="1"/>
     </row>
-    <row r="160" ht="12.8">
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="M160" s="1"/>
     </row>
-    <row r="161" ht="23.85">
+    <row r="161" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G161" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I161" s="1">
+      <c r="I161" s="1" t="n">
         <v>91</v>
       </c>
       <c r="J161" s="7" t="s">
@@ -6401,15 +5412,12 @@
       <c r="K161" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="L161" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="162" ht="13.8">
+    </row>
+    <row r="162" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G162" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I162" s="1">
+      <c r="I162" s="1" t="n">
         <v>92</v>
       </c>
       <c r="J162" s="7" t="s">
@@ -6418,15 +5426,12 @@
       <c r="K162" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="L162" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="163" ht="13.8">
+    </row>
+    <row r="163" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G163" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="I163" s="1">
+      <c r="I163" s="1" t="n">
         <v>93</v>
       </c>
       <c r="J163" s="12" t="s">
@@ -6435,15 +5440,12 @@
       <c r="K163" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="L163" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="164" ht="13.8">
+    </row>
+    <row r="164" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G164" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I164" s="1">
+      <c r="I164" s="1" t="n">
         <v>94</v>
       </c>
       <c r="J164" s="12" t="s">
@@ -6452,15 +5454,12 @@
       <c r="K164" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="L164" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="165" ht="13.8">
+    </row>
+    <row r="165" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G165" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="I165" s="1">
+      <c r="I165" s="1" t="n">
         <v>95</v>
       </c>
       <c r="J165" s="12" t="s">
@@ -6469,15 +5468,12 @@
       <c r="K165" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="L165" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="166" ht="13.8">
+    </row>
+    <row r="166" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G166" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I166" s="1">
+      <c r="I166" s="1" t="n">
         <v>96</v>
       </c>
       <c r="J166" s="7" t="s">
@@ -6486,15 +5482,12 @@
       <c r="K166" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="L166" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="167" ht="13.8">
+    </row>
+    <row r="167" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G167" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="I167" s="1">
+      <c r="I167" s="1" t="n">
         <v>97</v>
       </c>
       <c r="J167" s="12" t="s">
@@ -6503,15 +5496,12 @@
       <c r="K167" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="L167" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="168" ht="13.8">
+    </row>
+    <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G168" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I168" s="1">
+      <c r="I168" s="1" t="n">
         <v>98</v>
       </c>
       <c r="J168" s="7" t="s">
@@ -6520,15 +5510,12 @@
       <c r="K168" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="L168" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="169" ht="13.8">
+    </row>
+    <row r="169" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G169" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="I169" s="1">
+      <c r="I169" s="1" t="n">
         <v>99</v>
       </c>
       <c r="J169" s="12" t="s">
@@ -6537,44 +5524,41 @@
       <c r="K169" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="L169" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="170" ht="13.8">
+    </row>
+    <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E170" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F170" s="6">
+      <c r="F170" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J170" s="7"/>
       <c r="K170" s="9"/>
     </row>
-    <row r="171" ht="13.8">
+    <row r="171" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E171" s="6"/>
       <c r="F171" s="10"/>
       <c r="J171" s="7"/>
       <c r="K171" s="9"/>
     </row>
-    <row r="172" ht="13.8">
+    <row r="172" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E172" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F172" s="6">
+      <c r="F172" s="6" t="n">
         <v>3</v>
       </c>
       <c r="G172" s="6"/>
       <c r="J172" s="7"/>
       <c r="K172" s="9"/>
     </row>
-    <row r="173" ht="13.8">
+    <row r="173" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E173" s="6"/>
       <c r="F173" s="6"/>
       <c r="G173" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="I173" s="1">
+      <c r="I173" s="1" t="n">
         <v>100</v>
       </c>
       <c r="J173" s="7" t="s">
@@ -6583,17 +5567,14 @@
       <c r="K173" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="L173" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="174" ht="13.8">
+    </row>
+    <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E174" s="6"/>
       <c r="F174" s="6"/>
       <c r="G174" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="I174" s="1">
+      <c r="I174" s="1" t="n">
         <v>101</v>
       </c>
       <c r="J174" s="7" t="s">
@@ -6602,17 +5583,14 @@
       <c r="K174" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="L174" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="175" ht="13.8">
+    </row>
+    <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E175" s="6"/>
       <c r="F175" s="6"/>
       <c r="G175" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="I175" s="1">
+      <c r="I175" s="1" t="n">
         <v>102</v>
       </c>
       <c r="J175" s="7" t="s">
@@ -6621,17 +5599,14 @@
       <c r="K175" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="L175" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="176" ht="13.8">
+    </row>
+    <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E176" s="6"/>
       <c r="F176" s="6"/>
       <c r="G176" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I176" s="1">
+      <c r="I176" s="1" t="n">
         <v>103</v>
       </c>
       <c r="J176" s="7" t="s">
@@ -6640,17 +5615,14 @@
       <c r="K176" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="L176" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="177" ht="79.85">
+    </row>
+    <row r="177" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E177" s="6"/>
       <c r="F177" s="6"/>
       <c r="G177" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I177" s="1">
+      <c r="I177" s="1" t="n">
         <v>104</v>
       </c>
       <c r="J177" s="7" t="s">
@@ -6659,17 +5631,14 @@
       <c r="K177" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="L177" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="178" ht="23.85">
+    </row>
+    <row r="178" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E178" s="6"/>
       <c r="F178" s="6"/>
       <c r="G178" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I178" s="1">
+      <c r="I178" s="1" t="n">
         <v>105</v>
       </c>
       <c r="J178" s="7" t="s">
@@ -6678,17 +5647,14 @@
       <c r="K178" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="L178" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="179" ht="68.65">
+    </row>
+    <row r="179" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E179" s="6"/>
       <c r="F179" s="6"/>
       <c r="G179" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I179" s="1">
+      <c r="I179" s="1" t="n">
         <v>106</v>
       </c>
       <c r="J179" s="7" t="s">
@@ -6697,17 +5663,14 @@
       <c r="K179" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="L179" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="180" ht="79.85">
+    </row>
+    <row r="180" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E180" s="6"/>
       <c r="F180" s="6"/>
       <c r="G180" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I180" s="1">
+      <c r="I180" s="1" t="n">
         <v>107</v>
       </c>
       <c r="J180" s="7" t="s">
@@ -6716,17 +5679,14 @@
       <c r="K180" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="L180" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="181" ht="79.85">
+    </row>
+    <row r="181" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E181" s="6"/>
       <c r="F181" s="6"/>
       <c r="G181" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I181" s="1">
+      <c r="I181" s="1" t="n">
         <v>108</v>
       </c>
       <c r="J181" s="7" t="s">
@@ -6735,17 +5695,14 @@
       <c r="K181" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="L181" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="182" ht="35.05">
+    </row>
+    <row r="182" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E182" s="6"/>
       <c r="F182" s="6"/>
       <c r="G182" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I182" s="1">
+      <c r="I182" s="1" t="n">
         <v>109</v>
       </c>
       <c r="J182" s="7" t="s">
@@ -6754,17 +5711,14 @@
       <c r="K182" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="L182" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="183" ht="35.05">
+    </row>
+    <row r="183" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E183" s="6"/>
       <c r="F183" s="6"/>
       <c r="G183" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I183" s="1">
+      <c r="I183" s="1" t="n">
         <v>110</v>
       </c>
       <c r="J183" s="7" t="s">
@@ -6773,17 +5727,14 @@
       <c r="K183" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="L183" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="184" ht="102.2">
+    </row>
+    <row r="184" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E184" s="6"/>
       <c r="F184" s="6"/>
       <c r="G184" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I184" s="1">
+      <c r="I184" s="1" t="n">
         <v>111</v>
       </c>
       <c r="J184" s="7" t="s">
@@ -6792,40 +5743,37 @@
       <c r="K184" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="L184" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="185" ht="13.8">
+    </row>
+    <row r="185" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E185" s="6"/>
       <c r="F185" s="6"/>
       <c r="G185" s="6"/>
       <c r="J185" s="7"/>
       <c r="K185" s="9"/>
     </row>
-    <row r="186" ht="13.8">
+    <row r="186" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E186" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F186" s="6">
+      <c r="F186" s="6" t="n">
         <v>3</v>
       </c>
       <c r="G186" s="6"/>
       <c r="J186" s="12"/>
       <c r="K186" s="9"/>
     </row>
-    <row r="187" ht="13.8">
+    <row r="187" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E187" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F187" s="1">
+      <c r="F187" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="G187" s="6"/>
       <c r="J187" s="12"/>
       <c r="K187" s="9"/>
     </row>
-    <row r="188" ht="13.8">
+    <row r="188" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E188" s="1" t="s">
         <v>76</v>
       </c>
@@ -6833,12 +5781,12 @@
       <c r="J188" s="12"/>
       <c r="K188" s="9"/>
     </row>
-    <row r="191" ht="12.8">
+    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="192" ht="12.8">
+    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E192" s="1" t="s">
         <v>81</v>
       </c>
@@ -6848,7 +5796,7 @@
       <c r="J192" s="14"/>
       <c r="K192" s="14"/>
     </row>
-    <row r="193" ht="12.8">
+    <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E193" s="1" t="s">
         <v>82</v>
       </c>
@@ -6858,11 +5806,11 @@
       <c r="J193" s="14"/>
       <c r="K193" s="14"/>
     </row>
-    <row r="194" ht="12.8">
+    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E194" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F194" s="1">
+      <c r="F194" s="1" t="n">
         <v>13</v>
       </c>
       <c r="J194" s="14"/>
@@ -7114,7 +6062,7 @@
       <c r="IW194" s="1"/>
       <c r="IX194" s="1"/>
     </row>
-    <row r="195" ht="12.8">
+    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E195" s="1" t="s">
         <v>85</v>
       </c>
@@ -7124,11 +6072,11 @@
       <c r="J195" s="14"/>
       <c r="K195" s="14"/>
     </row>
-    <row r="196" ht="12.8">
+    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G196" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I196" s="1">
+      <c r="I196" s="1" t="n">
         <v>112</v>
       </c>
       <c r="J196" s="14" t="s">
@@ -7136,9 +6084,6 @@
       </c>
       <c r="K196" s="14" t="s">
         <v>203</v>
-      </c>
-      <c r="L196" t="s">
-        <v>202</v>
       </c>
       <c r="M196" s="1"/>
       <c r="N196" s="1"/>
@@ -7387,14 +6332,14 @@
       <c r="IW196" s="1"/>
       <c r="IX196" s="1"/>
     </row>
-    <row r="197" ht="12.8">
+    <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="M197" s="1"/>
     </row>
-    <row r="198" ht="68.65">
+    <row r="198" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G198" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I198" s="1">
+      <c r="I198" s="1" t="n">
         <v>113</v>
       </c>
       <c r="J198" s="7" t="s">
@@ -7403,15 +6348,12 @@
       <c r="K198" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="L198" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="199" ht="57.45">
+    </row>
+    <row r="199" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G199" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I199" s="1">
+      <c r="I199" s="1" t="n">
         <v>114</v>
       </c>
       <c r="J199" s="7" t="s">
@@ -7420,15 +6362,12 @@
       <c r="K199" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="L199" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="200" ht="79.85">
+    </row>
+    <row r="200" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G200" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I200" s="1">
+      <c r="I200" s="1" t="n">
         <v>115</v>
       </c>
       <c r="J200" s="7" t="s">
@@ -7437,15 +6376,12 @@
       <c r="K200" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="L200" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="201" ht="46.25">
+    </row>
+    <row r="201" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G201" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I201" s="1">
+      <c r="I201" s="1" t="n">
         <v>116</v>
       </c>
       <c r="J201" s="7" t="s">
@@ -7454,15 +6390,12 @@
       <c r="K201" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="L201" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="202" ht="35.05">
+    </row>
+    <row r="202" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G202" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I202" s="1">
+      <c r="I202" s="1" t="n">
         <v>117</v>
       </c>
       <c r="J202" s="7" t="s">
@@ -7471,15 +6404,12 @@
       <c r="K202" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="L202" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="203" ht="68.65">
+    </row>
+    <row r="203" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G203" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I203" s="1">
+      <c r="I203" s="1" t="n">
         <v>118</v>
       </c>
       <c r="J203" s="7" t="s">
@@ -7488,15 +6418,12 @@
       <c r="K203" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="L203" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="204" ht="68.65">
+    </row>
+    <row r="204" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G204" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I204" s="1">
+      <c r="I204" s="1" t="n">
         <v>119</v>
       </c>
       <c r="J204" s="7" t="s">
@@ -7505,15 +6432,12 @@
       <c r="K204" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="L204" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="205" ht="67.9">
+    </row>
+    <row r="205" customFormat="false" ht="67.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G205" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I205" s="1">
+      <c r="I205" s="1" t="n">
         <v>120</v>
       </c>
       <c r="J205" s="7" t="s">
@@ -7522,15 +6446,12 @@
       <c r="K205" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="L205" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="206" ht="13.8">
+    </row>
+    <row r="206" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G206" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I206" s="1">
+      <c r="I206" s="1" t="n">
         <v>121</v>
       </c>
       <c r="J206" s="7" t="s">
@@ -7539,15 +6460,12 @@
       <c r="K206" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="L206" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="207" ht="13.8">
+    </row>
+    <row r="207" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G207" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I207" s="1">
+      <c r="I207" s="1" t="n">
         <v>122</v>
       </c>
       <c r="J207" s="7" t="s">
@@ -7556,15 +6474,12 @@
       <c r="K207" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="L207" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="208" ht="23.85">
+    </row>
+    <row r="208" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G208" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I208" s="1">
+      <c r="I208" s="1" t="n">
         <v>123</v>
       </c>
       <c r="J208" s="7" t="s">
@@ -7573,15 +6488,12 @@
       <c r="K208" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="L208" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="209" ht="23.85">
+    </row>
+    <row r="209" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G209" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I209" s="1">
+      <c r="I209" s="1" t="n">
         <v>124</v>
       </c>
       <c r="J209" s="7" t="s">
@@ -7590,15 +6502,12 @@
       <c r="K209" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="L209" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="210" ht="35.05">
+    </row>
+    <row r="210" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G210" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I210" s="1">
+      <c r="I210" s="1" t="n">
         <v>125</v>
       </c>
       <c r="J210" s="7" t="s">
@@ -7607,15 +6516,12 @@
       <c r="K210" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="L210" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="211" ht="102.2">
+    </row>
+    <row r="211" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G211" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I211" s="1">
+      <c r="I211" s="1" t="n">
         <v>126</v>
       </c>
       <c r="J211" s="7" t="s">
@@ -7624,15 +6530,12 @@
       <c r="K211" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="L211" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="212" ht="23.85">
+    </row>
+    <row r="212" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G212" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I212" s="1">
+      <c r="I212" s="1" t="n">
         <v>127</v>
       </c>
       <c r="J212" s="7" t="s">
@@ -7641,15 +6544,12 @@
       <c r="K212" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="L212" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="213" ht="23.85">
+    </row>
+    <row r="213" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G213" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I213" s="1">
+      <c r="I213" s="1" t="n">
         <v>128</v>
       </c>
       <c r="J213" s="7" t="s">
@@ -7658,15 +6558,12 @@
       <c r="K213" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="L213" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="214" ht="13.8">
+    </row>
+    <row r="214" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G214" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I214" s="1">
+      <c r="I214" s="1" t="n">
         <v>129</v>
       </c>
       <c r="J214" s="7" t="s">
@@ -7675,15 +6572,12 @@
       <c r="K214" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="L214" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="215" ht="13.8">
+    </row>
+    <row r="215" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G215" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I215" s="1">
+      <c r="I215" s="1" t="n">
         <v>130</v>
       </c>
       <c r="J215" s="15" t="s">
@@ -7692,15 +6586,12 @@
       <c r="K215" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="L215" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="216" ht="13.8">
+    </row>
+    <row r="216" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G216" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I216" s="1">
+      <c r="I216" s="1" t="n">
         <v>131</v>
       </c>
       <c r="J216" s="7" t="s">
@@ -7709,15 +6600,12 @@
       <c r="K216" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="L216" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="217" ht="46.25">
+    </row>
+    <row r="217" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G217" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I217" s="1">
+      <c r="I217" s="1" t="n">
         <v>132</v>
       </c>
       <c r="J217" s="7" t="s">
@@ -7726,53 +6614,50 @@
       <c r="K217" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="L217" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="218" ht="13.8">
+    </row>
+    <row r="218" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G218" s="6"/>
       <c r="J218" s="7"/>
       <c r="K218" s="9"/>
     </row>
-    <row r="219" ht="13.8">
+    <row r="219" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E219" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F219" s="6">
+      <c r="F219" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J219" s="7"/>
       <c r="K219" s="9"/>
     </row>
-    <row r="220" ht="13.8">
+    <row r="220" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E220" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F220" s="1">
+      <c r="F220" s="1" t="n">
         <v>35</v>
       </c>
       <c r="J220" s="7"/>
       <c r="K220" s="9"/>
     </row>
-    <row r="221" ht="13.8">
+    <row r="221" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E221" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F221" s="6">
+      <c r="F221" s="6" t="n">
         <v>3</v>
       </c>
       <c r="G221" s="6"/>
       <c r="J221" s="7"/>
       <c r="K221" s="9"/>
     </row>
-    <row r="222" ht="13.8">
+    <row r="222" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E222" s="6"/>
       <c r="F222" s="6"/>
       <c r="G222" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I222" s="1">
+      <c r="I222" s="1" t="n">
         <v>133</v>
       </c>
       <c r="J222" s="7" t="s">
@@ -7781,17 +6666,14 @@
       <c r="K222" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="L222" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="223" ht="57.45">
+    </row>
+    <row r="223" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E223" s="6"/>
       <c r="F223" s="6"/>
       <c r="G223" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="I223" s="1">
+      <c r="I223" s="1" t="n">
         <v>134</v>
       </c>
       <c r="J223" s="7" t="s">
@@ -7800,17 +6682,14 @@
       <c r="K223" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="L223" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="224" ht="13.8">
+    </row>
+    <row r="224" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E224" s="6"/>
       <c r="F224" s="6"/>
       <c r="G224" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I224" s="1">
+      <c r="I224" s="1" t="n">
         <v>135</v>
       </c>
       <c r="J224" s="7" t="s">
@@ -7819,17 +6698,14 @@
       <c r="K224" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="L224" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="225" ht="13.8">
+    </row>
+    <row r="225" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E225" s="6"/>
       <c r="F225" s="6"/>
       <c r="G225" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I225" s="1">
+      <c r="I225" s="1" t="n">
         <v>136</v>
       </c>
       <c r="J225" s="7" t="s">
@@ -7838,17 +6714,14 @@
       <c r="K225" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="L225" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="226" ht="13.8">
+    </row>
+    <row r="226" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E226" s="6"/>
       <c r="F226" s="6"/>
       <c r="G226" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I226" s="1">
+      <c r="I226" s="1" t="n">
         <v>137</v>
       </c>
       <c r="J226" s="15" t="s">
@@ -7857,17 +6730,14 @@
       <c r="K226" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="L226" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="227" ht="102.2">
+    </row>
+    <row r="227" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E227" s="6"/>
       <c r="F227" s="6"/>
       <c r="G227" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I227" s="1">
+      <c r="I227" s="1" t="n">
         <v>138</v>
       </c>
       <c r="J227" s="5" t="s">
@@ -7876,55 +6746,52 @@
       <c r="K227" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="L227" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="228" ht="13.8">
+    </row>
+    <row r="228" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E228" s="6"/>
       <c r="F228" s="6"/>
       <c r="G228" s="6"/>
       <c r="J228" s="7"/>
       <c r="K228" s="9"/>
     </row>
-    <row r="229" ht="13.8">
+    <row r="229" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E229" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F229" s="6">
+      <c r="F229" s="6" t="n">
         <v>3</v>
       </c>
       <c r="G229" s="6"/>
       <c r="J229" s="12"/>
       <c r="K229" s="9"/>
     </row>
-    <row r="230" ht="13.8">
+    <row r="230" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E230" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F230" s="1">
+      <c r="F230" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="G230" s="6"/>
       <c r="J230" s="12"/>
       <c r="K230" s="9"/>
     </row>
-    <row r="231" ht="13.8">
+    <row r="231" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G231" s="6"/>
       <c r="J231" s="12"/>
       <c r="K231" s="9"/>
     </row>
-    <row r="232" ht="12.8">
+    <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E232" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="234" ht="12.8">
+    <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="1" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="235" ht="12.8">
+    <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E235" s="1" t="s">
         <v>81</v>
       </c>
@@ -7934,7 +6801,7 @@
       <c r="J235" s="14"/>
       <c r="K235" s="14"/>
     </row>
-    <row r="236" ht="12.8">
+    <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E236" s="1" t="s">
         <v>82</v>
       </c>
@@ -7944,11 +6811,11 @@
       <c r="J236" s="14"/>
       <c r="K236" s="14"/>
     </row>
-    <row r="237" ht="12.8">
+    <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E237" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F237" s="1">
+      <c r="F237" s="1" t="n">
         <v>13</v>
       </c>
       <c r="J237" s="14"/>
@@ -8200,7 +7067,7 @@
       <c r="IW237" s="1"/>
       <c r="IX237" s="1"/>
     </row>
-    <row r="238" ht="12.8">
+    <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E238" s="1" t="s">
         <v>85</v>
       </c>
@@ -8210,11 +7077,11 @@
       <c r="J238" s="14"/>
       <c r="K238" s="14"/>
     </row>
-    <row r="239" ht="12.8">
+    <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G239" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I239" s="1">
+      <c r="I239" s="1" t="n">
         <v>139</v>
       </c>
       <c r="J239" s="14" t="s">
@@ -8222,9 +7089,6 @@
       </c>
       <c r="K239" s="14" t="s">
         <v>203</v>
-      </c>
-      <c r="L239" t="s">
-        <v>202</v>
       </c>
       <c r="M239" s="1"/>
       <c r="N239" s="1"/>
@@ -8473,14 +7337,14 @@
       <c r="IW239" s="1"/>
       <c r="IX239" s="1"/>
     </row>
-    <row r="240" ht="12.8">
+    <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="M240" s="1"/>
     </row>
-    <row r="241" ht="79.85">
+    <row r="241" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G241" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I241" s="1">
+      <c r="I241" s="1" t="n">
         <v>140</v>
       </c>
       <c r="J241" s="7" t="s">
@@ -8489,15 +7353,12 @@
       <c r="K241" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="L241" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="242" ht="91">
+    </row>
+    <row r="242" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G242" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I242" s="1">
+      <c r="I242" s="1" t="n">
         <v>141</v>
       </c>
       <c r="J242" s="7" t="s">
@@ -8506,15 +7367,12 @@
       <c r="K242" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="L242" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="243" ht="68.65">
+    </row>
+    <row r="243" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G243" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I243" s="1">
+      <c r="I243" s="1" t="n">
         <v>142</v>
       </c>
       <c r="J243" s="7" t="s">
@@ -8523,15 +7381,12 @@
       <c r="K243" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="L243" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="244" ht="46.25">
+    </row>
+    <row r="244" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G244" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I244" s="1">
+      <c r="I244" s="1" t="n">
         <v>143</v>
       </c>
       <c r="J244" s="7" t="s">
@@ -8540,15 +7395,12 @@
       <c r="K244" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="L244" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="245" ht="113.4">
+    </row>
+    <row r="245" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G245" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I245" s="1">
+      <c r="I245" s="1" t="n">
         <v>144</v>
       </c>
       <c r="J245" s="7" t="s">
@@ -8557,15 +7409,12 @@
       <c r="K245" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="L245" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="246" ht="46.25">
+    </row>
+    <row r="246" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G246" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I246" s="1">
+      <c r="I246" s="1" t="n">
         <v>145</v>
       </c>
       <c r="J246" s="7" t="s">
@@ -8574,15 +7423,12 @@
       <c r="K246" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="L246" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="247" ht="68.65">
+    </row>
+    <row r="247" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G247" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I247" s="1">
+      <c r="I247" s="1" t="n">
         <v>146</v>
       </c>
       <c r="J247" s="7" t="s">
@@ -8591,15 +7437,12 @@
       <c r="K247" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="L247" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="248" ht="23.85">
+    </row>
+    <row r="248" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G248" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I248" s="1">
+      <c r="I248" s="1" t="n">
         <v>147</v>
       </c>
       <c r="J248" s="7" t="s">
@@ -8608,15 +7451,12 @@
       <c r="K248" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="L248" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="249" ht="13.8">
+    </row>
+    <row r="249" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G249" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I249" s="1">
+      <c r="I249" s="1" t="n">
         <v>148</v>
       </c>
       <c r="J249" s="7" t="s">
@@ -8625,15 +7465,12 @@
       <c r="K249" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="L249" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="250" ht="57.45">
+    </row>
+    <row r="250" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G250" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I250" s="1">
+      <c r="I250" s="1" t="n">
         <v>149</v>
       </c>
       <c r="J250" s="7" t="s">
@@ -8642,15 +7479,12 @@
       <c r="K250" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="L250" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="251" ht="57.45">
+    </row>
+    <row r="251" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G251" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I251" s="1">
+      <c r="I251" s="1" t="n">
         <v>150</v>
       </c>
       <c r="J251" s="7" t="s">
@@ -8659,15 +7493,12 @@
       <c r="K251" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="L251" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="252" ht="35.05">
+    </row>
+    <row r="252" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G252" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I252" s="1">
+      <c r="I252" s="1" t="n">
         <v>151</v>
       </c>
       <c r="J252" s="7" t="s">
@@ -8676,15 +7507,12 @@
       <c r="K252" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="L252" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="253" ht="13.8">
+    </row>
+    <row r="253" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G253" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I253" s="1">
+      <c r="I253" s="1" t="n">
         <v>152</v>
       </c>
       <c r="J253" s="7" t="s">
@@ -8693,15 +7521,12 @@
       <c r="K253" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="L253" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="254" ht="68.65">
+    </row>
+    <row r="254" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G254" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I254" s="1">
+      <c r="I254" s="1" t="n">
         <v>153</v>
       </c>
       <c r="J254" s="7" t="s">
@@ -8710,15 +7535,12 @@
       <c r="K254" s="9" t="s">
         <v>318</v>
       </c>
-      <c r="L254" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="255" ht="57.45">
+    </row>
+    <row r="255" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G255" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I255" s="1">
+      <c r="I255" s="1" t="n">
         <v>154</v>
       </c>
       <c r="J255" s="7" t="s">
@@ -8727,15 +7549,12 @@
       <c r="K255" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="L255" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="256" ht="13.8">
+    </row>
+    <row r="256" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G256" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I256" s="1">
+      <c r="I256" s="1" t="n">
         <v>155</v>
       </c>
       <c r="J256" s="7" t="s">
@@ -8744,15 +7563,12 @@
       <c r="K256" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="L256" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="257" ht="79.85">
+    </row>
+    <row r="257" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G257" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I257" s="1">
+      <c r="I257" s="1" t="n">
         <v>156</v>
       </c>
       <c r="J257" s="7" t="s">
@@ -8761,15 +7577,12 @@
       <c r="K257" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="L257" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="258" ht="13.8">
+    </row>
+    <row r="258" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G258" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I258" s="1">
+      <c r="I258" s="1" t="n">
         <v>157</v>
       </c>
       <c r="J258" s="7" t="s">
@@ -8778,15 +7591,12 @@
       <c r="K258" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="L258" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="259" ht="113.4">
+    </row>
+    <row r="259" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G259" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I259" s="1">
+      <c r="I259" s="1" t="n">
         <v>158</v>
       </c>
       <c r="J259" s="7" t="s">
@@ -8795,15 +7605,12 @@
       <c r="K259" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="L259" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="260" ht="13.8">
+    </row>
+    <row r="260" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G260" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I260" s="1">
+      <c r="I260" s="1" t="n">
         <v>159</v>
       </c>
       <c r="J260" s="7" t="s">
@@ -8812,15 +7619,12 @@
       <c r="K260" s="9" t="s">
         <v>330</v>
       </c>
-      <c r="L260" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="261" ht="13.8">
+    </row>
+    <row r="261" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G261" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I261" s="1">
+      <c r="I261" s="1" t="n">
         <v>160</v>
       </c>
       <c r="J261" s="7" t="s">
@@ -8829,15 +7633,12 @@
       <c r="K261" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="L261" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="262" ht="113.4">
+    </row>
+    <row r="262" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G262" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I262" s="1">
+      <c r="I262" s="1" t="n">
         <v>161</v>
       </c>
       <c r="J262" s="7" t="s">
@@ -8846,15 +7647,12 @@
       <c r="K262" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="L262" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="263" ht="102.2">
+    </row>
+    <row r="263" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G263" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I263" s="1">
+      <c r="I263" s="1" t="n">
         <v>162</v>
       </c>
       <c r="J263" s="7" t="s">
@@ -8863,15 +7661,12 @@
       <c r="K263" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="L263" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="264" ht="13.8">
+    </row>
+    <row r="264" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G264" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I264" s="1">
+      <c r="I264" s="1" t="n">
         <v>163</v>
       </c>
       <c r="J264" s="7" t="s">
@@ -8880,67 +7675,64 @@
       <c r="K264" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="L264" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="265" ht="13.8">
+    </row>
+    <row r="265" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G265" s="6"/>
       <c r="J265" s="7"/>
       <c r="K265" s="9"/>
     </row>
-    <row r="266" ht="13.8">
+    <row r="266" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G266" s="6"/>
       <c r="J266" s="7"/>
       <c r="K266" s="9"/>
     </row>
-    <row r="267" ht="13.8">
+    <row r="267" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G267" s="6"/>
       <c r="J267" s="7"/>
       <c r="K267" s="9"/>
     </row>
-    <row r="268" ht="13.8">
+    <row r="268" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E268" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F268" s="6">
+      <c r="F268" s="6" t="n">
         <v>3</v>
       </c>
       <c r="G268" s="6"/>
       <c r="J268" s="12"/>
       <c r="K268" s="9"/>
     </row>
-    <row r="269" ht="13.8">
+    <row r="269" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E269" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F269" s="1">
+      <c r="F269" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="G269" s="6"/>
       <c r="J269" s="12"/>
       <c r="K269" s="9"/>
     </row>
-    <row r="270" ht="13.8">
+    <row r="270" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G270" s="6"/>
       <c r="J270" s="12"/>
       <c r="K270" s="9"/>
     </row>
-    <row r="271" ht="12.8">
+    <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E271" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="274" ht="12.8">
+    <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="1" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="275" ht="12.8">
+    <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J275" s="14"/>
       <c r="K275" s="14"/>
     </row>
-    <row r="276" ht="12.8">
+    <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="6"/>
       <c r="B276" s="6"/>
       <c r="C276" s="6"/>
@@ -8958,7 +7750,7 @@
       <c r="L276" s="6"/>
       <c r="M276" s="1"/>
     </row>
-    <row r="277" ht="12.8">
+    <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="6"/>
       <c r="B277" s="6"/>
       <c r="C277" s="6"/>
@@ -8966,7 +7758,7 @@
       <c r="E277" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F277" s="6">
+      <c r="F277" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G277" s="6"/>
@@ -8976,7 +7768,7 @@
       <c r="L277" s="6"/>
       <c r="M277" s="1"/>
     </row>
-    <row r="278" ht="12.8">
+    <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="6"/>
       <c r="B278" s="6"/>
       <c r="C278" s="6"/>
@@ -8994,7 +7786,7 @@
       <c r="L278" s="6"/>
       <c r="M278" s="1"/>
     </row>
-    <row r="279" ht="12.8">
+    <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="6"/>
       <c r="B279" s="6"/>
       <c r="C279" s="6"/>
@@ -9008,7 +7800,7 @@
       <c r="L279" s="6"/>
       <c r="M279" s="1"/>
     </row>
-    <row r="280" ht="12.8">
+    <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="6"/>
       <c r="B280" s="6"/>
       <c r="C280" s="6"/>
@@ -9016,7 +7808,7 @@
       <c r="E280" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F280" s="6">
+      <c r="F280" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G280" s="6"/>
@@ -9026,23 +7818,23 @@
       <c r="L280" s="6"/>
       <c r="M280" s="1"/>
     </row>
-    <row r="281" ht="12.8">
+    <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J281" s="14"/>
       <c r="K281" s="14"/>
     </row>
-    <row r="282" ht="12.8">
+    <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J282" s="14"/>
       <c r="K282" s="14"/>
     </row>
-    <row r="283" ht="12.8">
+    <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J283" s="14"/>
       <c r="K283" s="14"/>
     </row>
-    <row r="284" ht="13.8">
+    <row r="284" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G284" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I284" s="1">
+      <c r="I284" s="1" t="n">
         <v>164</v>
       </c>
       <c r="J284" s="7" t="s">
@@ -9051,15 +7843,12 @@
       <c r="K284" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="L284" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="285" ht="13.8">
+    </row>
+    <row r="285" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G285" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="I285" s="1">
+      <c r="I285" s="1" t="n">
         <v>165</v>
       </c>
       <c r="J285" s="7" t="s">
@@ -9068,15 +7857,12 @@
       <c r="K285" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="L285" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="286" ht="13.8">
+    </row>
+    <row r="286" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G286" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I286" s="1">
+      <c r="I286" s="1" t="n">
         <v>166</v>
       </c>
       <c r="J286" s="7" t="s">
@@ -9085,13 +7871,10 @@
       <c r="K286" s="9" t="s">
         <v>341</v>
       </c>
-      <c r="L286" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="287" ht="13.8">
+    </row>
+    <row r="287" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G287" s="6"/>
-      <c r="I287" s="1">
+      <c r="I287" s="1" t="n">
         <v>167</v>
       </c>
       <c r="J287" s="7" t="s">
@@ -9100,15 +7883,12 @@
       <c r="K287" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="L287" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="288" ht="13.8">
+    </row>
+    <row r="288" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G288" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I288" s="1">
+      <c r="I288" s="1" t="n">
         <v>168</v>
       </c>
       <c r="J288" s="7" t="s">
@@ -9117,13 +7897,10 @@
       <c r="K288" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="L288" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="289" ht="35.05">
+    </row>
+    <row r="289" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G289" s="6"/>
-      <c r="I289" s="1">
+      <c r="I289" s="1" t="n">
         <v>169</v>
       </c>
       <c r="J289" s="7" t="s">
@@ -9132,15 +7909,12 @@
       <c r="K289" s="9" t="s">
         <v>347</v>
       </c>
-      <c r="L289" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="290" ht="13.8">
+    </row>
+    <row r="290" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G290" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="I290" s="1">
+      <c r="I290" s="1" t="n">
         <v>170</v>
       </c>
       <c r="J290" s="7" t="s">
@@ -9149,49 +7923,46 @@
       <c r="K290" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="L290" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="291" ht="13.8">
+    </row>
+    <row r="291" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G291" s="6"/>
       <c r="J291" s="7"/>
       <c r="K291" s="9"/>
     </row>
-    <row r="292" ht="13.8">
+    <row r="292" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E292" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F292" s="6">
+      <c r="F292" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J292" s="7"/>
       <c r="K292" s="9"/>
     </row>
-    <row r="293" ht="13.8">
+    <row r="293" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E293" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F293" s="1">
+      <c r="F293" s="1" t="n">
         <v>86</v>
       </c>
       <c r="J293" s="7"/>
       <c r="K293" s="9"/>
     </row>
-    <row r="294" ht="13.8">
+    <row r="294" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E294" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F294" s="6">
+      <c r="F294" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G294" s="6"/>
       <c r="J294" s="7"/>
       <c r="K294" s="9"/>
     </row>
-    <row r="295" ht="13.8">
+    <row r="295" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G295" s="6"/>
-      <c r="I295" s="1">
+      <c r="I295" s="1" t="n">
         <v>171</v>
       </c>
       <c r="J295" s="7" t="s">
@@ -9200,15 +7971,12 @@
       <c r="K295" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="L295" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="296" ht="23.85">
+    </row>
+    <row r="296" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G296" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I296" s="1">
+      <c r="I296" s="1" t="n">
         <v>172</v>
       </c>
       <c r="J296" s="7" t="s">
@@ -9217,15 +7985,12 @@
       <c r="K296" s="9" t="s">
         <v>353</v>
       </c>
-      <c r="L296" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="297" ht="35.05">
+    </row>
+    <row r="297" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G297" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I297" s="1">
+      <c r="I297" s="1" t="n">
         <v>173</v>
       </c>
       <c r="J297" s="7" t="s">
@@ -9234,15 +7999,12 @@
       <c r="K297" s="9" t="s">
         <v>355</v>
       </c>
-      <c r="L297" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="298" ht="23.85">
+    </row>
+    <row r="298" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G298" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I298" s="1">
+      <c r="I298" s="1" t="n">
         <v>174</v>
       </c>
       <c r="J298" s="7" t="s">
@@ -9251,15 +8013,12 @@
       <c r="K298" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="L298" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="299" ht="13.8">
+    </row>
+    <row r="299" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G299" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I299" s="1">
+      <c r="I299" s="1" t="n">
         <v>175</v>
       </c>
       <c r="J299" s="7" t="s">
@@ -9268,15 +8027,12 @@
       <c r="K299" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="L299" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="300" ht="135.8">
+    </row>
+    <row r="300" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G300" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I300" s="1">
+      <c r="I300" s="1" t="n">
         <v>176</v>
       </c>
       <c r="J300" s="7" t="s">
@@ -9285,15 +8041,12 @@
       <c r="K300" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="L300" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="301" ht="91">
+    </row>
+    <row r="301" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G301" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I301" s="1">
+      <c r="I301" s="1" t="n">
         <v>177</v>
       </c>
       <c r="J301" s="7" t="s">
@@ -9302,15 +8055,12 @@
       <c r="K301" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="L301" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="302" ht="35.05">
+    </row>
+    <row r="302" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G302" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I302" s="1">
+      <c r="I302" s="1" t="n">
         <v>178</v>
       </c>
       <c r="J302" s="7" t="s">
@@ -9319,15 +8069,12 @@
       <c r="K302" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="L302" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="303" ht="13.8">
+    </row>
+    <row r="303" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G303" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="I303" s="1">
+      <c r="I303" s="1" t="n">
         <v>179</v>
       </c>
       <c r="J303" s="7" t="s">
@@ -9336,15 +8083,12 @@
       <c r="K303" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="L303" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="304" ht="46.25">
+    </row>
+    <row r="304" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G304" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I304" s="1">
+      <c r="I304" s="1" t="n">
         <v>181</v>
       </c>
       <c r="J304" s="7" t="s">
@@ -9353,15 +8097,12 @@
       <c r="K304" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="L304" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="305" ht="23.85">
+    </row>
+    <row r="305" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G305" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I305" s="1">
+      <c r="I305" s="1" t="n">
         <v>182</v>
       </c>
       <c r="J305" s="7" t="s">
@@ -9370,15 +8111,12 @@
       <c r="K305" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="L305" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="306" ht="46.25">
+    </row>
+    <row r="306" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G306" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I306" s="1">
+      <c r="I306" s="1" t="n">
         <v>183</v>
       </c>
       <c r="J306" s="7" t="s">
@@ -9387,26 +8125,23 @@
       <c r="K306" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="L306" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="307" ht="13.8">
+    </row>
+    <row r="307" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E307" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F307" s="16">
+      <c r="F307" s="16" t="n">
         <v>74</v>
       </c>
       <c r="G307" s="6"/>
       <c r="J307" s="7"/>
       <c r="K307" s="9"/>
     </row>
-    <row r="308" ht="13.8">
+    <row r="308" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G308" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I308" s="1">
+      <c r="I308" s="1" t="n">
         <v>184</v>
       </c>
       <c r="J308" s="7" t="s">
@@ -9415,21 +8150,18 @@
       <c r="K308" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="L308" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="309" ht="13.8">
+    </row>
+    <row r="309" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F309" s="16"/>
       <c r="G309" s="6"/>
       <c r="J309" s="7"/>
       <c r="K309" s="9"/>
     </row>
-    <row r="310" ht="23.85">
+    <row r="310" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G310" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I310" s="1">
+      <c r="I310" s="1" t="n">
         <v>185</v>
       </c>
       <c r="J310" s="7" t="s">
@@ -9438,15 +8170,12 @@
       <c r="K310" s="9" t="s">
         <v>373</v>
       </c>
-      <c r="L310" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="311" ht="13.8">
+    </row>
+    <row r="311" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G311" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I311" s="1">
+      <c r="I311" s="1" t="n">
         <v>186</v>
       </c>
       <c r="J311" s="7" t="s">
@@ -9455,15 +8184,12 @@
       <c r="K311" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="L311" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="312" ht="13.8">
+    </row>
+    <row r="312" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G312" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I312" s="1">
+      <c r="I312" s="1" t="n">
         <v>187</v>
       </c>
       <c r="J312" s="7" t="s">
@@ -9472,15 +8198,12 @@
       <c r="K312" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="L312" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="313" ht="23.85">
+    </row>
+    <row r="313" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G313" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I313" s="1">
+      <c r="I313" s="1" t="n">
         <v>188</v>
       </c>
       <c r="J313" s="7" t="s">
@@ -9489,15 +8212,12 @@
       <c r="K313" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="L313" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="314" ht="23.85">
+    </row>
+    <row r="314" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G314" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I314" s="1">
+      <c r="I314" s="1" t="n">
         <v>189</v>
       </c>
       <c r="J314" s="7" t="s">
@@ -9506,15 +8226,12 @@
       <c r="K314" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="L314" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="315" ht="13.8">
+    </row>
+    <row r="315" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G315" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I315" s="1">
+      <c r="I315" s="1" t="n">
         <v>190</v>
       </c>
       <c r="J315" s="7" t="s">
@@ -9523,15 +8240,12 @@
       <c r="K315" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="L315" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="316" ht="13.8">
+    </row>
+    <row r="316" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G316" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I316" s="1">
+      <c r="I316" s="1" t="n">
         <v>191</v>
       </c>
       <c r="J316" s="7" t="s">
@@ -9540,15 +8254,12 @@
       <c r="K316" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="L316" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="317" ht="13.8">
+    </row>
+    <row r="317" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G317" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="I317" s="1">
+      <c r="I317" s="1" t="n">
         <v>192</v>
       </c>
       <c r="J317" s="7" t="s">
@@ -9557,15 +8268,12 @@
       <c r="K317" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="L317" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="318" ht="113.4">
+    </row>
+    <row r="318" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G318" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I318" s="1">
+      <c r="I318" s="1" t="n">
         <v>193</v>
       </c>
       <c r="J318" s="7" t="s">
@@ -9574,21 +8282,18 @@
       <c r="K318" s="9" t="s">
         <v>382</v>
       </c>
-      <c r="L318" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="319" ht="13.8">
+    </row>
+    <row r="319" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G319" s="6"/>
       <c r="J319" s="7"/>
       <c r="K319" s="9"/>
     </row>
-    <row r="320" ht="13.8">
+    <row r="320" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G320" s="6"/>
       <c r="J320" s="7"/>
       <c r="K320" s="9"/>
     </row>
-    <row r="321" ht="13.8">
+    <row r="321" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E321" s="1" t="s">
         <v>383</v>
       </c>
@@ -9599,7 +8304,7 @@
       <c r="J321" s="7"/>
       <c r="K321" s="9"/>
     </row>
-    <row r="322" ht="13.8">
+    <row r="322" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E322" s="1" t="s">
         <v>383</v>
       </c>
@@ -9610,77 +8315,77 @@
       <c r="J322" s="7"/>
       <c r="K322" s="9"/>
     </row>
-    <row r="323" ht="13.8">
+    <row r="323" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G323" s="6"/>
       <c r="J323" s="7"/>
       <c r="K323" s="9"/>
     </row>
-    <row r="324" ht="13.8">
+    <row r="324" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G324" s="6"/>
       <c r="J324" s="7"/>
       <c r="K324" s="9"/>
     </row>
-    <row r="325" ht="13.8">
+    <row r="325" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G325" s="6"/>
       <c r="J325" s="7"/>
       <c r="K325" s="9"/>
     </row>
-    <row r="326" ht="13.8">
+    <row r="326" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E326" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F326" s="6">
+      <c r="F326" s="6" t="n">
         <v>3</v>
       </c>
       <c r="G326" s="6"/>
       <c r="J326" s="12"/>
       <c r="K326" s="9"/>
     </row>
-    <row r="327" ht="13.8">
+    <row r="327" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E327" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F327" s="1">
+      <c r="F327" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="G327" s="6"/>
       <c r="J327" s="12"/>
       <c r="K327" s="9"/>
     </row>
-    <row r="328" ht="13.8">
+    <row r="328" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G328" s="6"/>
       <c r="J328" s="12"/>
       <c r="K328" s="9"/>
     </row>
-    <row r="329" ht="12.8">
+    <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E329" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="332" ht="12.8">
+    <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="1" t="s">
         <v>386</v>
       </c>
       <c r="F332" s="16"/>
     </row>
-    <row r="333" ht="12.8">
+    <row r="333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E333" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="F333" s="16">
+      <c r="F333" s="16" t="n">
         <v>77</v>
       </c>
       <c r="J333" s="6"/>
     </row>
-    <row r="334" ht="12.8">
+    <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F334" s="16"/>
     </row>
-    <row r="335" ht="35.05">
+    <row r="335" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F335" s="16"/>
       <c r="G335" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I335" s="1">
+      <c r="I335" s="1" t="n">
         <v>200</v>
       </c>
       <c r="J335" s="7" t="s">
@@ -9689,16 +8394,13 @@
       <c r="K335" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="L335" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="336" ht="23.85">
+    </row>
+    <row r="336" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F336" s="16"/>
       <c r="G336" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I336" s="1">
+      <c r="I336" s="1" t="n">
         <v>201</v>
       </c>
       <c r="J336" s="7" t="s">
@@ -9707,21 +8409,18 @@
       <c r="K336" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="L336" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="337" ht="13.8">
+    </row>
+    <row r="337" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F337" s="16"/>
       <c r="J337" s="7"/>
       <c r="K337" s="4"/>
     </row>
-    <row r="338" ht="35.05">
+    <row r="338" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F338" s="16"/>
       <c r="G338" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I338" s="1">
+      <c r="I338" s="1" t="n">
         <v>202</v>
       </c>
       <c r="J338" s="7" t="s">
@@ -9730,11 +8429,8 @@
       <c r="K338" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="L338" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="339" ht="13.8">
+    </row>
+    <row r="339" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="1" t="s">
         <v>394</v>
       </c>
@@ -9742,12 +8438,12 @@
       <c r="J339" s="7"/>
       <c r="K339" s="6"/>
     </row>
-    <row r="340" ht="79.85">
+    <row r="340" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F340" s="16"/>
       <c r="G340" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I340" s="1">
+      <c r="I340" s="1" t="n">
         <v>203</v>
       </c>
       <c r="J340" s="7" t="s">
@@ -9756,11 +8452,8 @@
       <c r="K340" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="L340" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="341" ht="13.8">
+    </row>
+    <row r="341" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B341" s="1" t="s">
         <v>397</v>
       </c>
@@ -9768,7 +8461,7 @@
         <v>18</v>
       </c>
       <c r="F341" s="16"/>
-      <c r="I341" s="1">
+      <c r="I341" s="1" t="n">
         <v>204</v>
       </c>
       <c r="J341" s="7" t="s">
@@ -9777,11 +8470,8 @@
       <c r="K341" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="L341" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="342" ht="13.8">
+    </row>
+    <row r="342" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B342" s="1" t="s">
         <v>400</v>
       </c>
@@ -9789,7 +8479,7 @@
         <v>18</v>
       </c>
       <c r="F342" s="16"/>
-      <c r="I342" s="1">
+      <c r="I342" s="1" t="n">
         <v>205</v>
       </c>
       <c r="J342" s="7" t="s">
@@ -9798,11 +8488,8 @@
       <c r="K342" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="L342" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="343" ht="13.8">
+    </row>
+    <row r="343" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="1" t="s">
         <v>397</v>
       </c>
@@ -9810,12 +8497,12 @@
       <c r="J343" s="7"/>
       <c r="K343" s="6"/>
     </row>
-    <row r="344" ht="46.25">
+    <row r="344" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F344" s="16"/>
       <c r="G344" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I344" s="1">
+      <c r="I344" s="1" t="n">
         <v>206</v>
       </c>
       <c r="J344" s="7" t="s">
@@ -9824,11 +8511,8 @@
       <c r="K344" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="L344" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="345" ht="13.8">
+    </row>
+    <row r="345" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B345" s="1" t="s">
         <v>405</v>
       </c>
@@ -9836,7 +8520,7 @@
         <v>18</v>
       </c>
       <c r="F345" s="16"/>
-      <c r="I345" s="1">
+      <c r="I345" s="1" t="n">
         <v>207</v>
       </c>
       <c r="J345" s="7" t="s">
@@ -9845,11 +8529,8 @@
       <c r="K345" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="L345" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="346" ht="13.8">
+    </row>
+    <row r="346" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B346" s="1" t="s">
         <v>394</v>
       </c>
@@ -9857,7 +8538,7 @@
         <v>18</v>
       </c>
       <c r="F346" s="16"/>
-      <c r="I346" s="1">
+      <c r="I346" s="1" t="n">
         <v>208</v>
       </c>
       <c r="J346" s="7" t="s">
@@ -9866,11 +8547,8 @@
       <c r="K346" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="L346" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="347" ht="13.8">
+    </row>
+    <row r="347" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="1" t="s">
         <v>400</v>
       </c>
@@ -9878,12 +8556,12 @@
       <c r="J347" s="7"/>
       <c r="K347" s="6"/>
     </row>
-    <row r="348" ht="46.25">
+    <row r="348" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F348" s="16"/>
       <c r="G348" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I348" s="1">
+      <c r="I348" s="1" t="n">
         <v>209</v>
       </c>
       <c r="J348" s="7" t="s">
@@ -9892,11 +8570,8 @@
       <c r="K348" s="6" t="s">
         <v>411</v>
       </c>
-      <c r="L348" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="349" ht="13.8">
+    </row>
+    <row r="349" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B349" s="1" t="s">
         <v>412</v>
       </c>
@@ -9904,7 +8579,7 @@
         <v>18</v>
       </c>
       <c r="F349" s="16"/>
-      <c r="I349" s="1">
+      <c r="I349" s="1" t="n">
         <v>210</v>
       </c>
       <c r="J349" s="7" t="s">
@@ -9913,11 +8588,8 @@
       <c r="K349" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="L349" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="350" ht="13.8">
+    </row>
+    <row r="350" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B350" s="1" t="s">
         <v>394</v>
       </c>
@@ -9925,7 +8597,7 @@
         <v>18</v>
       </c>
       <c r="F350" s="16"/>
-      <c r="I350" s="1">
+      <c r="I350" s="1" t="n">
         <v>211</v>
       </c>
       <c r="J350" s="7" t="s">
@@ -9934,16 +8606,13 @@
       <c r="K350" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="L350" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="351" ht="13.8">
+    </row>
+    <row r="351" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F351" s="16"/>
       <c r="J351" s="7"/>
       <c r="K351" s="6"/>
     </row>
-    <row r="352" ht="13.8">
+    <row r="352" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="1" t="s">
         <v>412</v>
       </c>
@@ -9951,7 +8620,7 @@
       <c r="J352" s="7"/>
       <c r="K352" s="6"/>
     </row>
-    <row r="353" ht="13.8">
+    <row r="353" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E353" s="1" t="s">
         <v>413</v>
       </c>
@@ -9961,7 +8630,7 @@
       <c r="J353" s="7"/>
       <c r="K353" s="6"/>
     </row>
-    <row r="354" ht="13.8">
+    <row r="354" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="1" t="s">
         <v>405</v>
       </c>
@@ -9969,12 +8638,12 @@
       <c r="J354" s="7"/>
       <c r="K354" s="6"/>
     </row>
-    <row r="355" ht="46.25">
+    <row r="355" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F355" s="16"/>
       <c r="G355" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I355" s="1">
+      <c r="I355" s="1" t="n">
         <v>212</v>
       </c>
       <c r="J355" s="7" t="s">
@@ -9983,16 +8652,13 @@
       <c r="K355" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="L355" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="356" ht="46.25">
+    </row>
+    <row r="356" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F356" s="16"/>
       <c r="G356" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I356" s="1">
+      <c r="I356" s="1" t="n">
         <v>213</v>
       </c>
       <c r="J356" s="7" t="s">
@@ -10001,11 +8667,8 @@
       <c r="K356" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="L356" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="357" ht="13.8">
+    </row>
+    <row r="357" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E357" s="1" t="s">
         <v>419</v>
       </c>
@@ -10015,12 +8678,12 @@
       <c r="J357" s="7"/>
       <c r="K357" s="6"/>
     </row>
-    <row r="358" ht="13.8">
+    <row r="358" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F358" s="16"/>
       <c r="G358" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I358" s="1">
+      <c r="I358" s="1" t="n">
         <v>214</v>
       </c>
       <c r="J358" s="7" t="s">
@@ -10029,21 +8692,18 @@
       <c r="K358" s="6" t="s">
         <v>422</v>
       </c>
-      <c r="L358" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="359" ht="13.8">
+    </row>
+    <row r="359" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F359" s="16"/>
       <c r="J359" s="7"/>
       <c r="K359" s="6"/>
     </row>
-    <row r="360" ht="13.8">
+    <row r="360" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F360" s="16"/>
       <c r="G360" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I360" s="1">
+      <c r="I360" s="1" t="n">
         <v>215</v>
       </c>
       <c r="J360" s="7" t="s">
@@ -10052,16 +8712,13 @@
       <c r="K360" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="L360" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="361" ht="13.8">
+    </row>
+    <row r="361" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F361" s="16"/>
       <c r="G361" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="I361" s="1">
+      <c r="I361" s="1" t="n">
         <v>216</v>
       </c>
       <c r="J361" s="7" t="s">
@@ -10070,11 +8727,8 @@
       <c r="K361" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="L361" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="362" ht="13.8">
+    </row>
+    <row r="362" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E362" s="1" t="s">
         <v>383</v>
       </c>
@@ -10084,7 +8738,7 @@
       <c r="J362" s="7"/>
       <c r="K362" s="6"/>
     </row>
-    <row r="363" ht="13.8">
+    <row r="363" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E363" s="1" t="s">
         <v>383</v>
       </c>
@@ -10094,12 +8748,12 @@
       <c r="J363" s="7"/>
       <c r="K363" s="6"/>
     </row>
-    <row r="364" ht="68.65">
+    <row r="364" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F364" s="16"/>
       <c r="G364" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I364" s="1">
+      <c r="I364" s="1" t="n">
         <v>217</v>
       </c>
       <c r="J364" s="7" t="s">
@@ -10108,16 +8762,13 @@
       <c r="K364" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="L364" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="365" ht="13.8">
+    </row>
+    <row r="365" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F365" s="16"/>
       <c r="G365" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I365" s="1">
+      <c r="I365" s="1" t="n">
         <v>218</v>
       </c>
       <c r="J365" s="7" t="s">
@@ -10126,16 +8777,13 @@
       <c r="K365" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="L365" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="366" ht="13.8">
+    </row>
+    <row r="366" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F366" s="16"/>
       <c r="G366" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I366" s="1">
+      <c r="I366" s="1" t="n">
         <v>219</v>
       </c>
       <c r="J366" s="7" t="s">
@@ -10144,16 +8792,13 @@
       <c r="K366" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="L366" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="367" ht="13.8">
+    </row>
+    <row r="367" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F367" s="16"/>
       <c r="G367" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I367" s="1">
+      <c r="I367" s="1" t="n">
         <v>220</v>
       </c>
       <c r="J367" s="7" t="s">
@@ -10162,16 +8807,13 @@
       <c r="K367" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="L367" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="368" ht="13.8">
+    </row>
+    <row r="368" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F368" s="16"/>
       <c r="J368" s="7"/>
       <c r="K368" s="6"/>
     </row>
-    <row r="369" ht="12.8">
+    <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E369" s="1" t="s">
         <v>433</v>
       </c>
@@ -10180,16 +8822,16 @@
       </c>
       <c r="J369" s="6"/>
     </row>
-    <row r="370" ht="12.8">
+    <row r="370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F370" s="16"/>
       <c r="J370" s="6"/>
     </row>
-    <row r="371" ht="13.8">
+    <row r="371" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F371" s="16"/>
       <c r="J371" s="3"/>
       <c r="K371" s="4"/>
     </row>
-    <row r="372" ht="13.8">
+    <row r="372" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E372" s="1" t="s">
         <v>435</v>
       </c>
@@ -10197,7 +8839,7 @@
       <c r="J372" s="3"/>
       <c r="K372" s="4"/>
     </row>
-    <row r="373" ht="13.8">
+    <row r="373" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E373" s="1" t="s">
         <v>239</v>
       </c>
@@ -10207,17 +8849,17 @@
       <c r="J373" s="3"/>
       <c r="K373" s="4"/>
     </row>
-    <row r="374" ht="13.8">
+    <row r="374" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E374" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="F374" s="16">
+      <c r="F374" s="16" t="n">
         <v>107</v>
       </c>
       <c r="J374" s="3"/>
       <c r="K374" s="4"/>
     </row>
-    <row r="375" ht="12.8">
+    <row r="375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E375" s="1" t="s">
         <v>239</v>
       </c>
@@ -10225,12 +8867,12 @@
         <v>436</v>
       </c>
     </row>
-    <row r="376" ht="45.5">
+    <row r="376" customFormat="false" ht="45.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F376" s="16"/>
       <c r="G376" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="I376" s="1">
+      <c r="I376" s="1" t="n">
         <v>221</v>
       </c>
       <c r="J376" s="6" t="s">
@@ -10239,16 +8881,13 @@
       <c r="K376" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="L376" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="377" ht="13.8">
+    </row>
+    <row r="377" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F377" s="16"/>
       <c r="G377" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I377" s="1">
+      <c r="I377" s="1" t="n">
         <v>222</v>
       </c>
       <c r="J377" s="7" t="s">
@@ -10257,16 +8896,13 @@
       <c r="K377" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="L377" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="378" ht="13.8">
+    </row>
+    <row r="378" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F378" s="16"/>
       <c r="G378" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I378" s="1">
+      <c r="I378" s="1" t="n">
         <v>223</v>
       </c>
       <c r="J378" s="7" t="s">
@@ -10275,16 +8911,13 @@
       <c r="K378" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="L378" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="379" ht="23.85">
+    </row>
+    <row r="379" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F379" s="16"/>
       <c r="G379" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="I379" s="1">
+      <c r="I379" s="1" t="n">
         <v>224</v>
       </c>
       <c r="J379" s="18" t="s">
@@ -10293,16 +8926,13 @@
       <c r="K379" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="L379" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="380" ht="23.1">
+    </row>
+    <row r="380" customFormat="false" ht="23.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F380" s="16"/>
       <c r="G380" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I380" s="1">
+      <c r="I380" s="1" t="n">
         <v>225</v>
       </c>
       <c r="J380" s="18" t="s">
@@ -10311,16 +8941,13 @@
       <c r="K380" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="L380" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="381" ht="79.85">
+    </row>
+    <row r="381" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F381" s="16"/>
       <c r="G381" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I381" s="1">
+      <c r="I381" s="1" t="n">
         <v>226</v>
       </c>
       <c r="J381" s="7" t="s">
@@ -10329,11 +8956,8 @@
       <c r="K381" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="L381" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="382" ht="12.8">
+    </row>
+    <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E382" s="1" t="s">
         <v>433</v>
       </c>
@@ -10341,7 +8965,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="383" ht="12.8">
+    <row r="383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E383" s="1" t="s">
         <v>239</v>
       </c>
@@ -10349,7 +8973,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="384" ht="12.8">
+    <row r="384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E384" s="1" t="s">
         <v>433</v>
       </c>
@@ -10357,22 +8981,22 @@
         <v>451</v>
       </c>
     </row>
-    <row r="385" ht="12.8">
+    <row r="385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E385" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F385" s="16"/>
     </row>
-    <row r="386" ht="12.8">
+    <row r="386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F386" s="16"/>
     </row>
-    <row r="388" ht="12.8">
+    <row r="388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="1" t="s">
         <v>452</v>
       </c>
       <c r="F388" s="16"/>
     </row>
-    <row r="389" ht="12.8">
+    <row r="389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E389" s="1" t="s">
         <v>239</v>
       </c>
@@ -10380,21 +9004,21 @@
         <v>200</v>
       </c>
     </row>
-    <row r="390" ht="12.8">
+    <row r="390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E390" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="F390" s="1">
+      <c r="F390" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G390" s="6"/>
       <c r="J390" s="6"/>
     </row>
-    <row r="392" ht="13.8">
+    <row r="392" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G392" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I392" s="1">
+      <c r="I392" s="1" t="n">
         <v>230</v>
       </c>
       <c r="J392" s="7" t="s">
@@ -10403,16 +9027,13 @@
       <c r="K392" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="L392" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="393" ht="12.8">
+    </row>
+    <row r="393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F393" s="16"/>
       <c r="G393" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I393" s="1">
+      <c r="I393" s="1" t="n">
         <v>231</v>
       </c>
       <c r="J393" s="6" t="s">
@@ -10421,16 +9042,13 @@
       <c r="K393" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="L393" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="394" ht="22.35">
+    </row>
+    <row r="394" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F394" s="16"/>
       <c r="G394" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I394" s="1">
+      <c r="I394" s="1" t="n">
         <v>232</v>
       </c>
       <c r="J394" s="18" t="s">
@@ -10439,16 +9057,13 @@
       <c r="K394" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="L394" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="395" ht="43.25">
+    </row>
+    <row r="395" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F395" s="16"/>
       <c r="G395" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I395" s="1">
+      <c r="I395" s="1" t="n">
         <v>233</v>
       </c>
       <c r="J395" s="18" t="s">
@@ -10457,16 +9072,13 @@
       <c r="K395" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="L395" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="396" ht="23.85">
+    </row>
+    <row r="396" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F396" s="16"/>
       <c r="G396" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I396" s="1">
+      <c r="I396" s="1" t="n">
         <v>234</v>
       </c>
       <c r="J396" s="7" t="s">
@@ -10475,16 +9087,13 @@
       <c r="K396" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="L396" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="397" ht="32.8">
+    </row>
+    <row r="397" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F397" s="16"/>
       <c r="G397" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I397" s="1">
+      <c r="I397" s="1" t="n">
         <v>235</v>
       </c>
       <c r="J397" s="6" t="s">
@@ -10493,30 +9102,27 @@
       <c r="K397" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="L397" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="398" ht="12.8">
+    </row>
+    <row r="398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F398" s="16"/>
       <c r="J398" s="6"/>
     </row>
-    <row r="399" ht="12.8">
+    <row r="399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E399" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F399" s="16"/>
     </row>
-    <row r="400" ht="12.8">
+    <row r="400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F400" s="16"/>
     </row>
-    <row r="401" ht="12.8">
+    <row r="401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="1" t="s">
         <v>466</v>
       </c>
       <c r="F401" s="16"/>
     </row>
-    <row r="403" ht="12.8">
+    <row r="403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E403" s="6" t="s">
         <v>79</v>
       </c>
@@ -10526,15 +9132,15 @@
       <c r="G403" s="6"/>
       <c r="J403" s="6"/>
     </row>
-    <row r="404" ht="12.8">
+    <row r="404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E404" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F404" s="6">
+      <c r="F404" s="6" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="405" ht="13.8">
+    <row r="405" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E405" s="6" t="s">
         <v>82</v>
       </c>
@@ -10544,41 +9150,41 @@
       <c r="J405" s="7"/>
       <c r="K405" s="6"/>
     </row>
-    <row r="406" ht="12.8">
+    <row r="406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E406" s="6"/>
       <c r="F406" s="10"/>
       <c r="J406" s="6"/>
       <c r="K406" s="6"/>
     </row>
-    <row r="407" ht="12.8">
+    <row r="407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E407" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F407" s="1">
+      <c r="F407" s="1" t="n">
         <v>41</v>
       </c>
       <c r="J407" s="6"/>
       <c r="K407" s="6"/>
     </row>
-    <row r="408" ht="12.8">
+    <row r="408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E408" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F408" s="6">
+      <c r="F408" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J408" s="18"/>
       <c r="K408" s="6"/>
     </row>
-    <row r="409" ht="12.8">
+    <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J409" s="18"/>
       <c r="K409" s="6"/>
     </row>
-    <row r="410" ht="13.8">
+    <row r="410" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G410" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="I410" s="1">
+      <c r="I410" s="1" t="n">
         <v>250</v>
       </c>
       <c r="J410" s="15" t="s">
@@ -10587,15 +9193,12 @@
       <c r="K410" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="L410" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="411" ht="13.8">
+    </row>
+    <row r="411" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G411" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I411" s="1">
+      <c r="I411" s="1" t="n">
         <v>251</v>
       </c>
       <c r="J411" s="7" t="s">
@@ -10604,15 +9207,12 @@
       <c r="K411" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="L411" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="412" ht="35.05">
+    </row>
+    <row r="412" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G412" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="I412" s="1">
+      <c r="I412" s="1" t="n">
         <v>252</v>
       </c>
       <c r="J412" s="7" t="s">
@@ -10621,15 +9221,12 @@
       <c r="K412" s="6" t="s">
         <v>473</v>
       </c>
-      <c r="L412" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="413" ht="46.25">
+    </row>
+    <row r="413" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G413" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I413" s="1">
+      <c r="I413" s="1" t="n">
         <v>253</v>
       </c>
       <c r="J413" s="7" t="s">
@@ -10638,15 +9235,12 @@
       <c r="K413" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="L413" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="414" ht="13.8">
+    </row>
+    <row r="414" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G414" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="I414" s="1">
+      <c r="I414" s="1" t="n">
         <v>254</v>
       </c>
       <c r="J414" s="15" t="s">
@@ -10655,15 +9249,12 @@
       <c r="K414" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="L414" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="415" ht="46.25">
+    </row>
+    <row r="415" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G415" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I415" s="1">
+      <c r="I415" s="1" t="n">
         <v>255</v>
       </c>
       <c r="J415" s="7" t="s">
@@ -10672,15 +9263,12 @@
       <c r="K415" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="L415" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="416" ht="13.8">
+    </row>
+    <row r="416" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G416" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I416" s="1">
+      <c r="I416" s="1" t="n">
         <v>256</v>
       </c>
       <c r="J416" s="7" t="s">
@@ -10689,15 +9277,12 @@
       <c r="K416" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="L416" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="417" ht="13.8">
+    </row>
+    <row r="417" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G417" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I417" s="1">
+      <c r="I417" s="1" t="n">
         <v>257</v>
       </c>
       <c r="J417" s="7" t="s">
@@ -10706,15 +9291,12 @@
       <c r="K417" s="6" t="s">
         <v>483</v>
       </c>
-      <c r="L417" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="418" ht="23.85">
+    </row>
+    <row r="418" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G418" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I418" s="1">
+      <c r="I418" s="1" t="n">
         <v>258</v>
       </c>
       <c r="J418" s="7" t="s">
@@ -10723,15 +9305,12 @@
       <c r="K418" s="6" t="s">
         <v>485</v>
       </c>
-      <c r="L418" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="419" ht="68.65">
+    </row>
+    <row r="419" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G419" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I419" s="1">
+      <c r="I419" s="1" t="n">
         <v>259</v>
       </c>
       <c r="J419" s="7" t="s">
@@ -10740,15 +9319,12 @@
       <c r="K419" s="6" t="s">
         <v>487</v>
       </c>
-      <c r="L419" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="420" ht="13.8">
+    </row>
+    <row r="420" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G420" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I420" s="1">
+      <c r="I420" s="1" t="n">
         <v>260</v>
       </c>
       <c r="J420" s="7" t="s">
@@ -10757,15 +9333,12 @@
       <c r="K420" s="6" t="s">
         <v>489</v>
       </c>
-      <c r="L420" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="421" ht="23.85">
+    </row>
+    <row r="421" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G421" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I421" s="1">
+      <c r="I421" s="1" t="n">
         <v>261</v>
       </c>
       <c r="J421" s="7" t="s">
@@ -10774,15 +9347,12 @@
       <c r="K421" s="9" t="s">
         <v>491</v>
       </c>
-      <c r="L421" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="422" ht="23.85">
+    </row>
+    <row r="422" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G422" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I422" s="1">
+      <c r="I422" s="1" t="n">
         <v>262</v>
       </c>
       <c r="J422" s="7" t="s">
@@ -10791,15 +9361,12 @@
       <c r="K422" s="6" t="s">
         <v>493</v>
       </c>
-      <c r="L422" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="423" ht="23.85">
+    </row>
+    <row r="423" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G423" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I423" s="1">
+      <c r="I423" s="1" t="n">
         <v>263</v>
       </c>
       <c r="J423" s="7" t="s">
@@ -10808,55 +9375,52 @@
       <c r="K423" s="6" t="s">
         <v>495</v>
       </c>
-      <c r="L423" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="424" ht="13.8">
+    </row>
+    <row r="424" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J424" s="7"/>
       <c r="K424" s="6"/>
     </row>
-    <row r="425" ht="13.8">
+    <row r="425" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E425" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F425" s="6">
+      <c r="F425" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J425" s="7"/>
       <c r="K425" s="6"/>
     </row>
-    <row r="426" ht="13.8">
+    <row r="426" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E426" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F426" s="1">
+      <c r="F426" s="1" t="n">
         <v>13</v>
       </c>
       <c r="J426" s="7"/>
       <c r="K426" s="6"/>
     </row>
-    <row r="427" ht="13.8">
+    <row r="427" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E427" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F427" s="6">
+      <c r="F427" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G427" s="6"/>
       <c r="J427" s="7"/>
       <c r="K427" s="6"/>
     </row>
-    <row r="428" ht="12.8">
+    <row r="428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J428" s="18"/>
       <c r="K428" s="6"/>
     </row>
-    <row r="429" ht="13.8">
+    <row r="429" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F429" s="16"/>
       <c r="G429" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I429" s="1">
+      <c r="I429" s="1" t="n">
         <v>264</v>
       </c>
       <c r="J429" s="7" t="s">
@@ -10865,16 +9429,13 @@
       <c r="K429" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="L429" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="430" ht="46.25">
+    </row>
+    <row r="430" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F430" s="16"/>
       <c r="G430" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I430" s="1">
+      <c r="I430" s="1" t="n">
         <v>265</v>
       </c>
       <c r="J430" s="7" t="s">
@@ -10883,16 +9444,13 @@
       <c r="K430" s="6" t="s">
         <v>497</v>
       </c>
-      <c r="L430" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="431" ht="13.8">
+    </row>
+    <row r="431" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F431" s="16"/>
       <c r="G431" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I431" s="1">
+      <c r="I431" s="1" t="n">
         <v>266</v>
       </c>
       <c r="J431" s="7" t="s">
@@ -10901,16 +9459,13 @@
       <c r="K431" s="9" t="s">
         <v>499</v>
       </c>
-      <c r="L431" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="432" ht="91">
+    </row>
+    <row r="432" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F432" s="16"/>
       <c r="G432" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I432" s="1">
+      <c r="I432" s="1" t="n">
         <v>267</v>
       </c>
       <c r="J432" s="7" t="s">
@@ -10919,16 +9474,13 @@
       <c r="K432" s="6" t="s">
         <v>501</v>
       </c>
-      <c r="L432" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="433" ht="13.8">
+    </row>
+    <row r="433" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F433" s="16"/>
       <c r="G433" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I433" s="1">
+      <c r="I433" s="1" t="n">
         <v>268</v>
       </c>
       <c r="J433" s="7" t="s">
@@ -10937,16 +9489,13 @@
       <c r="K433" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="L433" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="434" ht="35.05">
+    </row>
+    <row r="434" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F434" s="16"/>
       <c r="G434" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I434" s="1">
+      <c r="I434" s="1" t="n">
         <v>269</v>
       </c>
       <c r="J434" s="7" t="s">
@@ -10955,16 +9504,13 @@
       <c r="K434" s="6" t="s">
         <v>503</v>
       </c>
-      <c r="L434" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="435" ht="68.65">
+    </row>
+    <row r="435" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F435" s="16"/>
       <c r="G435" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I435" s="1">
+      <c r="I435" s="1" t="n">
         <v>270</v>
       </c>
       <c r="J435" s="7" t="s">
@@ -10973,16 +9519,13 @@
       <c r="K435" s="6" t="s">
         <v>505</v>
       </c>
-      <c r="L435" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="436" ht="85.05">
+    </row>
+    <row r="436" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F436" s="16"/>
       <c r="G436" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I436" s="1">
+      <c r="I436" s="1" t="n">
         <v>271</v>
       </c>
       <c r="J436" s="19" t="s">
@@ -10991,16 +9534,13 @@
       <c r="K436" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="L436" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="437" ht="46.25">
+    </row>
+    <row r="437" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F437" s="16"/>
       <c r="G437" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I437" s="1">
+      <c r="I437" s="1" t="n">
         <v>272</v>
       </c>
       <c r="J437" s="7" t="s">
@@ -11009,16 +9549,13 @@
       <c r="K437" s="6" t="s">
         <v>509</v>
       </c>
-      <c r="L437" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="438" ht="13.8">
+    </row>
+    <row r="438" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F438" s="16"/>
       <c r="G438" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I438" s="1">
+      <c r="I438" s="1" t="n">
         <v>273</v>
       </c>
       <c r="J438" s="7" t="s">
@@ -11027,16 +9564,13 @@
       <c r="K438" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="L438" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="439" ht="35.05">
+    </row>
+    <row r="439" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F439" s="16"/>
       <c r="G439" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I439" s="1">
+      <c r="I439" s="1" t="n">
         <v>274</v>
       </c>
       <c r="J439" s="7" t="s">
@@ -11045,16 +9579,13 @@
       <c r="K439" s="6" t="s">
         <v>511</v>
       </c>
-      <c r="L439" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="440" ht="13.8">
+    </row>
+    <row r="440" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F440" s="16"/>
       <c r="G440" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I440" s="1">
+      <c r="I440" s="1" t="n">
         <v>275</v>
       </c>
       <c r="J440" s="7" t="s">
@@ -11063,16 +9594,13 @@
       <c r="K440" s="6" t="s">
         <v>513</v>
       </c>
-      <c r="L440" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="441" ht="13.8">
+    </row>
+    <row r="441" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F441" s="16"/>
       <c r="G441" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I441" s="1">
+      <c r="I441" s="1" t="n">
         <v>276</v>
       </c>
       <c r="J441" s="7" t="s">
@@ -11081,16 +9609,13 @@
       <c r="K441" s="6" t="s">
         <v>513</v>
       </c>
-      <c r="L441" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="442" ht="13.8">
+    </row>
+    <row r="442" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F442" s="16"/>
       <c r="G442" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I442" s="1">
+      <c r="I442" s="1" t="n">
         <v>277</v>
       </c>
       <c r="J442" s="7" t="s">
@@ -11099,16 +9624,13 @@
       <c r="K442" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="L442" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="443" ht="13.8">
+    </row>
+    <row r="443" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F443" s="16"/>
       <c r="G443" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I443" s="1">
+      <c r="I443" s="1" t="n">
         <v>278</v>
       </c>
       <c r="J443" s="7" t="s">
@@ -11117,16 +9639,13 @@
       <c r="K443" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="L443" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="444" ht="64.15">
+    </row>
+    <row r="444" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F444" s="16"/>
       <c r="G444" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I444" s="1">
+      <c r="I444" s="1" t="n">
         <v>279</v>
       </c>
       <c r="J444" s="7" t="s">
@@ -11135,16 +9654,13 @@
       <c r="K444" s="6" t="s">
         <v>517</v>
       </c>
-      <c r="L444" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="445" ht="53.7">
+    </row>
+    <row r="445" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F445" s="16"/>
       <c r="G445" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I445" s="1">
+      <c r="I445" s="1" t="n">
         <v>280</v>
       </c>
       <c r="J445" s="19" t="s">
@@ -11153,16 +9669,13 @@
       <c r="K445" s="6" t="s">
         <v>519</v>
       </c>
-      <c r="L445" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="446" ht="76.85">
+    </row>
+    <row r="446" customFormat="false" ht="76.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F446" s="16"/>
       <c r="G446" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I446" s="1">
+      <c r="I446" s="1" t="n">
         <v>281</v>
       </c>
       <c r="J446" s="7" t="s">
@@ -11171,21 +9684,18 @@
       <c r="K446" s="6" t="s">
         <v>521</v>
       </c>
-      <c r="L446" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="447" ht="13.8">
+    </row>
+    <row r="447" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F447" s="16"/>
       <c r="J447" s="7"/>
       <c r="K447" s="6"/>
     </row>
-    <row r="448" ht="13.8">
+    <row r="448" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F448" s="16"/>
       <c r="J448" s="7"/>
       <c r="K448" s="6"/>
     </row>
-    <row r="449" ht="12.8">
+    <row r="449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E449" s="1" t="s">
         <v>75</v>
       </c>
@@ -11193,11 +9703,11 @@
       <c r="J449" s="6"/>
       <c r="K449" s="6"/>
     </row>
-    <row r="450" ht="12.8">
+    <row r="450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F450" s="16"/>
       <c r="J450" s="6"/>
     </row>
-    <row r="451" ht="12.8">
+    <row r="451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E451" s="1" t="s">
         <v>76</v>
       </c>
@@ -11205,18 +9715,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I374 I384:I1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I383 I375:I381">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I382">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/kettle.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/kettle.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="kettle" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="kettle" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="733">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -299,12 +299,12 @@
 I did not share her past to speak of tragedies or the villagers' folly.</t>
   </si>
   <si>
-    <t xml:space="preserve">あの日…村を訪れた私を待っていたは、命あるもの全てが死に絶えた凄惨な静寂だった。それが彼女の「力」によるものかはわからない。だが、ロイテル、そして#pc、君たちには覚えておいてほしい。
+    <t xml:space="preserve">あの日…村を訪れた私が見たのは、命あるもの全てが死に絶えた凄惨な光景だった。それが彼女の「力」によるものかはわからない。だが、ロイテル、そして#pc、君たちには覚えておいてほしい。
 あの子は特別な力の元に生まれ、その力は確実に、彼女を取り巻くものたちの運命に影響を与えるだろう。
 もし君たちが望むなら、私とクルイツゥアは出ていくから、いつでも言ってくれ。</t>
   </si>
   <si>
-    <t xml:space="preserve">That day... what awaited me in the village I visited was a horrific silence of death　where every living thing had perished. Whether it was her ‘power’ I cannot say. But, Loytel, and you #pc, remember this. 
+    <t xml:space="preserve">That day... what I saw when I visited the village was a horrific scene of death where every living thing had perished. Whether it was her ‘power’ I cannot say. But, Loytel, and you #pc, remember this. 
 She was born under a peculiar power, and that power will undoubtedly affect the fates of those around her.
 If you ever wish us to leave, just say so.</t>
   </si>
@@ -600,7 +600,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">Their </t>
@@ -1836,7 +1836,7 @@
     <t xml:space="preserve">お、おほん…ということだ、#pcよ。
 この決断は私には荷が重い。お前に任せよう。
 死者の洞窟に赴き、「淀み」を見つけるんだ。そこでイスシズルに渡されたこの瓶を使うか、あるいはファリスさんに渡された「聖水」を使うか…それはお前次第だ、よく考えてくれ。
-…安心しろ、私もついていってやる。お前だけに責任を負わせるのは酷だからな。</t>
+…安心しろ、私もついていってやる。お前だけに責任を追わせるのは酷だからな。</t>
   </si>
   <si>
     <t xml:space="preserve">A-hem... So then, #pc.
@@ -2675,7 +2675,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">…フッ、まあ構いません。どのみち、この場に居る者の大半とは、もう二度と顔を合わせることもないのです。
@@ -2686,7 +2686,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">では、師よ。</t>
@@ -2730,7 +2730,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">…そして、僕にとって好都合とも言えるでしょう。
@@ -2740,7 +2740,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">竜の子と魔女の邂逅が意味するもの、 運命の糸に引かれた冒険者、そして何よりも師よ、魔石の秘密を知ってから、あなたという存在そのものが、僕の好奇心を離さないのです。</t>
@@ -2763,7 +2763,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">見返りか、そうだね、コルゴンがボロボロにした鍋の修理ぐらいは頼ませてもらうとするよ。
@@ -2774,7 +2774,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">そしてソリン、まだ私を師と呼ぶのなら、覚えておくといい。君も…私も、この世界にはまだ多くの学ぶべきことが残っているんだ、どれだけ長生きだろうともね。</t>
@@ -2784,6 +2784,755 @@
     <t xml:space="preserve">Well, I suppose I’ll at least ask you to repair the pots Corgon battered to pieces.
 But regardless, I welcome your stay here. 
 And Sorin, if you still call me your Master, remember. We still have much to learn from this world, however long our lives may be. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">你能听到风在用古老的语言低语吗？我为了学习风的故事，正在游历世界</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我有些问题</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我能帮到你什么吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">关于魔石</t>
+  </si>
+  <si>
+    <t xml:space="preserve">关于复制品贩卖</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(返回)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">帕罗米亚皇家图书馆的古书中，留下了一些关于魔石传承的记述。
+帕罗米亚曾经有三块蕴含着巨大力量的魔石。它们分别是霸者的魔石、贤者的魔石以及愚者的魔石，这些魔石曾给王国带来繁荣，但在扎西姆王的时代，这些魔石被作为保守某个秘密的代价送到了那些最强大最邪恶的存在身边。
+一个给了古代的王族，一个给了钢铁龙，还有一个给了不净的魔法师。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">此后魔石变成了怎样，扎西姆王守护的秘密到底是什么，很多学者和炼金术师们都挑战去阐明真相，但是答案却如同风中沙砾一般难以捉摸。
+也许能够在某一天解开这个谜团的，会是像你这样的冒险者吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">复制品贩卖？　嗯，我这么做是觉得能对你们的冒险活动有帮助。
+古老的炼金术中流传着一种可以复制物质特性的技术。虽然不能说所有的道具都可以进行复制，不过那些你已经制造过的手工道具和种子都可以复制哦。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">如果有想复制的物品，请交给我保管。虽然需要一些时间，但是可以定期的制作复制品。
+对了，可以复制的物品的最多个数和销售个数是根据我商店的规模决定的。虽然这样说也很令人难受，但是如果想要复制更多的物品的话，对我的商店投资就能帮上忙了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你好，罗伊特尔。怎么一副闷闷不乐的表情？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">凯特尔，你的弟子真是个难应付的孩子啊…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">弟子…？ 啊，是说库罗茨亚吗。她不是我的弟子。那孩子讨厌炼金术。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嚯，这又是为什么？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">因为她的母亲是炼金术师。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">库罗茨亚的母亲是我关系很好的朋友。她是一位乡下小村庄里的炼金术师，也是一位热情的研究者。但就像常见情况一样，村民们并不理解她。
+迷信的村民们疏远她，称她为魔女。作为「魔女」之子的库罗茨亚也受到村里孩子们排挤，天生颜色不同的两只眼睛也被人们称为「招来灾难之眼」，被大家所恐惧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">库罗茨亚的母亲因病去世后，她就被寄养在村中的教会，但是她在那里依然受到排挤。后来某一天，为了证明自己的清白，她用自己的手挖出了一只眼睛。
+我去到那个村子的时候，库罗茨亚就在村外的一间破烂小屋的床上，已经奄奄一息了。我用炼金术维系住了她的生命，同时也将我们的命运联结在一起。这就是她和我一直旅行的理由。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…这都是什么事啊。因为眼睛的颜色不同就把人当成魔女，简直愚蠢透顶！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我懂你会感到不平，但话说回来，人身上的一些特征有时也确实是一种与生俱来「力量」的表现呢。
+…我并不是为了讲述悲剧或者讽刺村民的愚蠢才告诉你有关她过去的事情。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那一天…我在抵达村子后所见到的，是所有曾拥有生命的东西全都死绝的凄惨景象。我不清楚那是不是她的「力量」导致的。但是，罗伊特尔，还有#pc，我希望你们能好好记住。
+那孩子于特殊的力量之下诞生，那份力量毫无疑问会影响她周围人的命运。
+如果你们不想让我们留下，那我和库罗茨亚就会马上离开。有这样的想法就随时告诉我吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">凯特尔……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">连一点风都没有，真是个安静到让人不舒服的夜晚。你在那里吗，迪米塔斯？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哼…果然躲不过汝。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">汝依然如往昔一般，埃鲁丁…至少在外貌上如此。
+即便我如今沦为如此存在，与汝交谈时，仍会忆起我人类时的样子。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当你还是人的时候，原来如此，呵呵…
+你从以前开始，遇到任何事就都会参一脚。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">夜夜在我的伙伴周围徘徊，散布奇怪故事，这确实是你的作风。
+…可你这是为了什么呢？竟会对那个女孩那么在意。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呵呵…不过是有点关心罢了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那女孩极为危险。汝也知道，她的瞳中寄宿着什么。
+灾眼乃是石之容器……而此时此刻，幼龙体内沉睡的魔石，也在渴求着那个容器。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">迪米塔斯，谢谢你的关心。但是，只要我还在这里，魔石就不会觉醒。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">原来如此，若是「最初的炼金术士」这样说，那便不会有错。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呵呵呵…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…尽管如此，埃鲁丁，命运依然会造访库罗茨亚与歌罗贡。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">龙之子与人类一同生活的传闻迟早会被人们知晓。或许常人不敢冒犯龙族……但唯有一人例外。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那人知晓魔石于扎西姆王的时代被送至钢铁龙手中，龙死后，他便虎视眈眈地寻找着那颗遗失魔石的下落。
+若那人听到龙之子的传闻，定不会不为所动。
+那人必将以魔石为目的，寻找库罗茨亚和歌罗贡。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">……伊斯西泽尔</t>
+  </si>
+  <si>
+    <t xml:space="preserve">没错，暗之畸形「伊斯西泽尔」。
+曾以伟大的魔法师之名享誉各地，却因对魔石着魔，变成了身陷黑暗之中的不洁怪物……他亦是汝无法杀之，也无法救之的可怜弟子。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">汝打算如何处理这个女孩？
+是想看她也沦为魔石的囚徒，还是看她被那人利用，又或是被杀呢……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不要逃避现实，「凯特尔」。
+那女孩无法获得救赎。汝正试图重蹈覆辙。而汝的软弱，必将再次给这个世界带来灾难。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">能稍微占用大家点时间吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">姆啾？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">怎么了凯特尔？在这么晚的时候找我们。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">其实我们正面临着一些危险。
+有些事想让你们知道。关于曾是我弟子的那个男人，伊斯西泽尔的事，以及库罗茨亚眼中潜藏的力量的事…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嗯…。这可真是错综复杂啊。
+库罗茨亚体内流淌着古代魔女的血脉…然后，歌罗贡小小的身体里竟然有魔石…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">凯特尔先生，如果真的如您所说，伊斯西泽尔是冲着魔石来的…那我们现在就应该为保护库罗茨亚和歌罗贡做些相应的准备了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">又是你啊…有什么好笑的？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那位女孩与龙之子的安全不是问题。
+这世界本身，已然显露出末日的征兆，他们的存在即为象征。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这是什么意思，迪米塔斯先生？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这些家伙…「古老的存在」们只会给这个世界带来灾难和停滞。像他们那样强大的存在会滋生歪曲，其光辉会将周围的一切都卷入并焚烧殆尽。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">吾等所创造、在乎的一切，皆会被他们的法则轻易践踏，无论那是不是他们想要的。吾等皆为在恐惧中窥望命运的人偶。这样的世界，有何发展可言？
+众神因此停止干涉人类，并离开了这片大地。神之子…神所创造的古老存在亦应当效仿。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…呃？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…即是说，无论伊斯西泽尔，龙亦或是魔女，这些碍事之物唯有被消灭掉才对这个世界好。
+凯特尔，可曾忘记汝之仁慈所引发的灾祸？汝本应杀死伊斯西泽尔。而如今，汝亦当杀死这位女孩与龙之子。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">喂喂喂，这是说到哪去了。这话可我可不能当没听到。
+你当自己是什么人？就想决定这些孩子的生死？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">库罗茨亚极其危险。汝当深知此事。此女的灾厄之眼，已将一村覆灭。而且其力量尚未「觉醒」。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">但是引起这件事的契机是什么？是把库罗茨亚逼迫到绝境的迷信村民们吧？
+这孩子对自己的力量根本一无所知。因此受到谴责就更不应该了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那么，是要因为怜悯那女孩，任由这世界灭亡也无妨？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这，这个嘛…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…我才不在乎。如果这个世界如此不通情理，否定库罗茨亚存在，那它毁灭了才好。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">姆啾！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">法…法莉斯小姐，这么说就太过分了…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不，罗伊特尔大人。库罗茨亚是我们重要的伙伴。为了保护她我什么都愿意做。就算要对抗这个世界的天意。
+…这是理所当然的吧，罗伊特尔大人？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当然了！
+不，应该说是你让我再次看清了一切，法莉斯小姐。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我并不关心这个世界怎样。
+库罗茨亚的命运由库罗茨亚自身来决定。我不会让任何人说三道四，我会从伊斯西泽尔这些家伙的手中保护他们。
+仅此而已。这都是理所当然的。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">至于迪米塔斯说的「古老的存在」什么的，我觉得伊斯西泽尔那种危险的家伙也是不能跟库罗茨亚他们相提并论的。
+他们可是会互相叫着「妈…妈…」「歌罗贡♪」在一起腻腻歪歪一整天的，有哪个危险的古老存在会这样？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">法莉斯…罗伊特尔…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">任由感情驱使，不明事理的愚钝之人…如此定论，只会让同样的错误再次重演。
+汝等不知，那种无法拯救，亦无法毁灭的苦痛。汝等的仁慈，终将为此女带来更大的悲哀！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">迪米塔斯…难道说，你还在为特蕾西亚的事情…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">特蕾西亚…？ 呵…是吗，呵呵呵…原来如此。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呵呵…原来是在此女身上看到她的影子…真不像我会做的事…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…算了，我们互相还不够了解呢。但是这点可以靠时间可以解决。
+当务之急是要大家共同努力，想想把伊斯西泽尔赶走的方法。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我赞成，罗伊特尔。关于这点，我也有些想法。
+…但是，今天就到此为止吧。已经快天亮了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哼，真是的，为了这种理所当然的结论，居然消耗了一整晚的时间。
+#pc，你听到了么？ 接下来要有的忙了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…索林，是你吗？自从和你最后一次见面，已经不知过了多少岁月。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你还记得我吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（无法听懂的古代语言）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真令我意外。就是说，你依然…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你在等着…我？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哼，这样就差不多了吧。我已经好久没以这个样子示人了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">如何，用现在的样子我们就能更方便地对话了吧，老师？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">知道你还记得自己以前的样子，让我放心多了，索林。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真是讽刺。无论我是否记得自己从前的样子，我都从未拥有过你所期待的人性。
+…无所谓了。我可不想给时隔二百年的再会泼冷水。就像以前一样在这个昏暗的房间里聊聊…关于「魔石」的事吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">看起来，我的到来和我的来意，都早被你看穿了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…钢铁龙「歌罗贡」。过去被帕罗米亚王授予魔石的伟大之龙，在二十年前被屠龙者「托兰」消灭。但是愚蠢的托兰并没有带回魔石，后来魔石的下落便不知所踪。
+…直到最近，你们找到了歌罗贡的遗孤。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">听到龙之子传闻的那天，我就找到了它。这对我来说易如反掌。原本我只需杀了龙之子，再夺取魔石即可。然而，我却看到了在龙之子身旁的你。
+于是，我就在这个城里等着你的到来。我知道，如果是你的话一定会来这里。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好了，说来听听吧，老师。你对那个龙之子…还有龙体内的魔石到底有何打算？
+你早在几百年前就同意了我的计划。难道这期间有什么让你改变了心意？　毕竟你没有带龙之子来见我，也就是说你已经不打算继续协助我了吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">正如你所说，我不能交出歌罗贡。在我说出理由前，有一件事我要问你，索林。你还在继续研究魔石吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哼，那是当然的。灵魂被束缚在腐臭的躯体里，还要背上暗之畸形这样忌讳的名号在朽烂阴暗的古城中生活，难道我甘愿这样还能是有什么其他理由？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我必须揭开魔石的秘密。
+…诸神离去，神秘正从这个世界中逐渐消失。「古老的存在」也都在缓缓地步入衰亡。这一切都意味着魔法的终结。
+没错，我是必须得到魔石。让这个世界继续存在下去，依靠魔石的力量，将诸神再度呼唤回大地。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">如你所知，如今的世界，无论是「古老的存在」们，还是神秘的根源——魔法，都在无声地消失。
+我不清楚这一切消亡的终点是会在百年后还是千年后。但是自从诸神离开之后，这个结果就已经是我们无法逃离的宿命了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">正是如此…这样下去再过不久神话就会变成睡前讲的陈年故事，元素精灵也将不复存在，变成只能从书中插画才看得到的东西。
+但是，你有没有这样想过，也许这才是世界回到了原本的样子？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">原本那个无聊、野蛮、连生存价值都没有的世界吗？
+…你所说的这种变化如今已经有所预示了。曾席卷整个西埃尔·泰尔的古代艾沃达纳失去了昔日的荣光，倒是在东方出现了一支以科学为势的新王国耶鲁正在日益兴盛。魔法正在被降格为单纯的学问，古老的种族大多都面临被人类灭亡或奴役的命运。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是的，人的时代正在到来。而且，如果回顾这个星球的整个历史你就会明白…正如艾斯·泰尔或是莱姆·伊德的下场一样，人类迟早会仓促地走向灭亡之路。而他们甚至不会理解自己夺走和破坏之物的价值。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">无论什么文明，终结都不可避免。然而有毁灭，就会有新生。你不觉得这才是超越了我们善恶观的真理吗，索林？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哼，这话题就到此为止吧，别再拐弯抹角了。
+人类的盛衰，善恶…这些都是该诸神去考虑的事情，与我无关。我只是不想失去我的力量。能够摆布世界的魔法之力就是我的一切。我无论如何都不能容忍它被夺走。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…老师啊，二百年前，你为什么没有杀我呢？　我还以为我们是坐在同一条船上。
+难道说你来这座城堡，是为了弥补二百年前没有对我下手的遗憾吗？　可惜我的力量早已今非昔比，也远远超过了你。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">魔石是原初时代众神所创之物…只要解析它的力量，就能将诸神重新唤回大地，阻止这个世界的「退化」。
+…我要杀了龙之子得到魔石。就算你想阻止也是徒劳的。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">索林，你误会一件事情。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">误会…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你的魔石研究，已经完成了。你恐怕已经把魔石的力量「全部激发出来了」。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">研究已经完成？　开什么玩笑。魔石之力岂会仅有如此程度…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你已经掌握了魔石的力量。但是…没错，正如你所察觉的那样，很遗憾，那个魔石…不，就算你拿到另外两个魔石，也远远无法达到你所期望的力量。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哼，还以为你要说什么…老师啊，连魔石都没有的你究竟懂什么？
+确实，你对魔石的研究之深令人匪夷所思，但那都是陈年旧事了。如今的你的知识不可能比得过在这件事上倾注了二百年时间的我。
+魔石蕴藏的力量，可以打开众神领域的大门，把众神唤回大地…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…如果是真正的魔石，那或许可以。但是，你所拥有的不过是魔石的伪造品。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真是胡说八道…呵呵，你就是为了说这种蠢话才特意来找我的？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">索林，你的魔石，是我做的。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">老师啊，你是什么时候学会说这种笑话的…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你不信吗…也难怪。
+那就来看看我的眼睛吧，索林。看看我眼中被刻下的永恒的诅咒。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你一定听说过《奥拉的石晶》的传说吧，这才是真正的魔石啊，索林。
+你和歌罗贡手中魔石，不过是很久以前，我模仿石晶制作的仿品。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不可能…《奥拉的石晶》…永恒之瞳…？　那只是神话故事里的…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神话……　是…是…真的…？　是吗，是这样啊…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呵呵…呵呵呵…我竟然也会犯下这种错…原来如此，原来是这样啊…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「最初的炼金术师」…。这样啊，你才是一切的起点。
+人类在这个时代发出第一声啼哭时，你就已经活着了。不，应该说是没能死成吧。现在我明白了。你眼睛的秘密，还有你没有杀我的理由。
+呼，请坐吧，老师。我们似乎还有很多话要说。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那么，那个传说就应该是真的了。
+…她还身为森林的精灵时的名字是奥拉。
+爱上了人类男子，将自己囚禁在石棺中的她，最终与向往天空的雏鸟一起展翅高飞，升格为了女神。没错，这就是璐璐薇诞生的神话。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">虽然这段神话很有名，但几乎没有记录有关那人类男子之后命运的书籍留存下来。
+有一种说法是，奥拉…不对，是璐璐薇。为了把自己曾倾心于人类这件事当作教训，就给予了那男人残酷的命运。为了让那男人再也看不到她的身影，她夺走了他的双眼，还对他施加了不死的诅咒。因为她知道那个男人今后也会爱着自己，所以这样就可以让他承受永远的痛苦。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…女神璐璐薇诞生于上古时代，那是被人们称作「起源的时代」的第二纪。那之后到底是经过了多少的岁月？　数千万年，不，数亿年…？
+哼哼，真没想到…老师啊，也不知这世界上无数的秘密还会有多少与你有关？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">可以确定的是，那都不会是让人羡慕的经历。
+那传说毫无疑问也是我本人写的，但流传至今会不会出现偏差就另当别论了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">没错，我在那片森林里…「偶然」遇见了已经成为女神的她。
+当她转向我的瞬间，我的眼睛就被刻上了这石晶。感情也好，言语也罢，什么都没有了。在那以后，我曾在永恒的黑暗中追寻过她的声音，她却再也没有在我面前出现过。
+这眼睛，也算不上什么惩罚，只是她随性而起的决定罢了。对于已经成为女神的璐璐薇，我不过是风中的一粒尘埃，根本不是什么值得让她留意的东西。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…话虽如此，这双眼睛却成了我与璐璐薇唯一的联系。只要解开这双眼睛的秘密，或许就能再一次得到她的垂怜。我就是怀揣着这份微弱的希望，开始不分昼夜地探寻晶石的秘密，也是这份热忱最终驱使我踏上了仿造晶石的道路。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不知不觉中我就被称为了伟大的炼金术师。但是人的智慧还是难以企及神的奇迹。我创造的无数魔石中没有一个能拥有和这双眼一样的力量。
+…最终我放弃了，赝品的魔石也被埋藏进了历史的尘埃之中。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…然而，你所创造的那三块魔石却在经过漫长时间的考验后又出现在了这个时代。是这样吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…嗯，没错。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你在得知弟子拿到魔石，成了那股力量的俘虏时，就来到了我所在的城堡。你一向对弟子关爱有加，所以你是为了拯救我的灵魂，来杀我的。
+但当你知道我的计划时…你犹豫了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你想到如果把我强大的魔力与魔石结合起来，也许真的可以把众神唤回大地。
+这样一来或许你就能和璐璐薇重逢，好知晓你眼中诅咒的真正含义。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…这双眼睛的含义吗。其实这件事已经无所谓了。
+索林，我只是想再见一次璐璐薇。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呵呵，呵呵呵…老师啊，看来你我之间终于能找到一个共同点了。
+在你内心的深处，也有一股理性和道德都无法压制的黑暗火焰在燃烧着。你和我一样，都有着无论这个世界变得怎样也没法放下的强烈愿望。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…而成为你这股黑暗热情牺牲品的，就是我的身体吗。
+让我变成污秽的怪物，去渴求伪造的魔石。这可真是…太好笑了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…抱歉，索林。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不，老师。
+…讽刺的是，这污秽的身体除了延长了我可悲的生命之外，也还是有点别的用处的。
+倒不如说在魔石研究之路被断绝的现在，靠这幅身体所得到的知识才成了我最后的希望。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你是什么意思，索林？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">死者的世界里，是有活人无从知晓的秘密的。
+但在谈论这秘密之前，有一件事情我们必须说清楚。即使夺取龙之子的假魔石对我而言几乎没有意义…但也只是「几乎」而已。多拿一块魔石对我是没有坏处的。
+毕竟交涉筹码还是在拥有夺取魔石力量的我手中。 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">你的意思是…有事情想让我做吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你如此通情达理真是太好了。其实也没什么，只是想让你帮忙做一件小事。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在离这座古城稍有距离的沼泽地里，有一个无人靠近的洞窟。在那个被称为「死者的洞窟」之处的深处，有着被死者守护，但死者无法接近的「黑潭」。
+…拿好这个瓶子。
+我希望你把这个瓶子里的液体滴一滴到那个「黑潭」里。
+…怎么样，很简单吧？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当然，要进入死者洞窟的深层也需要相当的实力。和跟你在一起的冒险者商量一下就好了吧。
+呵呵，你看起来一脸诧异呢…但我不会告诉你更多的秘密了。
+那一滴显现效果只会是在几百年后了。至少我可以保证这件事绝对不会危害到你的同伴。我认为用这件事换来龙之子的性命还是很划算的，你觉得呢，老师？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">啊…是凯特尔。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">欢迎回来，凯特尔！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我回来了，库罗茨亚，歌罗贡。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">闷闷不乐的表情呢…怎么了？　果然是…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不是的，不是坏消息。只是…
+是啊，首先，能叫大家来吗，库罗茨亚？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">姆啾…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…事情就是这样了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">原来如此，作为保证歌罗贡安全的交换条件，要向那个「黑潭」里面滴一滴液体吗。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嗯…探索洞窟时肯定少不了#pc的帮助。不过也就是滴一滴液体而已，好像也没什么危险，这听起来是笔不错的买卖？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不行。绝对不能把那瓶子里的液体和「黑潭」混合！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">可是，法莉斯小姐…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不，听我说，罗伊特尔大人。我觉得这事情没有那么简单，甚至可能有邪恶的阴谋。
+关于死者的洞窟，其实流传着这样一种传说。
+那洞窟中曾有一个「污秽不净之人」，在里面不断重复着令人毛骨悚然的可怕仪式。尽管足以威胁大地与天界的异形最终被诸神消灭了，但污秽不净之人的血肉却溶入了洞窟的最深处，变成了绝对不会干涸的黑色淤积物。
+罗伊特尔大人，那「黑潭」是凡人绝不能接触的东西。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">原来如此，真是可怕的传说…等等，原来是这样，我懂了。
+将瓶中的东西滴一滴到淤积物里，在数百年后让邪恶发芽…一个连众神都无法忽视的邪恶…就能成为让众神回归地上的诱饵。这一定就是他的打算吧。
+确实，如果听了伊斯西泽尔的要求，肯定会给后世留下不得了的诅咒之物。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">可…按照凯特尔所说的，伊斯西泽尔是十分强大的魔法师。如果我们拒绝了这笔交易，光靠自己的力量能从他手中守住这只小不点龙么？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不是的，不需要拒绝这笔交易。我有一样东西，罗伊特尔大人。
+就拿这个瓶子代替吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">代替？　这是哪来的瓶子？　确实很像伊斯西泽尔交给我们的瓶子…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嗯…但是，这个瓶子里是股清爽的香味。里面装的是哪种圣水吗？
+我懂了，你是想利用圣水把「黑潭」净化掉吗。不愧是法莉斯小姐…可是这样的东西到底是哪里来的？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不过…这味道还真是让人舒服。清香又清爽，…对了，简直就像刚洗好的…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">难道说这里面是…呃，算了，刨根问底就有点不识趣了。我觉得这主意不错，法莉斯小姐。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">至少，这瓶子里的一滴液体不至于把邪神唤回这个世界。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是…是啊。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嗯，咳咳…事情就是这样了，#pc。  
+这个决断对我而言太沉重了，还是交给你吧。
+前往死者的洞窟，找到「黑潭」。至于在那里是用伊斯西泽尔的瓶子，还是用法莉斯小姐交给我们的「圣水」…就看你的了。
+…不过放心吧，我也和你一起去。让你独自承担责任也太残酷了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这就是「黑潭」吗。
+漆黑又浑浊…只是凝视着就仿佛要被吞噬一样。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真是个恶心的地方。办完伊斯西泽尔的事，就早点离开吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这点我完全赞同。
+向这「黑潭」滴下一滴液体…简单的工作。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那么，#pc，要用哪个瓶子呢？是伊斯西泽尔给的那个可疑的瓶子，还是法莉斯小姐特制的洗…圣水呢。
+（…喂，#pc，听得到吗？）
+（法莉斯小姐虽然也跟来了，不过放心吧，不管你怎么选，我都不会让她知道的。我尊重你的决定。）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">使用伊斯西泽尔的瓶子</t>
+  </si>
+  <si>
+    <t xml:space="preserve">使用法莉斯的瓶子</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…伊斯西泽尔的瓶子没错吧？
+这污秽至极的气味。恐怕只要一滴，就能孕育出邪恶之物。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是的</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不是</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…法莉斯小姐的瓶子没错吧？
+十分…好闻的味道。只是很难想象这一滴下去会发生什么啊。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好了。那么我就把这瓶子里的液体滴一滴到「黑潭」里吧。
+不，#pc，这里就交给我吧。不能把重担压在你一个人身上。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…一想到这一滴或许会改变世界的命运，就让人感到窒息。
+而且这地板好像变得…有点黏糊糊的…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">啊！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">冷、冷静点，我没事！
+…呼，全身都湿透了，真恶心啊，还好这「黑潭」没有多深。
+哈啊…瓶子…那两个瓶子去哪里了？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…罗伊特尔大人…！！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">法莉斯小姐，冷静点…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">后面，你后面！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">什么…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">虽然我根本不知道它在说什么，但是看上去相当生气啊。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哦哦…污秽不净之人安茨拉西祖鲁…曾令世间陷入恐惧，被众神封印的邪神…！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…这个「黑潭」的真面目，就是迟早萌芽的灾厄之种吗。正好，这种东西，就该趁现在彻底斩草除根。
+呼，就算是邪神，在那清新的香气下也无法发挥全部力量。
+来吧，#pc，接下来就交给你了！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哦哦，做得好，#pc！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">干得漂亮，#player大人。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在那怪物出来的时候，我还以为完蛋了呢…嗯，不过最终还是船到桥头自然直。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">伊斯西泽尔这家伙…真是个疯子。居然为了自己的野心，打算在将来放这样的家伙出来。
+可是这下麻烦了啊。这样一来我们就无法实现和他的约定了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我们什么都没看到，这里什么都没发生…没错吧，罗伊特尔大人？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…嗯。虽然我觉得他不会这么轻易就相信，但也没别的办法了。
+好了，总之我们先回到据点，等待伊斯西泽尔吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">凯特尔…有时间吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">怎么了，库罗茨亚？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">刚才有个我们没见过的黑袍男孩，他一直盯着我和歌罗贡看。正打算和他搭话的时候，迪米塔斯突然气势汹汹地插了进来，和他吵了起来…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…是吗，我也觉得他差不多该出现了呢。
+那个穿黑袍的叫索林，是伊斯西泽尔的人类形态。迪米塔斯和他在过去曾有些因缘。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那孩子是…伊斯西泽尔？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">没什么好怕的，库罗茨亚。我们在死者的洞窟已经完成了与他的约定。
+没错吧，罗伊特尔？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…那个，凯特尔…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">怎么了？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">没、没什么，确实危险已经过去了…不过以防万一还是问一下。如果伊斯西泽尔发怒的话…会发生什么？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">像他这样的魔法师，如果有那个意愿，力量足以轻松毁灭一个国家。他应该是这个时代里，我们最不该去惹怒的一个人了。
+但是，不用担心，罗伊特尔。要说为什么的话，呵呵，如果你做了什么「让他发怒」的事情的话，你早就已经在地下长眠了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…哈…哈哈哈，这样啊…！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（交头接耳）法莉斯小姐，「黑潭」发生的事情，绝对不能让他知道。凯特尔都开始起疑心了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（交头接耳）好的，罗伊特尔大人…不能把它编成歌曲真是遗憾，但这次也是不得已了啊。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…好了，迪米塔斯这会儿应该也冷静下来了。我们去听听他要说什么吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…那么，可以认为约定已经顺利完成了吧？
+没事，只是确认下而已。对「黑潭」的干涉，我也能立刻感受到。只是…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">只是…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">只是从那时起，我就失去了部分魔力。准确来说，我失去了「伊斯西泽尔」的不死之躯。
+哼，当然，这也意味着「黑潭」再次开始活动，无疑是令我欣喜的证据。
+无须担心。只要「黑潭」中那位的力量增长，我的魔力也会随之恢复。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你失去了魔力吗？　真是太好…不对，真是灾难啊！
+那么，歌罗贡和库罗茨亚已经不会再面临危险了吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…老师啊，为了让这里的这群愚钝之人也能理解，您最好还是好好教教他们。对魔法师而言，话语是多么沉重的东西。
+我决定遵守约定。即便我现在依然留有足够的魔力，可以仅因那个男人触怒了我而将此地化为地狱。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…哼，也罢。 反正我与大多数在场者，今后都不会再相见了。 
+看到了龙与魔女这种稀罕物，和老朋友来了场充实又融洽的交流，看来是不虚此行了。
+那么再会了，老师。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…索林，你真的打算以这样的身体返回那古城吗？
+我并无恶意，之前拜访的时候，那里看起来可不像是「人类」能够放松休息的地方啊。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呵呵，别摆出那么可怕的表情啦。我换个说法吧。
+为什么不在你的魔力恢复之前，试着在这里生活呢，索林？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（嘶…）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这可真是…意外的邀请啊，老师。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…而这对我来说也很有利。
+龙之子与魔女邂逅的意义， 被命运之线所牵引的冒险者，还有最重要的是，老师，在知晓了魔石的秘密后，对于你这个存在本身，我实在难以放下好奇心啊。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当然，我不打算免费住下。
+你希望从我这里得到什么作为回报呢？ 是失落的上古魔法书，长生不老的灵药，还是说，想要制造一批不眠不休能一直劳作的死者军团呢？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">回报吗，对了，被歌罗贡弄坏的锅就拜托你修理吧。
+不过首先，还是要欢迎你的留宿。
+还有索林，如果你还称呼我为老师的话，就记住一点。不管是你也好…我也好，无论我们活了多久，在这世上都仍有很多需要学习的事物。</t>
   </si>
 </sst>
 </file>
@@ -2805,25 +3554,25 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -2837,7 +3586,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -2902,7 +3651,7 @@
     <font>
       <sz val="10"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -2921,7 +3670,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -2930,110 +3679,110 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3047,13 +3796,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -3229,26 +3978,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:IX451"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="60.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="62.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.06"/>
+    <col min="1" max="1" width="8.85" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.28" style="1" customWidth="1"/>
+    <col min="4" max="5" width="11.85" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
+    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
+    <col min="10" max="10" width="60.76" style="1" customWidth="1"/>
+    <col min="11" max="11" width="62.33" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.06" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3286,24 +4035,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I2" s="1" t="n">
-        <f aca="false">MAX(I4:I1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="I2" s="1">
+        <f>MAX(I4:I1048576)</f>
         <v>281</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.8">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I8" s="1" t="n">
+    <row r="8" ht="13.8">
+      <c r="I8" s="1">
         <v>1</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -3312,12 +4061,15 @@
       <c r="K8" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L8" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="9" ht="12.8">
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="12.8">
       <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
@@ -3327,7 +4079,7 @@
       <c r="E10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="1" t="n">
+      <c r="I10" s="1">
         <v>2</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -3336,8 +4088,11 @@
       <c r="K10" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L10" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="11" ht="12.8">
       <c r="E11" s="1" t="s">
         <v>21</v>
       </c>
@@ -3345,21 +4100,21 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="12.8">
       <c r="E12" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="12.8">
       <c r="E13" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="12.8">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I15" s="1" t="n">
+      <c r="I15" s="1">
         <v>3</v>
       </c>
       <c r="J15" s="1" t="s">
@@ -3368,15 +4123,18 @@
       <c r="K15" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L15" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="16" ht="12.8">
       <c r="B16" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="1" t="n">
+      <c r="I16" s="1">
         <v>4</v>
       </c>
       <c r="J16" s="1" t="s">
@@ -3385,8 +4143,11 @@
       <c r="K16" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L16" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="17" ht="12.8">
       <c r="B17" s="1" t="s">
         <v>30</v>
       </c>
@@ -3396,7 +4157,7 @@
       <c r="E17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I17" s="1" t="n">
+      <c r="I17" s="1">
         <v>21</v>
       </c>
       <c r="J17" s="1" t="s">
@@ -3405,15 +4166,18 @@
       <c r="K17" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L17" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="18" ht="12.8">
       <c r="B18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I18" s="1" t="n">
+      <c r="I18" s="1">
         <v>5</v>
       </c>
       <c r="J18" s="1" t="s">
@@ -3422,8 +4186,11 @@
       <c r="K18" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L18" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="19" ht="12.8">
       <c r="B19" s="1" t="s">
         <v>13</v>
       </c>
@@ -3431,13 +4198,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" ht="12.8">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I22" s="1" t="n">
+    <row r="22" ht="116.4">
+      <c r="I22" s="1">
         <v>6</v>
       </c>
       <c r="J22" s="5" t="s">
@@ -3446,9 +4213,12 @@
       <c r="K22" s="6" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I23" s="1" t="n">
+      <c r="L22" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="23" ht="74.6">
+      <c r="I23" s="1">
         <v>7</v>
       </c>
       <c r="J23" s="7" t="s">
@@ -3457,19 +4227,22 @@
       <c r="K23" s="6" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L23" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="24" ht="12.8">
       <c r="B24" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" ht="12.8">
       <c r="A26" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I27" s="1" t="n">
+    <row r="27" ht="64.15">
+      <c r="I27" s="1">
         <v>22</v>
       </c>
       <c r="J27" s="6" t="s">
@@ -3478,9 +4251,12 @@
       <c r="K27" s="6" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I28" s="1" t="n">
+      <c r="L27" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="28" ht="64.15">
+      <c r="I28" s="1">
         <v>23</v>
       </c>
       <c r="J28" s="6" t="s">
@@ -3489,18 +4265,21 @@
       <c r="K28" s="6" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L28" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="29" ht="12.8">
       <c r="B29" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" ht="12.8">
       <c r="A31" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" ht="12.8">
       <c r="E32" s="1" t="s">
         <v>46</v>
       </c>
@@ -3508,7 +4287,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" ht="12.8">
       <c r="E33" s="1" t="s">
         <v>48</v>
       </c>
@@ -3516,8 +4295,8 @@
         <v>49</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I34" s="1" t="n">
+    <row r="34" ht="13.8">
+      <c r="I34" s="1">
         <v>10</v>
       </c>
       <c r="J34" s="7" t="s">
@@ -3526,12 +4305,15 @@
       <c r="K34" s="9" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L34" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="35" ht="13.8">
       <c r="G35" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I35" s="1" t="n">
+      <c r="I35" s="1">
         <v>11</v>
       </c>
       <c r="J35" s="7" t="s">
@@ -3540,9 +4322,12 @@
       <c r="K35" s="9" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I36" s="1" t="n">
+      <c r="L35" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="36" ht="23.85">
+      <c r="I36" s="1">
         <v>12</v>
       </c>
       <c r="J36" s="7" t="s">
@@ -3551,12 +4336,15 @@
       <c r="K36" s="9" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L36" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="37" ht="13.8">
       <c r="G37" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I37" s="1" t="n">
+      <c r="I37" s="1">
         <v>13</v>
       </c>
       <c r="J37" s="7" t="s">
@@ -3565,9 +4353,12 @@
       <c r="K37" s="9" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I38" s="1" t="n">
+      <c r="L37" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="38" ht="13.8">
+      <c r="I38" s="1">
         <v>14</v>
       </c>
       <c r="J38" s="7" t="s">
@@ -3576,12 +4367,15 @@
       <c r="K38" s="9" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L38" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="39" ht="13.8">
       <c r="G39" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I39" s="1" t="n">
+      <c r="I39" s="1">
         <v>15</v>
       </c>
       <c r="J39" s="7" t="s">
@@ -3590,19 +4384,22 @@
       <c r="K39" s="9" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L39" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40" ht="13.8">
       <c r="E40" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F40" s="1" t="n">
+      <c r="F40" s="1">
         <v>58</v>
       </c>
       <c r="J40" s="7"/>
       <c r="K40" s="4"/>
     </row>
-    <row r="41" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I41" s="1" t="n">
+    <row r="41" ht="79.85">
+      <c r="I41" s="1">
         <v>16</v>
       </c>
       <c r="J41" s="7" t="s">
@@ -3611,9 +4408,12 @@
       <c r="K41" s="6" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I42" s="1" t="n">
+      <c r="L41" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="42" ht="91">
+      <c r="I42" s="1">
         <v>17</v>
       </c>
       <c r="J42" s="7" t="s">
@@ -3622,12 +4422,15 @@
       <c r="K42" s="6" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L42" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="43" ht="23.85">
       <c r="G43" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I43" s="1" t="n">
+      <c r="I43" s="1">
         <v>18</v>
       </c>
       <c r="J43" s="7" t="s">
@@ -3636,9 +4439,12 @@
       <c r="K43" s="9" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I44" s="1" t="n">
+      <c r="L43" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="44" ht="57.45">
+      <c r="I44" s="1">
         <v>19</v>
       </c>
       <c r="J44" s="7" t="s">
@@ -3647,9 +4453,12 @@
       <c r="K44" s="6" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I45" s="1" t="n">
+      <c r="L44" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="45" ht="102.2">
+      <c r="I45" s="1">
         <v>88</v>
       </c>
       <c r="J45" s="7" t="s">
@@ -3658,13 +4467,16 @@
       <c r="K45" s="6" t="s">
         <v>72</v>
       </c>
+      <c r="L45" t="s">
+        <v>542</v>
+      </c>
       <c r="M45" s="1"/>
     </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" ht="13.8">
       <c r="G46" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I46" s="1" t="n">
+      <c r="I46" s="1">
         <v>20</v>
       </c>
       <c r="J46" s="7" t="s">
@@ -3673,23 +4485,26 @@
       <c r="K46" s="6" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L46" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="47" ht="12.8">
       <c r="E47" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" ht="12.8">
       <c r="E48" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" ht="12.8">
       <c r="A50" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" ht="12.8">
       <c r="E51" s="1" t="s">
         <v>46</v>
       </c>
@@ -3697,7 +4512,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" ht="12.8">
       <c r="E52" s="1" t="s">
         <v>48</v>
       </c>
@@ -3705,7 +4520,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="53" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" s="1" customFormat="1" ht="12.8">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -3722,7 +4537,7 @@
       <c r="K53" s="6"/>
       <c r="L53" s="6"/>
     </row>
-    <row r="54" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" s="1" customFormat="1" ht="12.8">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -3730,7 +4545,7 @@
       <c r="E54" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F54" s="6" t="n">
+      <c r="F54" s="6">
         <v>2</v>
       </c>
       <c r="G54" s="6"/>
@@ -3739,7 +4554,7 @@
       <c r="K54" s="6"/>
       <c r="L54" s="6"/>
     </row>
-    <row r="55" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" s="1" customFormat="1" ht="12.8">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -3756,7 +4571,7 @@
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>
     </row>
-    <row r="56" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" s="1" customFormat="1" ht="12.8">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -3773,7 +4588,7 @@
       <c r="K56" s="6"/>
       <c r="L56" s="6"/>
     </row>
-    <row r="57" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" s="1" customFormat="1" ht="12.8">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -3781,7 +4596,7 @@
       <c r="E57" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F57" s="6" t="n">
+      <c r="F57" s="6">
         <v>2</v>
       </c>
       <c r="G57" s="6"/>
@@ -3790,8 +4605,8 @@
       <c r="K57" s="6"/>
       <c r="L57" s="6"/>
     </row>
-    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I59" s="1" t="n">
+    <row r="59" ht="23.85">
+      <c r="I59" s="1">
         <v>24</v>
       </c>
       <c r="J59" s="7" t="s">
@@ -3800,12 +4615,15 @@
       <c r="K59" s="9" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L59" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="60" ht="13.8">
       <c r="G60" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I60" s="1" t="n">
+      <c r="I60" s="1">
         <v>25</v>
       </c>
       <c r="J60" s="7" t="s">
@@ -3814,12 +4632,15 @@
       <c r="K60" s="9" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="61" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L60" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="61" ht="46.25">
       <c r="G61" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I61" s="1" t="n">
+      <c r="I61" s="1">
         <v>26</v>
       </c>
       <c r="J61" s="7" t="s">
@@ -3828,9 +4649,12 @@
       <c r="K61" s="9" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I62" s="1" t="n">
+      <c r="L61" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="62" ht="35.05">
+      <c r="I62" s="1">
         <v>27</v>
       </c>
       <c r="J62" s="7" t="s">
@@ -3839,9 +4663,12 @@
       <c r="K62" s="9" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="63" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I63" s="1" t="n">
+      <c r="L62" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="63" ht="46.25">
+      <c r="I63" s="1">
         <v>28</v>
       </c>
       <c r="J63" s="7" t="s">
@@ -3850,12 +4677,15 @@
       <c r="K63" s="9" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L63" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="64" ht="13.8">
       <c r="G64" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I64" s="1" t="n">
+      <c r="I64" s="1">
         <v>29</v>
       </c>
       <c r="J64" s="7" t="s">
@@ -3864,18 +4694,21 @@
       <c r="K64" s="9" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L64" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="65" ht="13.8">
       <c r="E65" s="6"/>
       <c r="F65" s="10"/>
       <c r="J65" s="7"/>
       <c r="K65" s="9"/>
     </row>
-    <row r="66" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" ht="57.45">
       <c r="G66" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I66" s="1" t="n">
+      <c r="I66" s="1">
         <v>30</v>
       </c>
       <c r="J66" s="7" t="s">
@@ -3884,11 +4717,14 @@
       <c r="K66" s="9" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L66" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="67" ht="23.85">
       <c r="E67" s="6"/>
       <c r="F67" s="10"/>
-      <c r="I67" s="1" t="n">
+      <c r="I67" s="1">
         <v>31</v>
       </c>
       <c r="J67" s="7" t="s">
@@ -3897,8 +4733,11 @@
       <c r="K67" s="9" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L67" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="68" ht="13.8">
       <c r="E68" s="6" t="s">
         <v>79</v>
       </c>
@@ -3908,15 +4747,15 @@
       <c r="J68" s="7"/>
       <c r="K68" s="9"/>
     </row>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" ht="13.8">
       <c r="J69" s="7"/>
       <c r="K69" s="9"/>
     </row>
-    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" ht="13.8">
       <c r="G70" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I70" s="1" t="n">
+      <c r="I70" s="1">
         <v>32</v>
       </c>
       <c r="J70" s="7" t="s">
@@ -3925,18 +4764,21 @@
       <c r="K70" s="9" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L70" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="71" ht="13.8">
       <c r="E71" s="6"/>
       <c r="F71" s="10"/>
       <c r="J71" s="7"/>
       <c r="K71" s="4"/>
     </row>
-    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" ht="13.8">
       <c r="G72" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I72" s="1" t="n">
+      <c r="I72" s="1">
         <v>33</v>
       </c>
       <c r="J72" s="7" t="s">
@@ -3945,8 +4787,11 @@
       <c r="K72" s="4" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L72" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="73" ht="13.8">
       <c r="E73" s="6" t="s">
         <v>62</v>
       </c>
@@ -3956,13 +4801,13 @@
       <c r="J73" s="7"/>
       <c r="K73" s="4"/>
     </row>
-    <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" ht="23.85">
       <c r="E74" s="6"/>
       <c r="F74" s="10"/>
       <c r="G74" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I74" s="1" t="n">
+      <c r="I74" s="1">
         <v>34</v>
       </c>
       <c r="J74" s="7" t="s">
@@ -3971,16 +4816,19 @@
       <c r="K74" s="9" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L74" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="75" ht="13.8">
       <c r="J75" s="7"/>
       <c r="K75" s="6"/>
     </row>
-    <row r="76" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" ht="35.05">
       <c r="G76" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I76" s="1" t="n">
+      <c r="I76" s="1">
         <v>35</v>
       </c>
       <c r="J76" s="7" t="s">
@@ -3989,9 +4837,12 @@
       <c r="K76" s="9" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I77" s="1" t="n">
+      <c r="L76" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="77" ht="13.8">
+      <c r="I77" s="1">
         <v>36</v>
       </c>
       <c r="J77" s="7" t="s">
@@ -4000,16 +4851,19 @@
       <c r="K77" s="6" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L77" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="78" ht="13.8">
       <c r="J78" s="7"/>
       <c r="K78" s="6"/>
     </row>
-    <row r="79" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" ht="79.85">
       <c r="G79" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I79" s="1" t="n">
+      <c r="I79" s="1">
         <v>37</v>
       </c>
       <c r="J79" s="7" t="s">
@@ -4018,9 +4872,12 @@
       <c r="K79" s="9" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I80" s="1" t="n">
+      <c r="L79" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="80" ht="13.8">
+      <c r="I80" s="1">
         <v>87</v>
       </c>
       <c r="J80" s="7" t="s">
@@ -4029,12 +4886,15 @@
       <c r="K80" s="9" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="81" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L80" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="81" ht="57.45">
       <c r="G81" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I81" s="1" t="n">
+      <c r="I81" s="1">
         <v>38</v>
       </c>
       <c r="J81" s="7" t="s">
@@ -4043,9 +4903,12 @@
       <c r="K81" s="9" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I82" s="1" t="n">
+      <c r="L81" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="82" ht="13.8">
+      <c r="I82" s="1">
         <v>39</v>
       </c>
       <c r="J82" s="7" t="s">
@@ -4054,12 +4917,15 @@
       <c r="K82" s="6" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="83" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L82" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="83" ht="43.25">
       <c r="G83" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I83" s="1" t="n">
+      <c r="I83" s="1">
         <v>40</v>
       </c>
       <c r="J83" s="7" t="s">
@@ -4068,12 +4934,15 @@
       <c r="K83" s="6" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="84" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L83" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="84" ht="46.25">
       <c r="G84" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I84" s="1" t="n">
+      <c r="I84" s="1">
         <v>41</v>
       </c>
       <c r="J84" s="7" t="s">
@@ -4082,33 +4951,36 @@
       <c r="K84" s="6" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L84" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="85" ht="13.8">
       <c r="E85" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F85" s="10" t="n">
+      <c r="F85" s="10">
         <v>3</v>
       </c>
       <c r="J85" s="7"/>
       <c r="K85" s="6"/>
     </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" ht="12.8">
       <c r="E86" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" ht="12.8">
       <c r="E87" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" ht="12.8">
       <c r="A90" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" ht="12.8">
       <c r="E91" s="1" t="s">
         <v>46</v>
       </c>
@@ -4116,7 +4988,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" ht="12.8">
       <c r="E92" s="1" t="s">
         <v>48</v>
       </c>
@@ -4124,7 +4996,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" ht="12.8">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -4142,7 +5014,7 @@
       <c r="L93" s="6"/>
       <c r="M93" s="1"/>
     </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" ht="12.8">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -4150,7 +5022,7 @@
       <c r="E94" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F94" s="6" t="n">
+      <c r="F94" s="6">
         <v>2</v>
       </c>
       <c r="G94" s="6"/>
@@ -4160,7 +5032,7 @@
       <c r="L94" s="6"/>
       <c r="M94" s="1"/>
     </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" ht="12.8">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -4178,7 +5050,7 @@
       <c r="L95" s="6"/>
       <c r="M95" s="1"/>
     </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" ht="12.8">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -4192,7 +5064,7 @@
       <c r="L96" s="6"/>
       <c r="M96" s="1"/>
     </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" ht="12.8">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -4200,7 +5072,7 @@
       <c r="E97" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F97" s="6" t="n">
+      <c r="F97" s="6">
         <v>2</v>
       </c>
       <c r="G97" s="6"/>
@@ -4210,11 +5082,11 @@
       <c r="L97" s="6"/>
       <c r="M97" s="1"/>
     </row>
-    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" ht="13.8">
       <c r="G99" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I99" s="1" t="n">
+      <c r="I99" s="1">
         <v>50</v>
       </c>
       <c r="J99" s="12" t="s">
@@ -4223,12 +5095,15 @@
       <c r="K99" s="9" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L99" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="100" ht="13.8">
       <c r="G100" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="I100" s="1" t="n">
+      <c r="I100" s="1">
         <v>51</v>
       </c>
       <c r="J100" s="12" t="s">
@@ -4237,12 +5112,15 @@
       <c r="K100" s="9" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L100" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="101" ht="13.8">
       <c r="G101" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I101" s="1" t="n">
+      <c r="I101" s="1">
         <v>52</v>
       </c>
       <c r="J101" s="12" t="s">
@@ -4251,12 +5129,15 @@
       <c r="K101" s="9" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="102" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L101" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="102" ht="61.15">
       <c r="G102" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I102" s="1" t="n">
+      <c r="I102" s="1">
         <v>53</v>
       </c>
       <c r="J102" s="12" t="s">
@@ -4265,18 +5146,21 @@
       <c r="K102" s="9" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L102" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="103" ht="13.8">
       <c r="E103" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F103" s="6" t="n">
+      <c r="F103" s="6">
         <v>1</v>
       </c>
       <c r="J103" s="7"/>
       <c r="K103" s="9"/>
     </row>
-    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" ht="13.8">
       <c r="E104" s="6" t="s">
         <v>62</v>
       </c>
@@ -4286,28 +5170,28 @@
       <c r="J104" s="7"/>
       <c r="K104" s="9"/>
     </row>
-    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" ht="13.8">
       <c r="E105" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F105" s="6" t="n">
+      <c r="F105" s="6">
         <v>1</v>
       </c>
       <c r="G105" s="6"/>
       <c r="J105" s="7"/>
       <c r="K105" s="9"/>
     </row>
-    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" ht="13.8">
       <c r="E106" s="6"/>
       <c r="F106" s="10"/>
       <c r="J106" s="7"/>
       <c r="K106" s="9"/>
     </row>
-    <row r="107" customFormat="false" ht="45.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" ht="45.5">
       <c r="G107" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I107" s="1" t="n">
+      <c r="I107" s="1">
         <v>54</v>
       </c>
       <c r="J107" s="6" t="s">
@@ -4316,14 +5200,17 @@
       <c r="K107" s="9" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="108" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L107" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="108" ht="37.3">
       <c r="E108" s="6"/>
       <c r="F108" s="10"/>
       <c r="G108" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I108" s="1" t="n">
+      <c r="I108" s="1">
         <v>55</v>
       </c>
       <c r="J108" s="12" t="s">
@@ -4332,20 +5219,23 @@
       <c r="K108" s="9" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L108" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="109" ht="13.8">
       <c r="E109" s="6"/>
       <c r="F109" s="10"/>
       <c r="J109" s="12"/>
       <c r="K109" s="9"/>
     </row>
-    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" ht="13.8">
       <c r="E110" s="6"/>
       <c r="F110" s="10"/>
       <c r="G110" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I110" s="1" t="n">
+      <c r="I110" s="1">
         <v>56</v>
       </c>
       <c r="J110" s="12" t="s">
@@ -4354,14 +5244,17 @@
       <c r="K110" s="9" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L110" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="111" ht="13.8">
       <c r="E111" s="6"/>
       <c r="F111" s="10"/>
       <c r="G111" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I111" s="1" t="n">
+      <c r="I111" s="1">
         <v>57</v>
       </c>
       <c r="J111" s="12" t="s">
@@ -4370,12 +5263,15 @@
       <c r="K111" s="9" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="112" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L111" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="112" ht="49.25">
       <c r="G112" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I112" s="1" t="n">
+      <c r="I112" s="1">
         <v>58</v>
       </c>
       <c r="J112" s="12" t="s">
@@ -4384,12 +5280,15 @@
       <c r="K112" s="9" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L112" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="113" ht="13.8">
       <c r="G113" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I113" s="1" t="n">
+      <c r="I113" s="1">
         <v>59</v>
       </c>
       <c r="J113" s="12" t="s">
@@ -4398,12 +5297,15 @@
       <c r="K113" s="9" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="114" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L113" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="114" ht="35.05">
       <c r="G114" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I114" s="1" t="n">
+      <c r="I114" s="1">
         <v>60</v>
       </c>
       <c r="J114" s="5" t="s">
@@ -4412,12 +5314,15 @@
       <c r="K114" s="7" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="115" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L114" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="115" ht="91">
       <c r="G115" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I115" s="1" t="n">
+      <c r="I115" s="1">
         <v>89</v>
       </c>
       <c r="J115" s="5" t="s">
@@ -4426,12 +5331,15 @@
       <c r="K115" s="13" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L115" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="116" ht="13.8">
       <c r="G116" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I116" s="1" t="n">
+      <c r="I116" s="1">
         <v>61</v>
       </c>
       <c r="J116" s="12" t="s">
@@ -4440,12 +5348,15 @@
       <c r="K116" s="9" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="117" customFormat="false" ht="73.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L116" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="117" ht="73.1">
       <c r="G117" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I117" s="1" t="n">
+      <c r="I117" s="1">
         <v>62</v>
       </c>
       <c r="J117" s="12" t="s">
@@ -4454,12 +5365,15 @@
       <c r="K117" s="13" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L117" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="118" ht="13.8">
       <c r="G118" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I118" s="1" t="n">
+      <c r="I118" s="1">
         <v>63</v>
       </c>
       <c r="J118" s="7" t="s">
@@ -4468,20 +5382,23 @@
       <c r="K118" s="4" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L118" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="119" ht="13.8">
       <c r="E119" s="6"/>
       <c r="F119" s="10"/>
       <c r="J119" s="7"/>
       <c r="K119" s="4"/>
     </row>
-    <row r="120" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" ht="37.3">
       <c r="E120" s="6"/>
       <c r="F120" s="10"/>
       <c r="G120" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I120" s="1" t="n">
+      <c r="I120" s="1">
         <v>64</v>
       </c>
       <c r="J120" s="12" t="s">
@@ -4490,12 +5407,15 @@
       <c r="K120" s="9" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="121" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L120" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="121" ht="37.3">
       <c r="G121" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I121" s="1" t="n">
+      <c r="I121" s="1">
         <v>65</v>
       </c>
       <c r="J121" s="12" t="s">
@@ -4504,12 +5424,15 @@
       <c r="K121" s="9" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="122" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L121" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="122" ht="57.45">
       <c r="G122" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I122" s="1" t="n">
+      <c r="I122" s="1">
         <v>66</v>
       </c>
       <c r="J122" s="7" t="s">
@@ -4518,12 +5441,15 @@
       <c r="K122" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="123" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L122" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="123" ht="25.35">
       <c r="G123" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I123" s="1" t="n">
+      <c r="I123" s="1">
         <v>67</v>
       </c>
       <c r="J123" s="12" t="s">
@@ -4532,8 +5458,11 @@
       <c r="K123" s="9" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L123" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="124" ht="13.8">
       <c r="E124" s="6" t="s">
         <v>79</v>
       </c>
@@ -4543,11 +5472,11 @@
       <c r="J124" s="12"/>
       <c r="K124" s="6"/>
     </row>
-    <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" ht="13.8">
       <c r="G125" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I125" s="1" t="n">
+      <c r="I125" s="1">
         <v>68</v>
       </c>
       <c r="J125" s="12" t="s">
@@ -4556,22 +5485,25 @@
       <c r="K125" s="9" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L125" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="126" ht="13.8">
       <c r="E126" s="6"/>
       <c r="F126" s="10"/>
       <c r="G126" s="6"/>
       <c r="J126" s="12"/>
       <c r="K126" s="6"/>
     </row>
-    <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" ht="13.8">
       <c r="E127" s="6"/>
       <c r="F127" s="10"/>
       <c r="G127" s="6"/>
       <c r="J127" s="12"/>
       <c r="K127" s="6"/>
     </row>
-    <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" ht="13.8">
       <c r="E128" s="6" t="s">
         <v>62</v>
       </c>
@@ -4581,11 +5513,11 @@
       <c r="J128" s="12"/>
       <c r="K128" s="6"/>
     </row>
-    <row r="129" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" ht="25.35">
       <c r="G129" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I129" s="1" t="n">
+      <c r="I129" s="1">
         <v>69</v>
       </c>
       <c r="J129" s="12" t="s">
@@ -4594,12 +5526,15 @@
       <c r="K129" s="9" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L129" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="130" ht="13.8">
       <c r="G130" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="I130" s="1" t="n">
+      <c r="I130" s="1">
         <v>70</v>
       </c>
       <c r="J130" s="12" t="s">
@@ -4608,12 +5543,15 @@
       <c r="K130" s="9" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L130" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="131" ht="13.8">
       <c r="G131" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I131" s="1" t="n">
+      <c r="I131" s="1">
         <v>71</v>
       </c>
       <c r="J131" s="12" t="s">
@@ -4622,12 +5560,15 @@
       <c r="K131" s="9" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="132" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L131" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="132" ht="61.15">
       <c r="G132" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I132" s="1" t="n">
+      <c r="I132" s="1">
         <v>72</v>
       </c>
       <c r="J132" s="12" t="s">
@@ -4636,12 +5577,15 @@
       <c r="K132" s="9" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L132" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="133" ht="13.8">
       <c r="G133" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I133" s="1" t="n">
+      <c r="I133" s="1">
         <v>73</v>
       </c>
       <c r="J133" s="12" t="s">
@@ -4650,12 +5594,15 @@
       <c r="K133" s="6" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="134" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L133" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="134" ht="37.3">
       <c r="G134" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I134" s="1" t="n">
+      <c r="I134" s="1">
         <v>74</v>
       </c>
       <c r="J134" s="12" t="s">
@@ -4664,12 +5611,15 @@
       <c r="K134" s="6" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="135" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L134" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="135" ht="85.05">
       <c r="G135" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I135" s="1" t="n">
+      <c r="I135" s="1">
         <v>75</v>
       </c>
       <c r="J135" s="12" t="s">
@@ -4678,12 +5628,15 @@
       <c r="K135" s="6" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="136" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L135" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="136" s="1" customFormat="1" ht="13.8">
       <c r="G136" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="I136" s="1" t="n">
+      <c r="I136" s="1">
         <v>76</v>
       </c>
       <c r="J136" s="12" t="s">
@@ -4692,12 +5645,15 @@
       <c r="K136" s="9" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="137" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L136" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="137" ht="53.7">
       <c r="G137" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I137" s="1" t="n">
+      <c r="I137" s="1">
         <v>77</v>
       </c>
       <c r="J137" s="5" t="s">
@@ -4706,12 +5662,15 @@
       <c r="K137" s="6" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L137" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="138" ht="13.8">
       <c r="G138" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I138" s="1" t="n">
+      <c r="I138" s="1">
         <v>78</v>
       </c>
       <c r="J138" s="12" t="s">
@@ -4720,12 +5679,15 @@
       <c r="K138" s="9" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L138" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="139" ht="13.8">
       <c r="G139" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I139" s="1" t="n">
+      <c r="I139" s="1">
         <v>79</v>
       </c>
       <c r="J139" s="12" t="s">
@@ -4734,12 +5696,15 @@
       <c r="K139" s="6" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="140" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L139" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="140" ht="68.65">
       <c r="G140" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I140" s="1" t="n">
+      <c r="I140" s="1">
         <v>80</v>
       </c>
       <c r="J140" s="7" t="s">
@@ -4748,9 +5713,12 @@
       <c r="K140" s="6" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I141" s="1" t="n">
+      <c r="L140" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="141" ht="13.8">
+      <c r="I141" s="1">
         <v>81</v>
       </c>
       <c r="J141" s="12" t="s">
@@ -4759,12 +5727,15 @@
       <c r="K141" s="9" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="142" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L141" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="142" s="1" customFormat="1" ht="13.8">
       <c r="G142" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I142" s="1" t="n">
+      <c r="I142" s="1">
         <v>82</v>
       </c>
       <c r="J142" s="12" t="s">
@@ -4773,12 +5744,15 @@
       <c r="K142" s="9" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="143" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L142" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="143" s="1" customFormat="1" ht="13.8">
       <c r="G143" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I143" s="1" t="n">
+      <c r="I143" s="1">
         <v>83</v>
       </c>
       <c r="J143" s="12" t="s">
@@ -4787,12 +5761,15 @@
       <c r="K143" s="9" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="144" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L143" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="144" ht="61.15">
       <c r="G144" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I144" s="1" t="n">
+      <c r="I144" s="1">
         <v>84</v>
       </c>
       <c r="J144" s="12" t="s">
@@ -4801,12 +5778,15 @@
       <c r="K144" s="6" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="145" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L144" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="145" ht="58.2">
       <c r="G145" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I145" s="1" t="n">
+      <c r="I145" s="1">
         <v>85</v>
       </c>
       <c r="J145" s="12" t="s">
@@ -4815,12 +5795,15 @@
       <c r="K145" s="6" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="146" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L145" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="146" ht="49.25">
       <c r="G146" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I146" s="1" t="n">
+      <c r="I146" s="1">
         <v>86</v>
       </c>
       <c r="J146" s="12" t="s">
@@ -4829,28 +5812,31 @@
       <c r="K146" s="6" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L146" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="147" ht="13.8">
       <c r="J147" s="12"/>
       <c r="K147" s="6"/>
     </row>
-    <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" ht="13.8">
       <c r="E148" s="6"/>
       <c r="F148" s="10"/>
       <c r="J148" s="7"/>
       <c r="K148" s="6"/>
     </row>
-    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" ht="12.8">
       <c r="E150" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" ht="12.8">
       <c r="A154" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" ht="12.8">
       <c r="E155" s="1" t="s">
         <v>81</v>
       </c>
@@ -4860,7 +5846,7 @@
       <c r="J155" s="14"/>
       <c r="K155" s="14"/>
     </row>
-    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" ht="12.8">
       <c r="E156" s="1" t="s">
         <v>82</v>
       </c>
@@ -4870,11 +5856,11 @@
       <c r="J156" s="14"/>
       <c r="K156" s="14"/>
     </row>
-    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" ht="12.8">
       <c r="E157" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F157" s="1" t="n">
+      <c r="F157" s="1">
         <v>13</v>
       </c>
       <c r="J157" s="14"/>
@@ -5126,7 +6112,7 @@
       <c r="IW157" s="1"/>
       <c r="IX157" s="1"/>
     </row>
-    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" ht="12.8">
       <c r="E158" s="1" t="s">
         <v>85</v>
       </c>
@@ -5136,11 +6122,11 @@
       <c r="J158" s="14"/>
       <c r="K158" s="14"/>
     </row>
-    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" ht="12.8">
       <c r="G159" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I159" s="1" t="n">
+      <c r="I159" s="1">
         <v>90</v>
       </c>
       <c r="J159" s="14" t="s">
@@ -5148,6 +6134,9 @@
       </c>
       <c r="K159" s="14" t="s">
         <v>203</v>
+      </c>
+      <c r="L159" t="s">
+        <v>202</v>
       </c>
       <c r="M159" s="1"/>
       <c r="N159" s="1"/>
@@ -5396,14 +6385,14 @@
       <c r="IW159" s="1"/>
       <c r="IX159" s="1"/>
     </row>
-    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" ht="12.8">
       <c r="M160" s="1"/>
     </row>
-    <row r="161" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" ht="23.85">
       <c r="G161" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I161" s="1" t="n">
+      <c r="I161" s="1">
         <v>91</v>
       </c>
       <c r="J161" s="7" t="s">
@@ -5412,12 +6401,15 @@
       <c r="K161" s="9" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="162" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L161" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="162" ht="13.8">
       <c r="G162" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I162" s="1" t="n">
+      <c r="I162" s="1">
         <v>92</v>
       </c>
       <c r="J162" s="7" t="s">
@@ -5426,12 +6418,15 @@
       <c r="K162" s="9" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="163" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L162" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="163" ht="13.8">
       <c r="G163" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="I163" s="1" t="n">
+      <c r="I163" s="1">
         <v>93</v>
       </c>
       <c r="J163" s="12" t="s">
@@ -5440,12 +6435,15 @@
       <c r="K163" s="9" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="164" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L163" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="164" ht="13.8">
       <c r="G164" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I164" s="1" t="n">
+      <c r="I164" s="1">
         <v>94</v>
       </c>
       <c r="J164" s="12" t="s">
@@ -5454,12 +6452,15 @@
       <c r="K164" s="9" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="165" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L164" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="165" ht="13.8">
       <c r="G165" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="I165" s="1" t="n">
+      <c r="I165" s="1">
         <v>95</v>
       </c>
       <c r="J165" s="12" t="s">
@@ -5468,12 +6469,15 @@
       <c r="K165" s="9" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="166" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L165" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="166" ht="13.8">
       <c r="G166" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I166" s="1" t="n">
+      <c r="I166" s="1">
         <v>96</v>
       </c>
       <c r="J166" s="7" t="s">
@@ -5482,12 +6486,15 @@
       <c r="K166" s="9" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="167" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L166" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="167" ht="13.8">
       <c r="G167" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="I167" s="1" t="n">
+      <c r="I167" s="1">
         <v>97</v>
       </c>
       <c r="J167" s="12" t="s">
@@ -5496,12 +6503,15 @@
       <c r="K167" s="9" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L167" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="168" ht="13.8">
       <c r="G168" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I168" s="1" t="n">
+      <c r="I168" s="1">
         <v>98</v>
       </c>
       <c r="J168" s="7" t="s">
@@ -5510,12 +6520,15 @@
       <c r="K168" s="9" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="169" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L168" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="169" ht="13.8">
       <c r="G169" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="I169" s="1" t="n">
+      <c r="I169" s="1">
         <v>99</v>
       </c>
       <c r="J169" s="12" t="s">
@@ -5524,41 +6537,44 @@
       <c r="K169" s="9" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L169" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="170" ht="13.8">
       <c r="E170" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F170" s="6" t="n">
+      <c r="F170" s="6">
         <v>1</v>
       </c>
       <c r="J170" s="7"/>
       <c r="K170" s="9"/>
     </row>
-    <row r="171" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" ht="13.8">
       <c r="E171" s="6"/>
       <c r="F171" s="10"/>
       <c r="J171" s="7"/>
       <c r="K171" s="9"/>
     </row>
-    <row r="172" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" ht="13.8">
       <c r="E172" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F172" s="6" t="n">
+      <c r="F172" s="6">
         <v>3</v>
       </c>
       <c r="G172" s="6"/>
       <c r="J172" s="7"/>
       <c r="K172" s="9"/>
     </row>
-    <row r="173" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" ht="13.8">
       <c r="E173" s="6"/>
       <c r="F173" s="6"/>
       <c r="G173" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="I173" s="1" t="n">
+      <c r="I173" s="1">
         <v>100</v>
       </c>
       <c r="J173" s="7" t="s">
@@ -5567,14 +6583,17 @@
       <c r="K173" s="9" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L173" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="174" ht="13.8">
       <c r="E174" s="6"/>
       <c r="F174" s="6"/>
       <c r="G174" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="I174" s="1" t="n">
+      <c r="I174" s="1">
         <v>101</v>
       </c>
       <c r="J174" s="7" t="s">
@@ -5583,14 +6602,17 @@
       <c r="K174" s="9" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L174" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="175" ht="13.8">
       <c r="E175" s="6"/>
       <c r="F175" s="6"/>
       <c r="G175" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="I175" s="1" t="n">
+      <c r="I175" s="1">
         <v>102</v>
       </c>
       <c r="J175" s="7" t="s">
@@ -5599,14 +6621,17 @@
       <c r="K175" s="9" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L175" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="176" ht="13.8">
       <c r="E176" s="6"/>
       <c r="F176" s="6"/>
       <c r="G176" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I176" s="1" t="n">
+      <c r="I176" s="1">
         <v>103</v>
       </c>
       <c r="J176" s="7" t="s">
@@ -5615,14 +6640,17 @@
       <c r="K176" s="9" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="177" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L176" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="177" ht="79.85">
       <c r="E177" s="6"/>
       <c r="F177" s="6"/>
       <c r="G177" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I177" s="1" t="n">
+      <c r="I177" s="1">
         <v>104</v>
       </c>
       <c r="J177" s="7" t="s">
@@ -5631,14 +6659,17 @@
       <c r="K177" s="9" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="178" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L177" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="178" ht="23.85">
       <c r="E178" s="6"/>
       <c r="F178" s="6"/>
       <c r="G178" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I178" s="1" t="n">
+      <c r="I178" s="1">
         <v>105</v>
       </c>
       <c r="J178" s="7" t="s">
@@ -5647,14 +6678,17 @@
       <c r="K178" s="9" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="179" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L178" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="179" ht="68.65">
       <c r="E179" s="6"/>
       <c r="F179" s="6"/>
       <c r="G179" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I179" s="1" t="n">
+      <c r="I179" s="1">
         <v>106</v>
       </c>
       <c r="J179" s="7" t="s">
@@ -5663,14 +6697,17 @@
       <c r="K179" s="9" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="180" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L179" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="180" ht="79.85">
       <c r="E180" s="6"/>
       <c r="F180" s="6"/>
       <c r="G180" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I180" s="1" t="n">
+      <c r="I180" s="1">
         <v>107</v>
       </c>
       <c r="J180" s="7" t="s">
@@ -5679,14 +6716,17 @@
       <c r="K180" s="9" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="181" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L180" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="181" ht="79.85">
       <c r="E181" s="6"/>
       <c r="F181" s="6"/>
       <c r="G181" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I181" s="1" t="n">
+      <c r="I181" s="1">
         <v>108</v>
       </c>
       <c r="J181" s="7" t="s">
@@ -5695,14 +6735,17 @@
       <c r="K181" s="9" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="182" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L181" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="182" ht="35.05">
       <c r="E182" s="6"/>
       <c r="F182" s="6"/>
       <c r="G182" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I182" s="1" t="n">
+      <c r="I182" s="1">
         <v>109</v>
       </c>
       <c r="J182" s="7" t="s">
@@ -5711,14 +6754,17 @@
       <c r="K182" s="9" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="183" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L182" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="183" ht="35.05">
       <c r="E183" s="6"/>
       <c r="F183" s="6"/>
       <c r="G183" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I183" s="1" t="n">
+      <c r="I183" s="1">
         <v>110</v>
       </c>
       <c r="J183" s="7" t="s">
@@ -5727,14 +6773,17 @@
       <c r="K183" s="9" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="184" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L183" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="184" ht="102.2">
       <c r="E184" s="6"/>
       <c r="F184" s="6"/>
       <c r="G184" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I184" s="1" t="n">
+      <c r="I184" s="1">
         <v>111</v>
       </c>
       <c r="J184" s="7" t="s">
@@ -5743,37 +6792,40 @@
       <c r="K184" s="9" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="185" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L184" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="185" ht="13.8">
       <c r="E185" s="6"/>
       <c r="F185" s="6"/>
       <c r="G185" s="6"/>
       <c r="J185" s="7"/>
       <c r="K185" s="9"/>
     </row>
-    <row r="186" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" ht="13.8">
       <c r="E186" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F186" s="6" t="n">
+      <c r="F186" s="6">
         <v>3</v>
       </c>
       <c r="G186" s="6"/>
       <c r="J186" s="12"/>
       <c r="K186" s="9"/>
     </row>
-    <row r="187" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" ht="13.8">
       <c r="E187" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F187" s="1" t="n">
+      <c r="F187" s="1">
         <v>0.5</v>
       </c>
       <c r="G187" s="6"/>
       <c r="J187" s="12"/>
       <c r="K187" s="9"/>
     </row>
-    <row r="188" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" ht="13.8">
       <c r="E188" s="1" t="s">
         <v>76</v>
       </c>
@@ -5781,12 +6833,12 @@
       <c r="J188" s="12"/>
       <c r="K188" s="9"/>
     </row>
-    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" ht="12.8">
       <c r="A191" s="1" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" ht="12.8">
       <c r="E192" s="1" t="s">
         <v>81</v>
       </c>
@@ -5796,7 +6848,7 @@
       <c r="J192" s="14"/>
       <c r="K192" s="14"/>
     </row>
-    <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" ht="12.8">
       <c r="E193" s="1" t="s">
         <v>82</v>
       </c>
@@ -5806,11 +6858,11 @@
       <c r="J193" s="14"/>
       <c r="K193" s="14"/>
     </row>
-    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" ht="12.8">
       <c r="E194" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F194" s="1" t="n">
+      <c r="F194" s="1">
         <v>13</v>
       </c>
       <c r="J194" s="14"/>
@@ -6062,7 +7114,7 @@
       <c r="IW194" s="1"/>
       <c r="IX194" s="1"/>
     </row>
-    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" ht="12.8">
       <c r="E195" s="1" t="s">
         <v>85</v>
       </c>
@@ -6072,11 +7124,11 @@
       <c r="J195" s="14"/>
       <c r="K195" s="14"/>
     </row>
-    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" ht="12.8">
       <c r="G196" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I196" s="1" t="n">
+      <c r="I196" s="1">
         <v>112</v>
       </c>
       <c r="J196" s="14" t="s">
@@ -6084,6 +7136,9 @@
       </c>
       <c r="K196" s="14" t="s">
         <v>203</v>
+      </c>
+      <c r="L196" t="s">
+        <v>202</v>
       </c>
       <c r="M196" s="1"/>
       <c r="N196" s="1"/>
@@ -6332,14 +7387,14 @@
       <c r="IW196" s="1"/>
       <c r="IX196" s="1"/>
     </row>
-    <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" ht="12.8">
       <c r="M197" s="1"/>
     </row>
-    <row r="198" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" ht="68.65">
       <c r="G198" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I198" s="1" t="n">
+      <c r="I198" s="1">
         <v>113</v>
       </c>
       <c r="J198" s="7" t="s">
@@ -6348,12 +7403,15 @@
       <c r="K198" s="9" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="199" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L198" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="199" ht="57.45">
       <c r="G199" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I199" s="1" t="n">
+      <c r="I199" s="1">
         <v>114</v>
       </c>
       <c r="J199" s="7" t="s">
@@ -6362,12 +7420,15 @@
       <c r="K199" s="9" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="200" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L199" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="200" ht="79.85">
       <c r="G200" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I200" s="1" t="n">
+      <c r="I200" s="1">
         <v>115</v>
       </c>
       <c r="J200" s="7" t="s">
@@ -6376,12 +7437,15 @@
       <c r="K200" s="9" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="201" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L200" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="201" ht="46.25">
       <c r="G201" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I201" s="1" t="n">
+      <c r="I201" s="1">
         <v>116</v>
       </c>
       <c r="J201" s="7" t="s">
@@ -6390,12 +7454,15 @@
       <c r="K201" s="9" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="202" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L201" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="202" ht="35.05">
       <c r="G202" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I202" s="1" t="n">
+      <c r="I202" s="1">
         <v>117</v>
       </c>
       <c r="J202" s="7" t="s">
@@ -6404,12 +7471,15 @@
       <c r="K202" s="9" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="203" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L202" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="203" ht="68.65">
       <c r="G203" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I203" s="1" t="n">
+      <c r="I203" s="1">
         <v>118</v>
       </c>
       <c r="J203" s="7" t="s">
@@ -6418,12 +7488,15 @@
       <c r="K203" s="9" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="204" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L203" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="204" ht="68.65">
       <c r="G204" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I204" s="1" t="n">
+      <c r="I204" s="1">
         <v>119</v>
       </c>
       <c r="J204" s="7" t="s">
@@ -6432,12 +7505,15 @@
       <c r="K204" s="9" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="205" customFormat="false" ht="67.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L204" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="205" ht="67.9">
       <c r="G205" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I205" s="1" t="n">
+      <c r="I205" s="1">
         <v>120</v>
       </c>
       <c r="J205" s="7" t="s">
@@ -6446,12 +7522,15 @@
       <c r="K205" s="9" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="206" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L205" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="206" ht="13.8">
       <c r="G206" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I206" s="1" t="n">
+      <c r="I206" s="1">
         <v>121</v>
       </c>
       <c r="J206" s="7" t="s">
@@ -6460,12 +7539,15 @@
       <c r="K206" s="9" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="207" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L206" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="207" ht="13.8">
       <c r="G207" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I207" s="1" t="n">
+      <c r="I207" s="1">
         <v>122</v>
       </c>
       <c r="J207" s="7" t="s">
@@ -6474,12 +7556,15 @@
       <c r="K207" s="9" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="208" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L207" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="208" ht="23.85">
       <c r="G208" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I208" s="1" t="n">
+      <c r="I208" s="1">
         <v>123</v>
       </c>
       <c r="J208" s="7" t="s">
@@ -6488,12 +7573,15 @@
       <c r="K208" s="9" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="209" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L208" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="209" ht="23.85">
       <c r="G209" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I209" s="1" t="n">
+      <c r="I209" s="1">
         <v>124</v>
       </c>
       <c r="J209" s="7" t="s">
@@ -6502,12 +7590,15 @@
       <c r="K209" s="9" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="210" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L209" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="210" ht="35.05">
       <c r="G210" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I210" s="1" t="n">
+      <c r="I210" s="1">
         <v>125</v>
       </c>
       <c r="J210" s="7" t="s">
@@ -6516,12 +7607,15 @@
       <c r="K210" s="9" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="211" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L210" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="211" ht="102.2">
       <c r="G211" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I211" s="1" t="n">
+      <c r="I211" s="1">
         <v>126</v>
       </c>
       <c r="J211" s="7" t="s">
@@ -6530,12 +7624,15 @@
       <c r="K211" s="9" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="212" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L211" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="212" ht="23.85">
       <c r="G212" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I212" s="1" t="n">
+      <c r="I212" s="1">
         <v>127</v>
       </c>
       <c r="J212" s="7" t="s">
@@ -6544,12 +7641,15 @@
       <c r="K212" s="9" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="213" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L212" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="213" ht="23.85">
       <c r="G213" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I213" s="1" t="n">
+      <c r="I213" s="1">
         <v>128</v>
       </c>
       <c r="J213" s="7" t="s">
@@ -6558,12 +7658,15 @@
       <c r="K213" s="9" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="214" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L213" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="214" ht="13.8">
       <c r="G214" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I214" s="1" t="n">
+      <c r="I214" s="1">
         <v>129</v>
       </c>
       <c r="J214" s="7" t="s">
@@ -6572,12 +7675,15 @@
       <c r="K214" s="9" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="215" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L214" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="215" ht="13.8">
       <c r="G215" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I215" s="1" t="n">
+      <c r="I215" s="1">
         <v>130</v>
       </c>
       <c r="J215" s="15" t="s">
@@ -6586,12 +7692,15 @@
       <c r="K215" s="9" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="216" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L215" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="216" ht="13.8">
       <c r="G216" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I216" s="1" t="n">
+      <c r="I216" s="1">
         <v>131</v>
       </c>
       <c r="J216" s="7" t="s">
@@ -6600,12 +7709,15 @@
       <c r="K216" s="9" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="217" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L216" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="217" ht="46.25">
       <c r="G217" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I217" s="1" t="n">
+      <c r="I217" s="1">
         <v>132</v>
       </c>
       <c r="J217" s="7" t="s">
@@ -6614,50 +7726,53 @@
       <c r="K217" s="9" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="218" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L217" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="218" ht="13.8">
       <c r="G218" s="6"/>
       <c r="J218" s="7"/>
       <c r="K218" s="9"/>
     </row>
-    <row r="219" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" ht="13.8">
       <c r="E219" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F219" s="6" t="n">
+      <c r="F219" s="6">
         <v>1</v>
       </c>
       <c r="J219" s="7"/>
       <c r="K219" s="9"/>
     </row>
-    <row r="220" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" ht="13.8">
       <c r="E220" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F220" s="1" t="n">
+      <c r="F220" s="1">
         <v>35</v>
       </c>
       <c r="J220" s="7"/>
       <c r="K220" s="9"/>
     </row>
-    <row r="221" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" ht="13.8">
       <c r="E221" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F221" s="6" t="n">
+      <c r="F221" s="6">
         <v>3</v>
       </c>
       <c r="G221" s="6"/>
       <c r="J221" s="7"/>
       <c r="K221" s="9"/>
     </row>
-    <row r="222" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" ht="13.8">
       <c r="E222" s="6"/>
       <c r="F222" s="6"/>
       <c r="G222" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I222" s="1" t="n">
+      <c r="I222" s="1">
         <v>133</v>
       </c>
       <c r="J222" s="7" t="s">
@@ -6666,14 +7781,17 @@
       <c r="K222" s="9" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="223" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L222" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="223" ht="57.45">
       <c r="E223" s="6"/>
       <c r="F223" s="6"/>
       <c r="G223" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="I223" s="1" t="n">
+      <c r="I223" s="1">
         <v>134</v>
       </c>
       <c r="J223" s="7" t="s">
@@ -6682,14 +7800,17 @@
       <c r="K223" s="9" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="224" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L223" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="224" ht="13.8">
       <c r="E224" s="6"/>
       <c r="F224" s="6"/>
       <c r="G224" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I224" s="1" t="n">
+      <c r="I224" s="1">
         <v>135</v>
       </c>
       <c r="J224" s="7" t="s">
@@ -6698,14 +7819,17 @@
       <c r="K224" s="9" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="225" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L224" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="225" ht="13.8">
       <c r="E225" s="6"/>
       <c r="F225" s="6"/>
       <c r="G225" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I225" s="1" t="n">
+      <c r="I225" s="1">
         <v>136</v>
       </c>
       <c r="J225" s="7" t="s">
@@ -6714,14 +7838,17 @@
       <c r="K225" s="9" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="226" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L225" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="226" ht="13.8">
       <c r="E226" s="6"/>
       <c r="F226" s="6"/>
       <c r="G226" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I226" s="1" t="n">
+      <c r="I226" s="1">
         <v>137</v>
       </c>
       <c r="J226" s="15" t="s">
@@ -6730,14 +7857,17 @@
       <c r="K226" s="9" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="227" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L226" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="227" ht="102.2">
       <c r="E227" s="6"/>
       <c r="F227" s="6"/>
       <c r="G227" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I227" s="1" t="n">
+      <c r="I227" s="1">
         <v>138</v>
       </c>
       <c r="J227" s="5" t="s">
@@ -6746,52 +7876,55 @@
       <c r="K227" s="9" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="228" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L227" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="228" ht="13.8">
       <c r="E228" s="6"/>
       <c r="F228" s="6"/>
       <c r="G228" s="6"/>
       <c r="J228" s="7"/>
       <c r="K228" s="9"/>
     </row>
-    <row r="229" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" ht="13.8">
       <c r="E229" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F229" s="6" t="n">
+      <c r="F229" s="6">
         <v>3</v>
       </c>
       <c r="G229" s="6"/>
       <c r="J229" s="12"/>
       <c r="K229" s="9"/>
     </row>
-    <row r="230" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" ht="13.8">
       <c r="E230" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F230" s="1" t="n">
+      <c r="F230" s="1">
         <v>0.5</v>
       </c>
       <c r="G230" s="6"/>
       <c r="J230" s="12"/>
       <c r="K230" s="9"/>
     </row>
-    <row r="231" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" ht="13.8">
       <c r="G231" s="6"/>
       <c r="J231" s="12"/>
       <c r="K231" s="9"/>
     </row>
-    <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" ht="12.8">
       <c r="E232" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" ht="12.8">
       <c r="A234" s="1" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" ht="12.8">
       <c r="E235" s="1" t="s">
         <v>81</v>
       </c>
@@ -6801,7 +7934,7 @@
       <c r="J235" s="14"/>
       <c r="K235" s="14"/>
     </row>
-    <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" ht="12.8">
       <c r="E236" s="1" t="s">
         <v>82</v>
       </c>
@@ -6811,11 +7944,11 @@
       <c r="J236" s="14"/>
       <c r="K236" s="14"/>
     </row>
-    <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="237" ht="12.8">
       <c r="E237" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F237" s="1" t="n">
+      <c r="F237" s="1">
         <v>13</v>
       </c>
       <c r="J237" s="14"/>
@@ -7067,7 +8200,7 @@
       <c r="IW237" s="1"/>
       <c r="IX237" s="1"/>
     </row>
-    <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" ht="12.8">
       <c r="E238" s="1" t="s">
         <v>85</v>
       </c>
@@ -7077,11 +8210,11 @@
       <c r="J238" s="14"/>
       <c r="K238" s="14"/>
     </row>
-    <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" ht="12.8">
       <c r="G239" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I239" s="1" t="n">
+      <c r="I239" s="1">
         <v>139</v>
       </c>
       <c r="J239" s="14" t="s">
@@ -7089,6 +8222,9 @@
       </c>
       <c r="K239" s="14" t="s">
         <v>203</v>
+      </c>
+      <c r="L239" t="s">
+        <v>202</v>
       </c>
       <c r="M239" s="1"/>
       <c r="N239" s="1"/>
@@ -7337,14 +8473,14 @@
       <c r="IW239" s="1"/>
       <c r="IX239" s="1"/>
     </row>
-    <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" ht="12.8">
       <c r="M240" s="1"/>
     </row>
-    <row r="241" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" ht="79.85">
       <c r="G241" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I241" s="1" t="n">
+      <c r="I241" s="1">
         <v>140</v>
       </c>
       <c r="J241" s="7" t="s">
@@ -7353,12 +8489,15 @@
       <c r="K241" s="9" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="242" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L241" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="242" ht="91">
       <c r="G242" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I242" s="1" t="n">
+      <c r="I242" s="1">
         <v>141</v>
       </c>
       <c r="J242" s="7" t="s">
@@ -7367,12 +8506,15 @@
       <c r="K242" s="9" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="243" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L242" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="243" ht="68.65">
       <c r="G243" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I243" s="1" t="n">
+      <c r="I243" s="1">
         <v>142</v>
       </c>
       <c r="J243" s="7" t="s">
@@ -7381,12 +8523,15 @@
       <c r="K243" s="9" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="244" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L243" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="244" ht="46.25">
       <c r="G244" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I244" s="1" t="n">
+      <c r="I244" s="1">
         <v>143</v>
       </c>
       <c r="J244" s="7" t="s">
@@ -7395,12 +8540,15 @@
       <c r="K244" s="9" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="245" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L244" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="245" ht="113.4">
       <c r="G245" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I245" s="1" t="n">
+      <c r="I245" s="1">
         <v>144</v>
       </c>
       <c r="J245" s="7" t="s">
@@ -7409,12 +8557,15 @@
       <c r="K245" s="9" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="246" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L245" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="246" ht="46.25">
       <c r="G246" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I246" s="1" t="n">
+      <c r="I246" s="1">
         <v>145</v>
       </c>
       <c r="J246" s="7" t="s">
@@ -7423,12 +8574,15 @@
       <c r="K246" s="9" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="247" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L246" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="247" ht="68.65">
       <c r="G247" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I247" s="1" t="n">
+      <c r="I247" s="1">
         <v>146</v>
       </c>
       <c r="J247" s="7" t="s">
@@ -7437,12 +8591,15 @@
       <c r="K247" s="9" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="248" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L247" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="248" ht="23.85">
       <c r="G248" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I248" s="1" t="n">
+      <c r="I248" s="1">
         <v>147</v>
       </c>
       <c r="J248" s="7" t="s">
@@ -7451,12 +8608,15 @@
       <c r="K248" s="9" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="249" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L248" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="249" ht="13.8">
       <c r="G249" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I249" s="1" t="n">
+      <c r="I249" s="1">
         <v>148</v>
       </c>
       <c r="J249" s="7" t="s">
@@ -7465,12 +8625,15 @@
       <c r="K249" s="9" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="250" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L249" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="250" ht="57.45">
       <c r="G250" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I250" s="1" t="n">
+      <c r="I250" s="1">
         <v>149</v>
       </c>
       <c r="J250" s="7" t="s">
@@ -7479,12 +8642,15 @@
       <c r="K250" s="9" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="251" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L250" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="251" ht="57.45">
       <c r="G251" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I251" s="1" t="n">
+      <c r="I251" s="1">
         <v>150</v>
       </c>
       <c r="J251" s="7" t="s">
@@ -7493,12 +8659,15 @@
       <c r="K251" s="9" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="252" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L251" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="252" ht="35.05">
       <c r="G252" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I252" s="1" t="n">
+      <c r="I252" s="1">
         <v>151</v>
       </c>
       <c r="J252" s="7" t="s">
@@ -7507,12 +8676,15 @@
       <c r="K252" s="9" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="253" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L252" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="253" ht="13.8">
       <c r="G253" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I253" s="1" t="n">
+      <c r="I253" s="1">
         <v>152</v>
       </c>
       <c r="J253" s="7" t="s">
@@ -7521,12 +8693,15 @@
       <c r="K253" s="9" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="254" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L253" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="254" ht="68.65">
       <c r="G254" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I254" s="1" t="n">
+      <c r="I254" s="1">
         <v>153</v>
       </c>
       <c r="J254" s="7" t="s">
@@ -7535,12 +8710,15 @@
       <c r="K254" s="9" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="255" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L254" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="255" ht="57.45">
       <c r="G255" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I255" s="1" t="n">
+      <c r="I255" s="1">
         <v>154</v>
       </c>
       <c r="J255" s="7" t="s">
@@ -7549,12 +8727,15 @@
       <c r="K255" s="9" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="256" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L255" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="256" ht="13.8">
       <c r="G256" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I256" s="1" t="n">
+      <c r="I256" s="1">
         <v>155</v>
       </c>
       <c r="J256" s="7" t="s">
@@ -7563,12 +8744,15 @@
       <c r="K256" s="9" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="257" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L256" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="257" ht="79.85">
       <c r="G257" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I257" s="1" t="n">
+      <c r="I257" s="1">
         <v>156</v>
       </c>
       <c r="J257" s="7" t="s">
@@ -7577,12 +8761,15 @@
       <c r="K257" s="9" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="258" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L257" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="258" ht="13.8">
       <c r="G258" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I258" s="1" t="n">
+      <c r="I258" s="1">
         <v>157</v>
       </c>
       <c r="J258" s="7" t="s">
@@ -7591,12 +8778,15 @@
       <c r="K258" s="9" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="259" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L258" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="259" ht="113.4">
       <c r="G259" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I259" s="1" t="n">
+      <c r="I259" s="1">
         <v>158</v>
       </c>
       <c r="J259" s="7" t="s">
@@ -7605,12 +8795,15 @@
       <c r="K259" s="9" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="260" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L259" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="260" ht="13.8">
       <c r="G260" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I260" s="1" t="n">
+      <c r="I260" s="1">
         <v>159</v>
       </c>
       <c r="J260" s="7" t="s">
@@ -7619,12 +8812,15 @@
       <c r="K260" s="9" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="261" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L260" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="261" ht="13.8">
       <c r="G261" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I261" s="1" t="n">
+      <c r="I261" s="1">
         <v>160</v>
       </c>
       <c r="J261" s="7" t="s">
@@ -7633,12 +8829,15 @@
       <c r="K261" s="9" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="262" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L261" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="262" ht="113.4">
       <c r="G262" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I262" s="1" t="n">
+      <c r="I262" s="1">
         <v>161</v>
       </c>
       <c r="J262" s="7" t="s">
@@ -7647,12 +8846,15 @@
       <c r="K262" s="9" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="263" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L262" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="263" ht="102.2">
       <c r="G263" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I263" s="1" t="n">
+      <c r="I263" s="1">
         <v>162</v>
       </c>
       <c r="J263" s="7" t="s">
@@ -7661,12 +8863,15 @@
       <c r="K263" s="9" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="264" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L263" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="264" ht="13.8">
       <c r="G264" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I264" s="1" t="n">
+      <c r="I264" s="1">
         <v>163</v>
       </c>
       <c r="J264" s="7" t="s">
@@ -7675,64 +8880,67 @@
       <c r="K264" s="9" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="265" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L264" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="265" ht="13.8">
       <c r="G265" s="6"/>
       <c r="J265" s="7"/>
       <c r="K265" s="9"/>
     </row>
-    <row r="266" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="266" ht="13.8">
       <c r="G266" s="6"/>
       <c r="J266" s="7"/>
       <c r="K266" s="9"/>
     </row>
-    <row r="267" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="267" ht="13.8">
       <c r="G267" s="6"/>
       <c r="J267" s="7"/>
       <c r="K267" s="9"/>
     </row>
-    <row r="268" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="268" ht="13.8">
       <c r="E268" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F268" s="6" t="n">
+      <c r="F268" s="6">
         <v>3</v>
       </c>
       <c r="G268" s="6"/>
       <c r="J268" s="12"/>
       <c r="K268" s="9"/>
     </row>
-    <row r="269" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="269" ht="13.8">
       <c r="E269" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F269" s="1" t="n">
+      <c r="F269" s="1">
         <v>0.5</v>
       </c>
       <c r="G269" s="6"/>
       <c r="J269" s="12"/>
       <c r="K269" s="9"/>
     </row>
-    <row r="270" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="270" ht="13.8">
       <c r="G270" s="6"/>
       <c r="J270" s="12"/>
       <c r="K270" s="9"/>
     </row>
-    <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" ht="12.8">
       <c r="E271" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" ht="12.8">
       <c r="A274" s="1" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="275" ht="12.8">
       <c r="J275" s="14"/>
       <c r="K275" s="14"/>
     </row>
-    <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="276" ht="12.8">
       <c r="A276" s="6"/>
       <c r="B276" s="6"/>
       <c r="C276" s="6"/>
@@ -7750,7 +8958,7 @@
       <c r="L276" s="6"/>
       <c r="M276" s="1"/>
     </row>
-    <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="277" ht="12.8">
       <c r="A277" s="6"/>
       <c r="B277" s="6"/>
       <c r="C277" s="6"/>
@@ -7758,7 +8966,7 @@
       <c r="E277" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F277" s="6" t="n">
+      <c r="F277" s="6">
         <v>2</v>
       </c>
       <c r="G277" s="6"/>
@@ -7768,7 +8976,7 @@
       <c r="L277" s="6"/>
       <c r="M277" s="1"/>
     </row>
-    <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" ht="12.8">
       <c r="A278" s="6"/>
       <c r="B278" s="6"/>
       <c r="C278" s="6"/>
@@ -7786,7 +8994,7 @@
       <c r="L278" s="6"/>
       <c r="M278" s="1"/>
     </row>
-    <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="279" ht="12.8">
       <c r="A279" s="6"/>
       <c r="B279" s="6"/>
       <c r="C279" s="6"/>
@@ -7800,7 +9008,7 @@
       <c r="L279" s="6"/>
       <c r="M279" s="1"/>
     </row>
-    <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="280" ht="12.8">
       <c r="A280" s="6"/>
       <c r="B280" s="6"/>
       <c r="C280" s="6"/>
@@ -7808,7 +9016,7 @@
       <c r="E280" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F280" s="6" t="n">
+      <c r="F280" s="6">
         <v>2</v>
       </c>
       <c r="G280" s="6"/>
@@ -7818,23 +9026,23 @@
       <c r="L280" s="6"/>
       <c r="M280" s="1"/>
     </row>
-    <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" ht="12.8">
       <c r="J281" s="14"/>
       <c r="K281" s="14"/>
     </row>
-    <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="282" ht="12.8">
       <c r="J282" s="14"/>
       <c r="K282" s="14"/>
     </row>
-    <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="283" ht="12.8">
       <c r="J283" s="14"/>
       <c r="K283" s="14"/>
     </row>
-    <row r="284" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" ht="13.8">
       <c r="G284" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I284" s="1" t="n">
+      <c r="I284" s="1">
         <v>164</v>
       </c>
       <c r="J284" s="7" t="s">
@@ -7843,12 +9051,15 @@
       <c r="K284" s="9" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="285" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L284" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="285" ht="13.8">
       <c r="G285" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="I285" s="1" t="n">
+      <c r="I285" s="1">
         <v>165</v>
       </c>
       <c r="J285" s="7" t="s">
@@ -7857,12 +9068,15 @@
       <c r="K285" s="9" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="286" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L285" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="286" ht="13.8">
       <c r="G286" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I286" s="1" t="n">
+      <c r="I286" s="1">
         <v>166</v>
       </c>
       <c r="J286" s="7" t="s">
@@ -7871,10 +9085,13 @@
       <c r="K286" s="9" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="287" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L286" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="287" ht="13.8">
       <c r="G287" s="6"/>
-      <c r="I287" s="1" t="n">
+      <c r="I287" s="1">
         <v>167</v>
       </c>
       <c r="J287" s="7" t="s">
@@ -7883,12 +9100,15 @@
       <c r="K287" s="9" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="288" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L287" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="288" ht="13.8">
       <c r="G288" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I288" s="1" t="n">
+      <c r="I288" s="1">
         <v>168</v>
       </c>
       <c r="J288" s="7" t="s">
@@ -7897,10 +9117,13 @@
       <c r="K288" s="9" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="289" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L288" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="289" ht="35.05">
       <c r="G289" s="6"/>
-      <c r="I289" s="1" t="n">
+      <c r="I289" s="1">
         <v>169</v>
       </c>
       <c r="J289" s="7" t="s">
@@ -7909,12 +9132,15 @@
       <c r="K289" s="9" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="290" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L289" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="290" ht="13.8">
       <c r="G290" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="I290" s="1" t="n">
+      <c r="I290" s="1">
         <v>170</v>
       </c>
       <c r="J290" s="7" t="s">
@@ -7923,46 +9149,49 @@
       <c r="K290" s="9" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="291" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L290" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="291" ht="13.8">
       <c r="G291" s="6"/>
       <c r="J291" s="7"/>
       <c r="K291" s="9"/>
     </row>
-    <row r="292" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="292" ht="13.8">
       <c r="E292" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F292" s="6" t="n">
+      <c r="F292" s="6">
         <v>2</v>
       </c>
       <c r="J292" s="7"/>
       <c r="K292" s="9"/>
     </row>
-    <row r="293" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="293" ht="13.8">
       <c r="E293" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F293" s="1" t="n">
+      <c r="F293" s="1">
         <v>86</v>
       </c>
       <c r="J293" s="7"/>
       <c r="K293" s="9"/>
     </row>
-    <row r="294" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="294" ht="13.8">
       <c r="E294" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F294" s="6" t="n">
+      <c r="F294" s="6">
         <v>2</v>
       </c>
       <c r="G294" s="6"/>
       <c r="J294" s="7"/>
       <c r="K294" s="9"/>
     </row>
-    <row r="295" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="295" ht="13.8">
       <c r="G295" s="6"/>
-      <c r="I295" s="1" t="n">
+      <c r="I295" s="1">
         <v>171</v>
       </c>
       <c r="J295" s="7" t="s">
@@ -7971,12 +9200,15 @@
       <c r="K295" s="9" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="296" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L295" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="296" ht="23.85">
       <c r="G296" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I296" s="1" t="n">
+      <c r="I296" s="1">
         <v>172</v>
       </c>
       <c r="J296" s="7" t="s">
@@ -7985,12 +9217,15 @@
       <c r="K296" s="9" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="297" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L296" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="297" ht="35.05">
       <c r="G297" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I297" s="1" t="n">
+      <c r="I297" s="1">
         <v>173</v>
       </c>
       <c r="J297" s="7" t="s">
@@ -7999,12 +9234,15 @@
       <c r="K297" s="9" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="298" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L297" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="298" ht="23.85">
       <c r="G298" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I298" s="1" t="n">
+      <c r="I298" s="1">
         <v>174</v>
       </c>
       <c r="J298" s="7" t="s">
@@ -8013,12 +9251,15 @@
       <c r="K298" s="9" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="299" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L298" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="299" ht="13.8">
       <c r="G299" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I299" s="1" t="n">
+      <c r="I299" s="1">
         <v>175</v>
       </c>
       <c r="J299" s="7" t="s">
@@ -8027,12 +9268,15 @@
       <c r="K299" s="9" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="300" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L299" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="300" ht="135.8">
       <c r="G300" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I300" s="1" t="n">
+      <c r="I300" s="1">
         <v>176</v>
       </c>
       <c r="J300" s="7" t="s">
@@ -8041,12 +9285,15 @@
       <c r="K300" s="9" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="301" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L300" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="301" ht="91">
       <c r="G301" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I301" s="1" t="n">
+      <c r="I301" s="1">
         <v>177</v>
       </c>
       <c r="J301" s="7" t="s">
@@ -8055,12 +9302,15 @@
       <c r="K301" s="9" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="302" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L301" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="302" ht="35.05">
       <c r="G302" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I302" s="1" t="n">
+      <c r="I302" s="1">
         <v>178</v>
       </c>
       <c r="J302" s="7" t="s">
@@ -8069,12 +9319,15 @@
       <c r="K302" s="9" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="303" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L302" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="303" ht="13.8">
       <c r="G303" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="I303" s="1" t="n">
+      <c r="I303" s="1">
         <v>179</v>
       </c>
       <c r="J303" s="7" t="s">
@@ -8083,12 +9336,15 @@
       <c r="K303" s="9" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="304" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L303" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="304" ht="46.25">
       <c r="G304" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I304" s="1" t="n">
+      <c r="I304" s="1">
         <v>181</v>
       </c>
       <c r="J304" s="7" t="s">
@@ -8097,12 +9353,15 @@
       <c r="K304" s="9" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="305" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L304" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="305" ht="23.85">
       <c r="G305" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I305" s="1" t="n">
+      <c r="I305" s="1">
         <v>182</v>
       </c>
       <c r="J305" s="7" t="s">
@@ -8111,12 +9370,15 @@
       <c r="K305" s="9" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="306" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L305" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="306" ht="46.25">
       <c r="G306" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I306" s="1" t="n">
+      <c r="I306" s="1">
         <v>183</v>
       </c>
       <c r="J306" s="7" t="s">
@@ -8125,23 +9387,26 @@
       <c r="K306" s="9" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="307" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L306" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="307" ht="13.8">
       <c r="E307" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F307" s="16" t="n">
+      <c r="F307" s="16">
         <v>74</v>
       </c>
       <c r="G307" s="6"/>
       <c r="J307" s="7"/>
       <c r="K307" s="9"/>
     </row>
-    <row r="308" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="308" ht="13.8">
       <c r="G308" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I308" s="1" t="n">
+      <c r="I308" s="1">
         <v>184</v>
       </c>
       <c r="J308" s="7" t="s">
@@ -8150,18 +9415,21 @@
       <c r="K308" s="9" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="309" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L308" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="309" ht="13.8">
       <c r="F309" s="16"/>
       <c r="G309" s="6"/>
       <c r="J309" s="7"/>
       <c r="K309" s="9"/>
     </row>
-    <row r="310" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="310" ht="23.85">
       <c r="G310" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I310" s="1" t="n">
+      <c r="I310" s="1">
         <v>185</v>
       </c>
       <c r="J310" s="7" t="s">
@@ -8170,12 +9438,15 @@
       <c r="K310" s="9" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="311" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L310" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="311" ht="13.8">
       <c r="G311" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I311" s="1" t="n">
+      <c r="I311" s="1">
         <v>186</v>
       </c>
       <c r="J311" s="7" t="s">
@@ -8184,12 +9455,15 @@
       <c r="K311" s="9" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="312" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L311" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="312" ht="13.8">
       <c r="G312" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I312" s="1" t="n">
+      <c r="I312" s="1">
         <v>187</v>
       </c>
       <c r="J312" s="7" t="s">
@@ -8198,12 +9472,15 @@
       <c r="K312" s="9" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="313" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L312" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="313" ht="23.85">
       <c r="G313" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I313" s="1" t="n">
+      <c r="I313" s="1">
         <v>188</v>
       </c>
       <c r="J313" s="7" t="s">
@@ -8212,12 +9489,15 @@
       <c r="K313" s="9" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="314" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L313" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="314" ht="23.85">
       <c r="G314" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I314" s="1" t="n">
+      <c r="I314" s="1">
         <v>189</v>
       </c>
       <c r="J314" s="7" t="s">
@@ -8226,12 +9506,15 @@
       <c r="K314" s="9" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="315" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L314" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="315" ht="13.8">
       <c r="G315" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I315" s="1" t="n">
+      <c r="I315" s="1">
         <v>190</v>
       </c>
       <c r="J315" s="7" t="s">
@@ -8240,12 +9523,15 @@
       <c r="K315" s="9" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="316" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L315" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="316" ht="13.8">
       <c r="G316" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I316" s="1" t="n">
+      <c r="I316" s="1">
         <v>191</v>
       </c>
       <c r="J316" s="7" t="s">
@@ -8254,12 +9540,15 @@
       <c r="K316" s="9" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="317" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L316" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="317" ht="13.8">
       <c r="G317" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="I317" s="1" t="n">
+      <c r="I317" s="1">
         <v>192</v>
       </c>
       <c r="J317" s="7" t="s">
@@ -8268,12 +9557,15 @@
       <c r="K317" s="9" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="318" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L317" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="318" ht="113.4">
       <c r="G318" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I318" s="1" t="n">
+      <c r="I318" s="1">
         <v>193</v>
       </c>
       <c r="J318" s="7" t="s">
@@ -8282,18 +9574,21 @@
       <c r="K318" s="9" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="319" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L318" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="319" ht="13.8">
       <c r="G319" s="6"/>
       <c r="J319" s="7"/>
       <c r="K319" s="9"/>
     </row>
-    <row r="320" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="320" ht="13.8">
       <c r="G320" s="6"/>
       <c r="J320" s="7"/>
       <c r="K320" s="9"/>
     </row>
-    <row r="321" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="321" ht="13.8">
       <c r="E321" s="1" t="s">
         <v>383</v>
       </c>
@@ -8304,7 +9599,7 @@
       <c r="J321" s="7"/>
       <c r="K321" s="9"/>
     </row>
-    <row r="322" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="322" ht="13.8">
       <c r="E322" s="1" t="s">
         <v>383</v>
       </c>
@@ -8315,77 +9610,77 @@
       <c r="J322" s="7"/>
       <c r="K322" s="9"/>
     </row>
-    <row r="323" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="323" ht="13.8">
       <c r="G323" s="6"/>
       <c r="J323" s="7"/>
       <c r="K323" s="9"/>
     </row>
-    <row r="324" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="324" ht="13.8">
       <c r="G324" s="6"/>
       <c r="J324" s="7"/>
       <c r="K324" s="9"/>
     </row>
-    <row r="325" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="325" ht="13.8">
       <c r="G325" s="6"/>
       <c r="J325" s="7"/>
       <c r="K325" s="9"/>
     </row>
-    <row r="326" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="326" ht="13.8">
       <c r="E326" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F326" s="6" t="n">
+      <c r="F326" s="6">
         <v>3</v>
       </c>
       <c r="G326" s="6"/>
       <c r="J326" s="12"/>
       <c r="K326" s="9"/>
     </row>
-    <row r="327" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="327" ht="13.8">
       <c r="E327" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F327" s="1" t="n">
+      <c r="F327" s="1">
         <v>0.5</v>
       </c>
       <c r="G327" s="6"/>
       <c r="J327" s="12"/>
       <c r="K327" s="9"/>
     </row>
-    <row r="328" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="328" ht="13.8">
       <c r="G328" s="6"/>
       <c r="J328" s="12"/>
       <c r="K328" s="9"/>
     </row>
-    <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="329" ht="12.8">
       <c r="E329" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="332" ht="12.8">
       <c r="A332" s="1" t="s">
         <v>386</v>
       </c>
       <c r="F332" s="16"/>
     </row>
-    <row r="333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="333" ht="12.8">
       <c r="E333" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="F333" s="16" t="n">
+      <c r="F333" s="16">
         <v>77</v>
       </c>
       <c r="J333" s="6"/>
     </row>
-    <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="334" ht="12.8">
       <c r="F334" s="16"/>
     </row>
-    <row r="335" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="335" ht="35.05">
       <c r="F335" s="16"/>
       <c r="G335" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I335" s="1" t="n">
+      <c r="I335" s="1">
         <v>200</v>
       </c>
       <c r="J335" s="7" t="s">
@@ -8394,13 +9689,16 @@
       <c r="K335" s="6" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="336" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L335" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="336" ht="23.85">
       <c r="F336" s="16"/>
       <c r="G336" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I336" s="1" t="n">
+      <c r="I336" s="1">
         <v>201</v>
       </c>
       <c r="J336" s="7" t="s">
@@ -8409,18 +9707,21 @@
       <c r="K336" s="1" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="337" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L336" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="337" ht="13.8">
       <c r="F337" s="16"/>
       <c r="J337" s="7"/>
       <c r="K337" s="4"/>
     </row>
-    <row r="338" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="338" ht="35.05">
       <c r="F338" s="16"/>
       <c r="G338" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I338" s="1" t="n">
+      <c r="I338" s="1">
         <v>202</v>
       </c>
       <c r="J338" s="7" t="s">
@@ -8429,8 +9730,11 @@
       <c r="K338" s="6" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="339" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L338" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="339" ht="13.8">
       <c r="A339" s="1" t="s">
         <v>394</v>
       </c>
@@ -8438,12 +9742,12 @@
       <c r="J339" s="7"/>
       <c r="K339" s="6"/>
     </row>
-    <row r="340" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="340" ht="79.85">
       <c r="F340" s="16"/>
       <c r="G340" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I340" s="1" t="n">
+      <c r="I340" s="1">
         <v>203</v>
       </c>
       <c r="J340" s="7" t="s">
@@ -8452,8 +9756,11 @@
       <c r="K340" s="6" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="341" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L340" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="341" ht="13.8">
       <c r="B341" s="1" t="s">
         <v>397</v>
       </c>
@@ -8461,7 +9768,7 @@
         <v>18</v>
       </c>
       <c r="F341" s="16"/>
-      <c r="I341" s="1" t="n">
+      <c r="I341" s="1">
         <v>204</v>
       </c>
       <c r="J341" s="7" t="s">
@@ -8470,8 +9777,11 @@
       <c r="K341" s="1" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="342" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L341" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="342" ht="13.8">
       <c r="B342" s="1" t="s">
         <v>400</v>
       </c>
@@ -8479,7 +9789,7 @@
         <v>18</v>
       </c>
       <c r="F342" s="16"/>
-      <c r="I342" s="1" t="n">
+      <c r="I342" s="1">
         <v>205</v>
       </c>
       <c r="J342" s="7" t="s">
@@ -8488,8 +9798,11 @@
       <c r="K342" s="1" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="343" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L342" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="343" ht="13.8">
       <c r="A343" s="1" t="s">
         <v>397</v>
       </c>
@@ -8497,12 +9810,12 @@
       <c r="J343" s="7"/>
       <c r="K343" s="6"/>
     </row>
-    <row r="344" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="344" ht="46.25">
       <c r="F344" s="16"/>
       <c r="G344" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I344" s="1" t="n">
+      <c r="I344" s="1">
         <v>206</v>
       </c>
       <c r="J344" s="7" t="s">
@@ -8511,8 +9824,11 @@
       <c r="K344" s="6" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="345" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L344" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="345" ht="13.8">
       <c r="B345" s="1" t="s">
         <v>405</v>
       </c>
@@ -8520,7 +9836,7 @@
         <v>18</v>
       </c>
       <c r="F345" s="16"/>
-      <c r="I345" s="1" t="n">
+      <c r="I345" s="1">
         <v>207</v>
       </c>
       <c r="J345" s="7" t="s">
@@ -8529,8 +9845,11 @@
       <c r="K345" s="1" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="346" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L345" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="346" ht="13.8">
       <c r="B346" s="1" t="s">
         <v>394</v>
       </c>
@@ -8538,7 +9857,7 @@
         <v>18</v>
       </c>
       <c r="F346" s="16"/>
-      <c r="I346" s="1" t="n">
+      <c r="I346" s="1">
         <v>208</v>
       </c>
       <c r="J346" s="7" t="s">
@@ -8547,8 +9866,11 @@
       <c r="K346" s="1" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="347" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L346" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="347" ht="13.8">
       <c r="A347" s="1" t="s">
         <v>400</v>
       </c>
@@ -8556,12 +9878,12 @@
       <c r="J347" s="7"/>
       <c r="K347" s="6"/>
     </row>
-    <row r="348" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="348" ht="46.25">
       <c r="F348" s="16"/>
       <c r="G348" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I348" s="1" t="n">
+      <c r="I348" s="1">
         <v>209</v>
       </c>
       <c r="J348" s="7" t="s">
@@ -8570,8 +9892,11 @@
       <c r="K348" s="6" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="349" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L348" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="349" ht="13.8">
       <c r="B349" s="1" t="s">
         <v>412</v>
       </c>
@@ -8579,7 +9904,7 @@
         <v>18</v>
       </c>
       <c r="F349" s="16"/>
-      <c r="I349" s="1" t="n">
+      <c r="I349" s="1">
         <v>210</v>
       </c>
       <c r="J349" s="7" t="s">
@@ -8588,8 +9913,11 @@
       <c r="K349" s="1" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="350" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L349" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="350" ht="13.8">
       <c r="B350" s="1" t="s">
         <v>394</v>
       </c>
@@ -8597,7 +9925,7 @@
         <v>18</v>
       </c>
       <c r="F350" s="16"/>
-      <c r="I350" s="1" t="n">
+      <c r="I350" s="1">
         <v>211</v>
       </c>
       <c r="J350" s="7" t="s">
@@ -8606,13 +9934,16 @@
       <c r="K350" s="1" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="351" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L350" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="351" ht="13.8">
       <c r="F351" s="16"/>
       <c r="J351" s="7"/>
       <c r="K351" s="6"/>
     </row>
-    <row r="352" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="352" ht="13.8">
       <c r="A352" s="1" t="s">
         <v>412</v>
       </c>
@@ -8620,7 +9951,7 @@
       <c r="J352" s="7"/>
       <c r="K352" s="6"/>
     </row>
-    <row r="353" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="353" ht="13.8">
       <c r="E353" s="1" t="s">
         <v>413</v>
       </c>
@@ -8630,7 +9961,7 @@
       <c r="J353" s="7"/>
       <c r="K353" s="6"/>
     </row>
-    <row r="354" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" ht="13.8">
       <c r="A354" s="1" t="s">
         <v>405</v>
       </c>
@@ -8638,12 +9969,12 @@
       <c r="J354" s="7"/>
       <c r="K354" s="6"/>
     </row>
-    <row r="355" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" ht="46.25">
       <c r="F355" s="16"/>
       <c r="G355" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I355" s="1" t="n">
+      <c r="I355" s="1">
         <v>212</v>
       </c>
       <c r="J355" s="7" t="s">
@@ -8652,13 +9983,16 @@
       <c r="K355" s="6" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="356" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L355" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="356" ht="46.25">
       <c r="F356" s="16"/>
       <c r="G356" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I356" s="1" t="n">
+      <c r="I356" s="1">
         <v>213</v>
       </c>
       <c r="J356" s="7" t="s">
@@ -8667,8 +10001,11 @@
       <c r="K356" s="6" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="357" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L356" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="357" ht="13.8">
       <c r="E357" s="1" t="s">
         <v>419</v>
       </c>
@@ -8678,12 +10015,12 @@
       <c r="J357" s="7"/>
       <c r="K357" s="6"/>
     </row>
-    <row r="358" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="358" ht="13.8">
       <c r="F358" s="16"/>
       <c r="G358" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I358" s="1" t="n">
+      <c r="I358" s="1">
         <v>214</v>
       </c>
       <c r="J358" s="7" t="s">
@@ -8692,18 +10029,21 @@
       <c r="K358" s="6" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="359" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L358" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="359" ht="13.8">
       <c r="F359" s="16"/>
       <c r="J359" s="7"/>
       <c r="K359" s="6"/>
     </row>
-    <row r="360" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="360" ht="13.8">
       <c r="F360" s="16"/>
       <c r="G360" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I360" s="1" t="n">
+      <c r="I360" s="1">
         <v>215</v>
       </c>
       <c r="J360" s="7" t="s">
@@ -8712,13 +10052,16 @@
       <c r="K360" s="6" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="361" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L360" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="361" ht="13.8">
       <c r="F361" s="16"/>
       <c r="G361" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="I361" s="1" t="n">
+      <c r="I361" s="1">
         <v>216</v>
       </c>
       <c r="J361" s="7" t="s">
@@ -8727,8 +10070,11 @@
       <c r="K361" s="6" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="362" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L361" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="362" ht="13.8">
       <c r="E362" s="1" t="s">
         <v>383</v>
       </c>
@@ -8738,7 +10084,7 @@
       <c r="J362" s="7"/>
       <c r="K362" s="6"/>
     </row>
-    <row r="363" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="363" ht="13.8">
       <c r="E363" s="1" t="s">
         <v>383</v>
       </c>
@@ -8748,12 +10094,12 @@
       <c r="J363" s="7"/>
       <c r="K363" s="6"/>
     </row>
-    <row r="364" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="364" ht="68.65">
       <c r="F364" s="16"/>
       <c r="G364" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I364" s="1" t="n">
+      <c r="I364" s="1">
         <v>217</v>
       </c>
       <c r="J364" s="7" t="s">
@@ -8762,13 +10108,16 @@
       <c r="K364" s="6" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="365" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L364" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="365" ht="13.8">
       <c r="F365" s="16"/>
       <c r="G365" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I365" s="1" t="n">
+      <c r="I365" s="1">
         <v>218</v>
       </c>
       <c r="J365" s="7" t="s">
@@ -8777,13 +10126,16 @@
       <c r="K365" s="6" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="366" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L365" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="366" ht="13.8">
       <c r="F366" s="16"/>
       <c r="G366" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I366" s="1" t="n">
+      <c r="I366" s="1">
         <v>219</v>
       </c>
       <c r="J366" s="7" t="s">
@@ -8792,13 +10144,16 @@
       <c r="K366" s="6" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="367" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L366" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="367" ht="13.8">
       <c r="F367" s="16"/>
       <c r="G367" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I367" s="1" t="n">
+      <c r="I367" s="1">
         <v>220</v>
       </c>
       <c r="J367" s="7" t="s">
@@ -8807,13 +10162,16 @@
       <c r="K367" s="6" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="368" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L367" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="368" ht="13.8">
       <c r="F368" s="16"/>
       <c r="J368" s="7"/>
       <c r="K368" s="6"/>
     </row>
-    <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="369" ht="12.8">
       <c r="E369" s="1" t="s">
         <v>433</v>
       </c>
@@ -8822,16 +10180,16 @@
       </c>
       <c r="J369" s="6"/>
     </row>
-    <row r="370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="370" ht="12.8">
       <c r="F370" s="16"/>
       <c r="J370" s="6"/>
     </row>
-    <row r="371" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="371" ht="13.8">
       <c r="F371" s="16"/>
       <c r="J371" s="3"/>
       <c r="K371" s="4"/>
     </row>
-    <row r="372" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="372" ht="13.8">
       <c r="E372" s="1" t="s">
         <v>435</v>
       </c>
@@ -8839,7 +10197,7 @@
       <c r="J372" s="3"/>
       <c r="K372" s="4"/>
     </row>
-    <row r="373" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="373" ht="13.8">
       <c r="E373" s="1" t="s">
         <v>239</v>
       </c>
@@ -8849,17 +10207,17 @@
       <c r="J373" s="3"/>
       <c r="K373" s="4"/>
     </row>
-    <row r="374" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="374" ht="13.8">
       <c r="E374" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="F374" s="16" t="n">
+      <c r="F374" s="16">
         <v>107</v>
       </c>
       <c r="J374" s="3"/>
       <c r="K374" s="4"/>
     </row>
-    <row r="375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="375" ht="12.8">
       <c r="E375" s="1" t="s">
         <v>239</v>
       </c>
@@ -8867,12 +10225,12 @@
         <v>436</v>
       </c>
     </row>
-    <row r="376" customFormat="false" ht="45.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="376" ht="45.5">
       <c r="F376" s="16"/>
       <c r="G376" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="I376" s="1" t="n">
+      <c r="I376" s="1">
         <v>221</v>
       </c>
       <c r="J376" s="6" t="s">
@@ -8881,13 +10239,16 @@
       <c r="K376" s="6" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="377" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L376" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="377" ht="13.8">
       <c r="F377" s="16"/>
       <c r="G377" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I377" s="1" t="n">
+      <c r="I377" s="1">
         <v>222</v>
       </c>
       <c r="J377" s="7" t="s">
@@ -8896,13 +10257,16 @@
       <c r="K377" s="6" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="378" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L377" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="378" ht="13.8">
       <c r="F378" s="16"/>
       <c r="G378" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I378" s="1" t="n">
+      <c r="I378" s="1">
         <v>223</v>
       </c>
       <c r="J378" s="7" t="s">
@@ -8911,13 +10275,16 @@
       <c r="K378" s="6" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="379" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L378" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="379" ht="23.85">
       <c r="F379" s="16"/>
       <c r="G379" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="I379" s="1" t="n">
+      <c r="I379" s="1">
         <v>224</v>
       </c>
       <c r="J379" s="18" t="s">
@@ -8926,13 +10293,16 @@
       <c r="K379" s="6" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="380" customFormat="false" ht="23.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L379" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="380" ht="23.1">
       <c r="F380" s="16"/>
       <c r="G380" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I380" s="1" t="n">
+      <c r="I380" s="1">
         <v>225</v>
       </c>
       <c r="J380" s="18" t="s">
@@ -8941,13 +10311,16 @@
       <c r="K380" s="6" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="381" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L380" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="381" ht="79.85">
       <c r="F381" s="16"/>
       <c r="G381" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I381" s="1" t="n">
+      <c r="I381" s="1">
         <v>226</v>
       </c>
       <c r="J381" s="7" t="s">
@@ -8956,8 +10329,11 @@
       <c r="K381" s="6" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L381" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="382" ht="12.8">
       <c r="E382" s="1" t="s">
         <v>433</v>
       </c>
@@ -8965,7 +10341,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="383" ht="12.8">
       <c r="E383" s="1" t="s">
         <v>239</v>
       </c>
@@ -8973,7 +10349,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="384" ht="12.8">
       <c r="E384" s="1" t="s">
         <v>433</v>
       </c>
@@ -8981,22 +10357,22 @@
         <v>451</v>
       </c>
     </row>
-    <row r="385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="385" ht="12.8">
       <c r="E385" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F385" s="16"/>
     </row>
-    <row r="386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="386" ht="12.8">
       <c r="F386" s="16"/>
     </row>
-    <row r="388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="388" ht="12.8">
       <c r="A388" s="1" t="s">
         <v>452</v>
       </c>
       <c r="F388" s="16"/>
     </row>
-    <row r="389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="389" ht="12.8">
       <c r="E389" s="1" t="s">
         <v>239</v>
       </c>
@@ -9004,21 +10380,21 @@
         <v>200</v>
       </c>
     </row>
-    <row r="390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="390" ht="12.8">
       <c r="E390" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="F390" s="1" t="n">
+      <c r="F390" s="1">
         <v>1</v>
       </c>
       <c r="G390" s="6"/>
       <c r="J390" s="6"/>
     </row>
-    <row r="392" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="392" ht="13.8">
       <c r="G392" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I392" s="1" t="n">
+      <c r="I392" s="1">
         <v>230</v>
       </c>
       <c r="J392" s="7" t="s">
@@ -9027,13 +10403,16 @@
       <c r="K392" s="6" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L392" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="393" ht="12.8">
       <c r="F393" s="16"/>
       <c r="G393" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I393" s="1" t="n">
+      <c r="I393" s="1">
         <v>231</v>
       </c>
       <c r="J393" s="6" t="s">
@@ -9042,13 +10421,16 @@
       <c r="K393" s="6" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="394" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L393" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="394" ht="22.35">
       <c r="F394" s="16"/>
       <c r="G394" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I394" s="1" t="n">
+      <c r="I394" s="1">
         <v>232</v>
       </c>
       <c r="J394" s="18" t="s">
@@ -9057,13 +10439,16 @@
       <c r="K394" s="6" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="395" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L394" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="395" ht="43.25">
       <c r="F395" s="16"/>
       <c r="G395" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I395" s="1" t="n">
+      <c r="I395" s="1">
         <v>233</v>
       </c>
       <c r="J395" s="18" t="s">
@@ -9072,13 +10457,16 @@
       <c r="K395" s="6" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="396" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L395" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="396" ht="23.85">
       <c r="F396" s="16"/>
       <c r="G396" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I396" s="1" t="n">
+      <c r="I396" s="1">
         <v>234</v>
       </c>
       <c r="J396" s="7" t="s">
@@ -9087,13 +10475,16 @@
       <c r="K396" s="6" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="397" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L396" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="397" ht="32.8">
       <c r="F397" s="16"/>
       <c r="G397" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I397" s="1" t="n">
+      <c r="I397" s="1">
         <v>235</v>
       </c>
       <c r="J397" s="6" t="s">
@@ -9102,27 +10493,30 @@
       <c r="K397" s="6" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L397" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="398" ht="12.8">
       <c r="F398" s="16"/>
       <c r="J398" s="6"/>
     </row>
-    <row r="399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="399" ht="12.8">
       <c r="E399" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F399" s="16"/>
     </row>
-    <row r="400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="400" ht="12.8">
       <c r="F400" s="16"/>
     </row>
-    <row r="401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="401" ht="12.8">
       <c r="A401" s="1" t="s">
         <v>466</v>
       </c>
       <c r="F401" s="16"/>
     </row>
-    <row r="403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="403" ht="12.8">
       <c r="E403" s="6" t="s">
         <v>79</v>
       </c>
@@ -9132,15 +10526,15 @@
       <c r="G403" s="6"/>
       <c r="J403" s="6"/>
     </row>
-    <row r="404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="404" ht="12.8">
       <c r="E404" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F404" s="6" t="n">
+      <c r="F404" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="405" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="405" ht="13.8">
       <c r="E405" s="6" t="s">
         <v>82</v>
       </c>
@@ -9150,41 +10544,41 @@
       <c r="J405" s="7"/>
       <c r="K405" s="6"/>
     </row>
-    <row r="406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="406" ht="12.8">
       <c r="E406" s="6"/>
       <c r="F406" s="10"/>
       <c r="J406" s="6"/>
       <c r="K406" s="6"/>
     </row>
-    <row r="407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="407" ht="12.8">
       <c r="E407" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F407" s="1" t="n">
+      <c r="F407" s="1">
         <v>41</v>
       </c>
       <c r="J407" s="6"/>
       <c r="K407" s="6"/>
     </row>
-    <row r="408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="408" ht="12.8">
       <c r="E408" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F408" s="6" t="n">
+      <c r="F408" s="6">
         <v>2</v>
       </c>
       <c r="J408" s="18"/>
       <c r="K408" s="6"/>
     </row>
-    <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="409" ht="12.8">
       <c r="J409" s="18"/>
       <c r="K409" s="6"/>
     </row>
-    <row r="410" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="410" ht="13.8">
       <c r="G410" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="I410" s="1" t="n">
+      <c r="I410" s="1">
         <v>250</v>
       </c>
       <c r="J410" s="15" t="s">
@@ -9193,12 +10587,15 @@
       <c r="K410" s="6" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="411" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L410" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="411" ht="13.8">
       <c r="G411" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I411" s="1" t="n">
+      <c r="I411" s="1">
         <v>251</v>
       </c>
       <c r="J411" s="7" t="s">
@@ -9207,12 +10604,15 @@
       <c r="K411" s="6" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="412" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L411" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="412" ht="35.05">
       <c r="G412" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="I412" s="1" t="n">
+      <c r="I412" s="1">
         <v>252</v>
       </c>
       <c r="J412" s="7" t="s">
@@ -9221,12 +10621,15 @@
       <c r="K412" s="6" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="413" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L412" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="413" ht="46.25">
       <c r="G413" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I413" s="1" t="n">
+      <c r="I413" s="1">
         <v>253</v>
       </c>
       <c r="J413" s="7" t="s">
@@ -9235,12 +10638,15 @@
       <c r="K413" s="6" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="414" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L413" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="414" ht="13.8">
       <c r="G414" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="I414" s="1" t="n">
+      <c r="I414" s="1">
         <v>254</v>
       </c>
       <c r="J414" s="15" t="s">
@@ -9249,12 +10655,15 @@
       <c r="K414" s="6" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="415" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L414" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="415" ht="46.25">
       <c r="G415" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I415" s="1" t="n">
+      <c r="I415" s="1">
         <v>255</v>
       </c>
       <c r="J415" s="7" t="s">
@@ -9263,12 +10672,15 @@
       <c r="K415" s="6" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="416" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L415" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="416" ht="13.8">
       <c r="G416" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I416" s="1" t="n">
+      <c r="I416" s="1">
         <v>256</v>
       </c>
       <c r="J416" s="7" t="s">
@@ -9277,12 +10689,15 @@
       <c r="K416" s="6" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="417" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L416" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="417" ht="13.8">
       <c r="G417" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I417" s="1" t="n">
+      <c r="I417" s="1">
         <v>257</v>
       </c>
       <c r="J417" s="7" t="s">
@@ -9291,12 +10706,15 @@
       <c r="K417" s="6" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="418" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L417" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="418" ht="23.85">
       <c r="G418" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I418" s="1" t="n">
+      <c r="I418" s="1">
         <v>258</v>
       </c>
       <c r="J418" s="7" t="s">
@@ -9305,12 +10723,15 @@
       <c r="K418" s="6" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="419" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L418" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="419" ht="68.65">
       <c r="G419" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I419" s="1" t="n">
+      <c r="I419" s="1">
         <v>259</v>
       </c>
       <c r="J419" s="7" t="s">
@@ -9319,12 +10740,15 @@
       <c r="K419" s="6" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="420" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L419" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="420" ht="13.8">
       <c r="G420" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I420" s="1" t="n">
+      <c r="I420" s="1">
         <v>260</v>
       </c>
       <c r="J420" s="7" t="s">
@@ -9333,12 +10757,15 @@
       <c r="K420" s="6" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="421" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L420" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="421" ht="23.85">
       <c r="G421" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I421" s="1" t="n">
+      <c r="I421" s="1">
         <v>261</v>
       </c>
       <c r="J421" s="7" t="s">
@@ -9347,12 +10774,15 @@
       <c r="K421" s="9" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="422" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L421" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="422" ht="23.85">
       <c r="G422" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I422" s="1" t="n">
+      <c r="I422" s="1">
         <v>262</v>
       </c>
       <c r="J422" s="7" t="s">
@@ -9361,12 +10791,15 @@
       <c r="K422" s="6" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="423" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L422" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="423" ht="23.85">
       <c r="G423" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I423" s="1" t="n">
+      <c r="I423" s="1">
         <v>263</v>
       </c>
       <c r="J423" s="7" t="s">
@@ -9375,52 +10808,55 @@
       <c r="K423" s="6" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="424" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L423" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="424" ht="13.8">
       <c r="J424" s="7"/>
       <c r="K424" s="6"/>
     </row>
-    <row r="425" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="425" ht="13.8">
       <c r="E425" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F425" s="6" t="n">
+      <c r="F425" s="6">
         <v>2</v>
       </c>
       <c r="J425" s="7"/>
       <c r="K425" s="6"/>
     </row>
-    <row r="426" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="426" ht="13.8">
       <c r="E426" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F426" s="1" t="n">
+      <c r="F426" s="1">
         <v>13</v>
       </c>
       <c r="J426" s="7"/>
       <c r="K426" s="6"/>
     </row>
-    <row r="427" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="427" ht="13.8">
       <c r="E427" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F427" s="6" t="n">
+      <c r="F427" s="6">
         <v>2</v>
       </c>
       <c r="G427" s="6"/>
       <c r="J427" s="7"/>
       <c r="K427" s="6"/>
     </row>
-    <row r="428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="428" ht="12.8">
       <c r="J428" s="18"/>
       <c r="K428" s="6"/>
     </row>
-    <row r="429" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="429" ht="13.8">
       <c r="F429" s="16"/>
       <c r="G429" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I429" s="1" t="n">
+      <c r="I429" s="1">
         <v>264</v>
       </c>
       <c r="J429" s="7" t="s">
@@ -9429,13 +10865,16 @@
       <c r="K429" s="6" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="430" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L429" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="430" ht="46.25">
       <c r="F430" s="16"/>
       <c r="G430" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I430" s="1" t="n">
+      <c r="I430" s="1">
         <v>265</v>
       </c>
       <c r="J430" s="7" t="s">
@@ -9444,13 +10883,16 @@
       <c r="K430" s="6" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="431" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L430" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="431" ht="13.8">
       <c r="F431" s="16"/>
       <c r="G431" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I431" s="1" t="n">
+      <c r="I431" s="1">
         <v>266</v>
       </c>
       <c r="J431" s="7" t="s">
@@ -9459,13 +10901,16 @@
       <c r="K431" s="9" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="432" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L431" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="432" ht="91">
       <c r="F432" s="16"/>
       <c r="G432" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I432" s="1" t="n">
+      <c r="I432" s="1">
         <v>267</v>
       </c>
       <c r="J432" s="7" t="s">
@@ -9474,13 +10919,16 @@
       <c r="K432" s="6" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="433" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L432" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="433" ht="13.8">
       <c r="F433" s="16"/>
       <c r="G433" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I433" s="1" t="n">
+      <c r="I433" s="1">
         <v>268</v>
       </c>
       <c r="J433" s="7" t="s">
@@ -9489,13 +10937,16 @@
       <c r="K433" s="6" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="434" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L433" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="434" ht="35.05">
       <c r="F434" s="16"/>
       <c r="G434" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I434" s="1" t="n">
+      <c r="I434" s="1">
         <v>269</v>
       </c>
       <c r="J434" s="7" t="s">
@@ -9504,13 +10955,16 @@
       <c r="K434" s="6" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="435" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L434" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="435" ht="68.65">
       <c r="F435" s="16"/>
       <c r="G435" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I435" s="1" t="n">
+      <c r="I435" s="1">
         <v>270</v>
       </c>
       <c r="J435" s="7" t="s">
@@ -9519,13 +10973,16 @@
       <c r="K435" s="6" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="436" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L435" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="436" ht="85.05">
       <c r="F436" s="16"/>
       <c r="G436" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I436" s="1" t="n">
+      <c r="I436" s="1">
         <v>271</v>
       </c>
       <c r="J436" s="19" t="s">
@@ -9534,13 +10991,16 @@
       <c r="K436" s="6" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="437" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L436" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="437" ht="46.25">
       <c r="F437" s="16"/>
       <c r="G437" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I437" s="1" t="n">
+      <c r="I437" s="1">
         <v>272</v>
       </c>
       <c r="J437" s="7" t="s">
@@ -9549,13 +11009,16 @@
       <c r="K437" s="6" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="438" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L437" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="438" ht="13.8">
       <c r="F438" s="16"/>
       <c r="G438" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I438" s="1" t="n">
+      <c r="I438" s="1">
         <v>273</v>
       </c>
       <c r="J438" s="7" t="s">
@@ -9564,13 +11027,16 @@
       <c r="K438" s="6" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="439" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L438" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="439" ht="35.05">
       <c r="F439" s="16"/>
       <c r="G439" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I439" s="1" t="n">
+      <c r="I439" s="1">
         <v>274</v>
       </c>
       <c r="J439" s="7" t="s">
@@ -9579,13 +11045,16 @@
       <c r="K439" s="6" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="440" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L439" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="440" ht="13.8">
       <c r="F440" s="16"/>
       <c r="G440" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I440" s="1" t="n">
+      <c r="I440" s="1">
         <v>275</v>
       </c>
       <c r="J440" s="7" t="s">
@@ -9594,13 +11063,16 @@
       <c r="K440" s="6" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="441" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L440" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="441" ht="13.8">
       <c r="F441" s="16"/>
       <c r="G441" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I441" s="1" t="n">
+      <c r="I441" s="1">
         <v>276</v>
       </c>
       <c r="J441" s="7" t="s">
@@ -9609,13 +11081,16 @@
       <c r="K441" s="6" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="442" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L441" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="442" ht="13.8">
       <c r="F442" s="16"/>
       <c r="G442" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I442" s="1" t="n">
+      <c r="I442" s="1">
         <v>277</v>
       </c>
       <c r="J442" s="7" t="s">
@@ -9624,13 +11099,16 @@
       <c r="K442" s="6" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="443" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L442" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="443" ht="13.8">
       <c r="F443" s="16"/>
       <c r="G443" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I443" s="1" t="n">
+      <c r="I443" s="1">
         <v>278</v>
       </c>
       <c r="J443" s="7" t="s">
@@ -9639,13 +11117,16 @@
       <c r="K443" s="6" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="444" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L443" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="444" ht="64.15">
       <c r="F444" s="16"/>
       <c r="G444" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I444" s="1" t="n">
+      <c r="I444" s="1">
         <v>279</v>
       </c>
       <c r="J444" s="7" t="s">
@@ -9654,13 +11135,16 @@
       <c r="K444" s="6" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="445" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L444" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="445" ht="53.7">
       <c r="F445" s="16"/>
       <c r="G445" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I445" s="1" t="n">
+      <c r="I445" s="1">
         <v>280</v>
       </c>
       <c r="J445" s="19" t="s">
@@ -9669,13 +11153,16 @@
       <c r="K445" s="6" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="446" customFormat="false" ht="76.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L445" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="446" ht="76.85">
       <c r="F446" s="16"/>
       <c r="G446" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I446" s="1" t="n">
+      <c r="I446" s="1">
         <v>281</v>
       </c>
       <c r="J446" s="7" t="s">
@@ -9684,18 +11171,21 @@
       <c r="K446" s="6" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="447" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L446" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="447" ht="13.8">
       <c r="F447" s="16"/>
       <c r="J447" s="7"/>
       <c r="K447" s="6"/>
     </row>
-    <row r="448" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="448" ht="13.8">
       <c r="F448" s="16"/>
       <c r="J448" s="7"/>
       <c r="K448" s="6"/>
     </row>
-    <row r="449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="449" ht="12.8">
       <c r="E449" s="1" t="s">
         <v>75</v>
       </c>
@@ -9703,11 +11193,11 @@
       <c r="J449" s="6"/>
       <c r="K449" s="6"/>
     </row>
-    <row r="450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="450" ht="12.8">
       <c r="F450" s="16"/>
       <c r="J450" s="6"/>
     </row>
-    <row r="451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="451" ht="12.8">
       <c r="E451" s="1" t="s">
         <v>76</v>
       </c>
@@ -9715,18 +11205,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I374 I384:I1048576">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I383 I375:I381">
-    <cfRule type="duplicateValues" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I382">
-    <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
